--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,6 @@
       <c r="L2" t="n">
         <v>20</v>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -695,7 +694,6 @@
       <c r="L4" t="n">
         <v>20</v>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -996,7 +994,6 @@
       <c r="L9" t="n">
         <v>13.58</v>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1419,7 +1416,6 @@
       <c r="L16" t="n">
         <v>9.99</v>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1476,7 +1472,6 @@
       <c r="L17" t="n">
         <v>9.99</v>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1655,7 +1650,6 @@
       <c r="L20" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1728,8 +1722,1216 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TECHNOCRAF</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Technocraft Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>317.68</v>
+      </c>
+      <c r="F22" t="n">
+        <v>284</v>
+      </c>
+      <c r="G22" t="n">
+        <v>318</v>
+      </c>
+      <c r="H22" t="n">
+        <v>284</v>
+      </c>
+      <c r="I22" t="n">
+        <v>212</v>
+      </c>
+      <c r="J22" t="n">
+        <v>317.68</v>
+      </c>
+      <c r="K22" t="n">
+        <v>12239375</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Technocraft Ventures Ltd. Share Price Today - Technocraft Ventures Ltd. Stock Price Live NSE/BSE - cnbctv18.com</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>['Technocraft Ventures Ltd. Share Price Today - Technocraft Ventures Ltd. Stock Price Live NSE/BSE - cnbctv18.com', 'Technocraft Ventures IPO Allotment Status: How to check share allotment online on NSE, BSE - Zee Business', 'Technocraft Ventures Limited: Performance &amp; Quotes, TECHNOCRAF Stock Price on NSE India S.E. Exchange - marketscreener.com', 'Technocraft Ventures IPO allotment status: How to check online on NSE, BSE, KFin Technologies - Dailyhunt', 'IPO Review: Technocraft Ventures Limited - moneylife.in']</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="F23" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="G23" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="H23" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="J23" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="K23" t="n">
+        <v>107009</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>['【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com', 'Bilcare Limited Announces Winding Up of Bilcare INC, A Wholly Owned Subsidiary of the Company - marketscreener.com', 'China’s CSI 300 Set to Lose Appeal Before Adding CXMT, BI Says - Bloomberg.com', "What AI-native analytics startups offer that BI vendors don't - techtarget.com", 'Shein IPO Value to Fall Short of $30 Billion Targeted by Some Investors, BI Says - Bloomberg.com']</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Limited</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="F24" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>403.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="J24" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4696738</v>
+      </c>
+      <c r="L24" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Apex Treasury Corporation Reports Earnings Results for the Second Quarter and Six Months Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>['Apex Treasury Corporation Reports Earnings Results for the Second Quarter and Six Months Ended June 30, 2026 - marketscreener.com', 'Apex Biotechnology Corp. Reports Earnings Results for the Second Quarter and Six Months Ended June 30, 2026 - marketscreener.com', 'Maha Rashtra Apex Q1 Results: Consolidated profit up 85% YoY to ₹347.6 lakh - scanx.trade', 'Apex Capital &amp; Finance Q1 Results: Net profit rises 74% YoY - scanx.trade', 'Apex Capital and Finance Q1 Results: Net profit rises 73% YoY - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G25" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H25" t="n">
+        <v>11</v>
+      </c>
+      <c r="I25" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="J25" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>913586</v>
+      </c>
+      <c r="L25" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K26" t="n">
+        <v>8163583</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>GALAXYSURF</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Galaxy Surfactants Limited</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>2497.8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>2412.5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2508.4</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2391.2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>2090.4</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2497.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>434720</v>
+      </c>
+      <c r="L27" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Galaxy Surfactants approves ₹22 final dividend at 40th AGM - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>['Galaxy Surfactants approves ₹22 final dividend at 40th AGM - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MANORAMA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Manorama Industries Limited</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1861</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1729</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1868</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1683.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1614.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1861</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2704746</v>
+      </c>
+      <c r="L28" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Manorama Industries: Final Dividend Record Date Announced - InvestyWise</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>['Manorama Industries: Final Dividend Record Date Announced - InvestyWise', 'MANORAMA: Q1FY27 revenue up 39.5% YoY, PAT up 67.6% YoY, with strong global expansion and capex plans - TradingView', 'What is ‘One Herb, One Standard initiative’? - Manorama Yearbook', 'National Commission for Scheduled Castes submits annual report to President Murmu - Manorama Yearbook', 'Congo’s Ebola outbreak set to become deadliest on record, warns WHO - Manorama Yearbook']</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HMAAGRO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="F29" t="n">
+        <v>23</v>
+      </c>
+      <c r="G29" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="H29" t="n">
+        <v>22</v>
+      </c>
+      <c r="I29" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="J29" t="n">
+        <v>25.08</v>
+      </c>
+      <c r="K29" t="n">
+        <v>5532483</v>
+      </c>
+      <c r="L29" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Q1 Results: Earnings Call Scheduled for Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>['HMA Agro Industries Q1 Results: Earnings Call Scheduled for Aug 14 - scanx.trade', 'HMA Agro Industries reports ₹21,103.19 million revenue for Q1 FY 2026-2027 - Business Upturn', 'HMA Agro Publishes Investor Presentation for June 2026 Quarter - tipranks.com', 'HMA Agro Industries Releases Q1 FY2026 Investor Presentation - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>LPDC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Landmark Property Development Company Limited</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="F30" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="G30" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="J30" t="n">
+        <v>8.65</v>
+      </c>
+      <c r="K30" t="n">
+        <v>1007660</v>
+      </c>
+      <c r="L30" t="n">
+        <v>14.42</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Gadzama to Rely on 2015 NBA Clearance in Appeal Against LPDC Suspension - Radio Nigeria Lagos</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>['Gadzama to Rely on 2015 NBA Clearance in Appeal Against LPDC Suspension - Radio Nigeria Lagos', 'LPDC Target Crowned Sarawak Closed Doubles Darts Champions - Sarawak Tribune', 'Zaki Biam Killings: LPDC Slams Three Years Suspension on Gadzama for Professional Misconduct - THISDAYLIVE', 'Full reasons why LPDC suspended senior advocate Gadzama, fellow lawyer from legal practice (DOWNLOAD) - Premium Times Nigeria', 'LPDC fixes Sept 30 for ruling in c’s alleged misconduct case - The Nation Newspaper']</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>XTRANET</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>168.17</v>
+      </c>
+      <c r="F31" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="I31" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="J31" t="n">
+        <v>168.17</v>
+      </c>
+      <c r="K31" t="n">
+        <v>737568</v>
+      </c>
+      <c r="L31" t="n">
+        <v>11.82</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies IPO Lists At Premium On NSE And BSE - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>['Xtranet Technologies IPO Lists At Premium On NSE And BSE - NDTV Profit', 'Price to earnings ratio of Xtranet Technologies Limited – NSE:XTRANET - TradingView', 'Indo-MIM, Lohia Corp, Xtranet Technologies List At A Premium; Check Share Price - NDTV Profit', 'Xtranet Technologies Limited Revenue Breakdown – NSE:XTRANET - TradingView', 'Xtranet Technologies Limited Income Statement – NSE:XTRANET - TradingView']</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BALUFORGE</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Limited</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>450</v>
+      </c>
+      <c r="G32" t="n">
+        <v>503</v>
+      </c>
+      <c r="H32" t="n">
+        <v>449.15</v>
+      </c>
+      <c r="I32" t="n">
+        <v>446.25</v>
+      </c>
+      <c r="J32" t="n">
+        <v>493.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3159579</v>
+      </c>
+      <c r="L32" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries announces strong Q1 FY27 results with aerospace sector entry - Business Upturn</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>['Balu Forge Industries announces strong Q1 FY27 results with aerospace sector entry - Business Upturn', 'Balu Forge Industries Q1 FY27: Net Profit Rises 15.9% YoY; Board Approves $60 Million Fundraise - Trade Brains', 'Balu Forge Board Approves $60M FCCB Issue &amp; ₹1000Cr Borrowing Hike - InvestyWise']</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Welspun Living Limited</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>174.82</v>
+      </c>
+      <c r="F33" t="n">
+        <v>170</v>
+      </c>
+      <c r="G33" t="n">
+        <v>178</v>
+      </c>
+      <c r="H33" t="n">
+        <v>165.16</v>
+      </c>
+      <c r="I33" t="n">
+        <v>159.83</v>
+      </c>
+      <c r="J33" t="n">
+        <v>174.82</v>
+      </c>
+      <c r="K33" t="n">
+        <v>37599345</v>
+      </c>
+      <c r="L33" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>WELSPUNLIV Share Price Today - Welspun Living on NSE/BSE - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>['WELSPUNLIV Share Price Today - Welspun Living on NSE/BSE - scanx.trade', 'Number of shareholders of Welspun Living Limited – NSE:WELSPUNLIV - TradingView', 'Earnings call transcript: Welspun Living lifts Q1 2026 sales, stock falls 3.3% - Investing.com India', 'Welspun Living: Strong Q1 FY27 Results with Revenue Up 23.5% - InvestyWise', 'Welspun Living: Q1 FY27 Revenue Jumps 23.5% to ₹2,828 Crore - InvestyWise']</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ZEEMEDIA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Zee Media Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="H34" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9.369999999999999</v>
+      </c>
+      <c r="K34" t="n">
+        <v>26669502</v>
+      </c>
+      <c r="L34" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ATAM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Atam Valves Limited</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="F35" t="n">
+        <v>54.8</v>
+      </c>
+      <c r="G35" t="n">
+        <v>59.95</v>
+      </c>
+      <c r="H35" t="n">
+        <v>54.53</v>
+      </c>
+      <c r="I35" t="n">
+        <v>54.35</v>
+      </c>
+      <c r="J35" t="n">
+        <v>59.25</v>
+      </c>
+      <c r="K35" t="n">
+        <v>44189</v>
+      </c>
+      <c r="L35" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>['Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade', 'Community Highlights: Meet Dunebari Atam of Blueprint Financial Firm &amp; EveryOneWins - voyagedallas.com']</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TIIL</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Technocraft Industries (India) Limited</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>3136.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>3145</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3299.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3061.2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2887.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>3136.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>458617</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Tiil Morning Airbus A380 (9GrJB881u0) - Mshale</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>['Tiil Morning Airbus A380 (9GrJB881u0) - Mshale']</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ISFT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Intrasoft Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>83</v>
+      </c>
+      <c r="F37" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="G37" t="n">
+        <v>84.5</v>
+      </c>
+      <c r="H37" t="n">
+        <v>77.89</v>
+      </c>
+      <c r="I37" t="n">
+        <v>76.70999999999999</v>
+      </c>
+      <c r="J37" t="n">
+        <v>83</v>
+      </c>
+      <c r="K37" t="n">
+        <v>14255</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>IntraSoft Technologies Limited (533181.BO) stock price, news, quote and history - Yahoo Finance UK</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>['IntraSoft Technologies Limited (533181.BO) stock price, news, quote and history - Yahoo Finance UK', 'Intrasoft Technologies Releases Q1 FY2026 Investor Presentation - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LG Electronics India Limited</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>1701.8</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1704.7</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1611</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1578.3</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1701.8</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4442442</v>
+      </c>
+      <c r="L38" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>LG Electronics India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>['LG Electronics India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'LG Electronics India Q1 Results: Earnings call scheduled for Aug 14 - scanx.trade', "LG Electronics India's quarterly profit rises on strong summer appliance sales - marketscreener.com", 'LG Electronics India Posts Strongest Quarterly Growth Since Listing - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>AYMSYNTEX</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>AYM Syntex Limited</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>274.95</v>
+      </c>
+      <c r="F39" t="n">
+        <v>261.75</v>
+      </c>
+      <c r="G39" t="n">
+        <v>276.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>258</v>
+      </c>
+      <c r="I39" t="n">
+        <v>256.45</v>
+      </c>
+      <c r="J39" t="n">
+        <v>274.95</v>
+      </c>
+      <c r="K39" t="n">
+        <v>37857</v>
+      </c>
+      <c r="L39" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>AYM Syntex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>['AYM Syntex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>JNKINDIA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>JNK India Limited</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="F40" t="n">
+        <v>429.85</v>
+      </c>
+      <c r="G40" t="n">
+        <v>449.95</v>
+      </c>
+      <c r="H40" t="n">
+        <v>425</v>
+      </c>
+      <c r="I40" t="n">
+        <v>413.15</v>
+      </c>
+      <c r="J40" t="n">
+        <v>441.75</v>
+      </c>
+      <c r="K40" t="n">
+        <v>551045</v>
+      </c>
+      <c r="L40" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>JNKINDIA: Revenue and profit surged in Q1 FY 2027, with strong order book and diversification underway - TradingView</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>['JNKINDIA: Revenue and profit surged in Q1 FY 2027, with strong order book and diversification underway - TradingView', 'JNKINDIA: Revenue up 80.6% YoY; order book at INR 1,801 cr; diversification on track - TradingView', 'JNKINDIA: Q1FY27 delivered 80.6% YoY income growth and robust margins, with strong order visibility - TradingView', 'JNK India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'JNK India Q1 Results: Net profit surges 1,059% YoY to ₹96.25 million - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MOTISONS</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Limited</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="F41" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G41" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="H41" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="I41" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="J41" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="K41" t="n">
+        <v>69267238</v>
+      </c>
+      <c r="L41" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Q1 Results: Net profit up 38% to ₹110.5 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>['Motisons Jewellers Q1 Results: Net profit up 38% to ₹110.5 crore - scanx.trade', "Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn", 'Motisons Jewellers standalone net profit rises 37.61% in the June 2026 quarter - business-standard.com', 'Motisons Jewellers Ltd Revenue Breakdown – NSE:MOTISONS - TradingView', 'Black Box shares jump over 7% after Q1 EBITDA rises 39% YoY to Rs 150 crore, revenue grows 24% - Business Upturn']</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1740,7 +2942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2248,7 +3450,6 @@
       <c r="L8" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2488,7 +3689,6 @@
       <c r="L12" t="n">
         <v>-8.58</v>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2911,7 +4111,6 @@
       <c r="L19" t="n">
         <v>-13.34</v>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3045,8 +4244,1188 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LEAPIND</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LEAP India Limited</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>153.46</v>
+      </c>
+      <c r="F22" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>167</v>
+      </c>
+      <c r="H22" t="n">
+        <v>152.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>159</v>
+      </c>
+      <c r="J22" t="n">
+        <v>153.46</v>
+      </c>
+      <c r="K22" t="n">
+        <v>49822702</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Basic earnings per share (basic EPS) of LEAP India Limited – NSE:LEAP - TradingView</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>['Basic earnings per share (basic EPS) of LEAP India Limited – NSE:LEAP - TradingView', 'Operating margin % of LEAP India Limited – NSE:LEAP - TradingView', 'LEAP India Limited Revenue Breakdown – NSE:LEAP - TradingView', 'LEAP India Limited Balance Sheet – NSE:LEAP - TradingView', 'LEAP India Limited Cash Flow – NSE:LEAP - TradingView']</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TMPV</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Tata Motors Passenger Vehicles Limited</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="F23" t="n">
+        <v>329</v>
+      </c>
+      <c r="G23" t="n">
+        <v>337.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>329</v>
+      </c>
+      <c r="I23" t="n">
+        <v>349.6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>330.8</v>
+      </c>
+      <c r="K23" t="n">
+        <v>14687197</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-5.38</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Q1 Results 14th Aug Live: Anupam Rasayan PAT up marginally, Ashok Leyland, NMDC, Alkem Lab, Bharat Dynamics, Voltas, 3M India, Cochin Shipyard, Physicswallah, Cholamandalam Fin, PTC Ind, Natco Pharma, Borosil to announce Q1 results, TMPV, Ma - BusinessLine</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>['Q1 Results 14th Aug Live: Anupam Rasayan PAT up marginally, Ashok Leyland, NMDC, Alkem Lab, Bharat Dynamics, Voltas, 3M India, Cochin Shipyard, Physicswallah, Cholamandalam Fin, PTC Ind, Natco Pharma, Borosil to announce Q1 results, TMPV, Ma - BusinessLine', 'Q1 Results 13th Aug Live: TMPV, Solar Ind, LG Electronics, Max Healthcare, GIC, Godrej Ind, Jubilant Foodworks, Amber Enterprises, Indraprastha Gas, Brigade, JSW Cement, Honasa Consumer to announce Q1 results, Tata Motors, HAL, Apollo Hospitals, Gr - BusinessLine', 'TMPV shares fall nearly 6% as JLR weakness and margin concerns weigh, brokerages divided - BusinessLine', 'Stocks to watch: Honasa, LG Electronics, Physicswalla, NMDC, TMPV - business-standard.com', 'Remain fully focused on driving growth: TMPV amid imminent change in Tata Group leadership - The Hans India']</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ZOTA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Zota Health Care LImited</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>1173.7</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1231.3</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1236.1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1163.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1241.3</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1173.7</v>
+      </c>
+      <c r="K24" t="n">
+        <v>79127</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Zota Health Care Ltd Says June-Quarter Consol Net Loss 435.6 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>['Zota Health Care Ltd Says June-Quarter Consol Net Loss 435.6 Million Rupees - TradingView', 'Q1 Results: Tata Motors PV, Solar Industries, LG Electronics, Max Healthcare, General Insurance, Page Industries, others to declare earnings on August 13 - Dailyhunt', 'Zota Health Care Ltd is Rated Strong Sell - MarketsMojo', 'Water and energy jobs push Costain to ‘inflection point’ - Construction News']</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>VPRPL</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Vishnu Prakash R Punglia Limited</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G25" t="n">
+        <v>36</v>
+      </c>
+      <c r="H25" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="I25" t="n">
+        <v>34.97</v>
+      </c>
+      <c r="J25" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="K25" t="n">
+        <v>689181</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>GOCLCORP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GOCL Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>405.8</v>
+      </c>
+      <c r="F26" t="n">
+        <v>417.55</v>
+      </c>
+      <c r="G26" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="I26" t="n">
+        <v>430.9</v>
+      </c>
+      <c r="J26" t="n">
+        <v>405.8</v>
+      </c>
+      <c r="K26" t="n">
+        <v>59961</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SWELECTES</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Swelect Energy Systems Limited</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>639.3</v>
+      </c>
+      <c r="F27" t="n">
+        <v>663</v>
+      </c>
+      <c r="G27" t="n">
+        <v>667.95</v>
+      </c>
+      <c r="H27" t="n">
+        <v>625</v>
+      </c>
+      <c r="I27" t="n">
+        <v>681.25</v>
+      </c>
+      <c r="J27" t="n">
+        <v>639.3</v>
+      </c>
+      <c r="K27" t="n">
+        <v>43507</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-6.16</v>
+      </c>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>MIDHANI</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Mishra Dhatu Nigam Limited</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>417.35</v>
+      </c>
+      <c r="F28" t="n">
+        <v>444</v>
+      </c>
+      <c r="G28" t="n">
+        <v>447.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>444.85</v>
+      </c>
+      <c r="J28" t="n">
+        <v>417.35</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2337306</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Midhani Q1 results: net profit up 27%, EBITDA margin narrows - Business Upturn</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>['Midhani Q1 results: net profit up 27%, EBITDA margin narrows - Business Upturn', 'MIDHANI: Q1 FY27 Results Show Strong Growth - InvestyWise', 'MIDHANI Shares Hit 52-Week High After GE Aerospace S400 Nod - Whalesbook', 'Why MIDHANI shares are rallying over 6% today? Here’s what triggered the rally - Business Upturn', 'MIDHANI becomes first Indian company to secure GE Aerospace S400 lab approval - cnbctv18.com']</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ARDEE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ardee Industries Limited</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="F29" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="G29" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="H29" t="n">
+        <v>60.59</v>
+      </c>
+      <c r="I29" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="J29" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="K29" t="n">
+        <v>9546604</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-6.47</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Ardee Industries Limited Earnings and Revenue – BSE:ARDEE - TradingView</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>['Ardee Industries Limited Earnings and Revenue – BSE:ARDEE - TradingView', 'Price to earnings ratio of Ardee Industries Limited – BSE:ARDEE - TradingView', 'Gross profit of Ardee Industries Limited – BSE:ARDEE - TradingView', 'CapEx per share of Ardee Industries Limited – NSE:ARDEE - TradingView', 'Net margin % of Ardee Industries Limited – BSE:ARDEE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FINOPB</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Fino Payments Bank Limited</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>152.42</v>
+      </c>
+      <c r="F30" t="n">
+        <v>158</v>
+      </c>
+      <c r="G30" t="n">
+        <v>158</v>
+      </c>
+      <c r="H30" t="n">
+        <v>150.53</v>
+      </c>
+      <c r="I30" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>152.42</v>
+      </c>
+      <c r="K30" t="n">
+        <v>627703</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-6.89</v>
+      </c>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>HARRMALAYA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Harrisons Malayalam Limited</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>207</v>
+      </c>
+      <c r="F31" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="H31" t="n">
+        <v>205</v>
+      </c>
+      <c r="I31" t="n">
+        <v>222.68</v>
+      </c>
+      <c r="J31" t="n">
+        <v>207</v>
+      </c>
+      <c r="K31" t="n">
+        <v>17461</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-7.04</v>
+      </c>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>209.45</v>
+      </c>
+      <c r="G32" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>195.9</v>
+      </c>
+      <c r="I32" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="J32" t="n">
+        <v>196.4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>282149</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-7.05</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Lawsuit filed against former Genesys doctor, hospital - MLive.com</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>['Lawsuit filed against former Genesys doctor, hospital - MLive.com', '2026-2027 YCS Advanced &amp; Genesys Prizing - ygorganization.com', 'Lawsuit filed against former Genesys doctor, hospital - NewsBreak: Local News &amp; Alerts', 'Genesys Puts AI Trust at the Center of Its Agentic CX Strategy - CX Today', 'Genesys’ Impact: Sustainable Procurement &amp; Responsible AI - Sustainability Magazine']</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MAHAPEXLTD</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Maha Rashtra Apex Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="F33" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G33" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>49.35</v>
+      </c>
+      <c r="I33" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="J33" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="K33" t="n">
+        <v>42944</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-7.09</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Maha Rashtra Apex signs deal to market Paulownia timber in India - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>['Maha Rashtra Apex signs deal to market Paulownia timber in India - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>BELLACASA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bella Casa Fashion &amp; Retail Limited</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221</v>
+      </c>
+      <c r="F34" t="n">
+        <v>237.39</v>
+      </c>
+      <c r="G34" t="n">
+        <v>237.4</v>
+      </c>
+      <c r="H34" t="n">
+        <v>220.2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>239.51</v>
+      </c>
+      <c r="J34" t="n">
+        <v>221</v>
+      </c>
+      <c r="K34" t="n">
+        <v>19320</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-7.73</v>
+      </c>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Limited</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>37</v>
+      </c>
+      <c r="F35" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="G35" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="H35" t="n">
+        <v>36.31</v>
+      </c>
+      <c r="I35" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="J35" t="n">
+        <v>37</v>
+      </c>
+      <c r="K35" t="n">
+        <v>19032</v>
+      </c>
+      <c r="L35" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Limited</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>399</v>
+      </c>
+      <c r="G36" t="n">
+        <v>399</v>
+      </c>
+      <c r="H36" t="n">
+        <v>370.75</v>
+      </c>
+      <c r="I36" t="n">
+        <v>410</v>
+      </c>
+      <c r="J36" t="n">
+        <v>375.2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>471071</v>
+      </c>
+      <c r="L36" t="n">
+        <v>-8.49</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - tipranks.com</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>['Asian Energy Services Files June-Quarter Unaudited Results with SEBI - tipranks.com', 'Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn']</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TARMAT</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Tarmat Limited</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="F37" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G37" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I37" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="J37" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="K37" t="n">
+        <v>506108</v>
+      </c>
+      <c r="L37" t="n">
+        <v>-8.609999999999999</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>['Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest', 'Tarmat Ltd announces demise of promoter group member holding 4.19% stake - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ABM International Limited</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="F38" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G38" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="I38" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="J38" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="K38" t="n">
+        <v>20529</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COCKERILL</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>John Cockerill India Limited</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>8418</v>
+      </c>
+      <c r="F39" t="n">
+        <v>8624</v>
+      </c>
+      <c r="G39" t="n">
+        <v>9040</v>
+      </c>
+      <c r="H39" t="n">
+        <v>8380</v>
+      </c>
+      <c r="I39" t="n">
+        <v>10101.5</v>
+      </c>
+      <c r="J39" t="n">
+        <v>8418</v>
+      </c>
+      <c r="K39" t="n">
+        <v>62941</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-16.67</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: John Cockerill India Q2 2026 revenue jumps, stock rises 4.7% - Investing.com</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>['Earnings call transcript: John Cockerill India Q2 2026 revenue jumps, stock rises 4.7% - Investing.com', 'COCKERILL: Strong revenue growth and robust order backlog drive improved profitability and future outlook - TradingView', 'John Cockerill India reports standalone net loss of Rs 4.58 crore in the June 2026 quarter - business-standard.com', 'John Cockerill India Limited Announces Cessation of Marc Dumont as Key Managerial Personnel, Effective July 31, 2026 - marketscreener.com', 'John Cockerill India Q2 2026 slides: 82% revenue surge, INR 4,600cr backlog - Investing.com']</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SHANTI-RE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited-RE</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" t="n">
+        <v>18</v>
+      </c>
+      <c r="G40" t="n">
+        <v>18</v>
+      </c>
+      <c r="H40" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="I40" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J40" t="n">
+        <v>14</v>
+      </c>
+      <c r="K40" t="n">
+        <v>58494</v>
+      </c>
+      <c r="L40" t="n">
+        <v>-17.16</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:19:04 IST</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GENESYS-RE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited-RE</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="F41" t="n">
+        <v>141</v>
+      </c>
+      <c r="G41" t="n">
+        <v>141</v>
+      </c>
+      <c r="H41" t="n">
+        <v>115.6</v>
+      </c>
+      <c r="I41" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="J41" t="n">
+        <v>128.1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>505071</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-20.58</v>
+      </c>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O21"/>
+  <autoFilter ref="A1:O41"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1950,7 +1950,6 @@
       <c r="L25" t="n">
         <v>19.94</v>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2007,7 +2006,6 @@
       <c r="L26" t="n">
         <v>19.51</v>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2491,7 +2489,6 @@
       <c r="L34" t="n">
         <v>9.210000000000001</v>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2930,8 +2927,1220 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>SHANTI-RE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited-RE</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="F42" t="n">
+        <v>18</v>
+      </c>
+      <c r="G42" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="H42" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="I42" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="J42" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="K42" t="n">
+        <v>236023</v>
+      </c>
+      <c r="L42" t="n">
+        <v>40</v>
+      </c>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="F43" t="n">
+        <v>69.94</v>
+      </c>
+      <c r="G43" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="H43" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="I43" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="J43" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="K43" t="n">
+        <v>121676</v>
+      </c>
+      <c r="L43" t="n">
+        <v>20</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>['【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com', 'Bilcare Limited Announces Winding Up of Bilcare INC, A Wholly Owned Subsidiary of the Company - marketscreener.com', 'China’s CSI 300 Set to Lose Appeal Before Adding CXMT, BI Says - bloomberg.com', "What AI-native analytics startups offer that BI vendors don't - TechTarget", 'Shein IPO Value to Fall Short of $30 Billion Targeted by Some Investors, BI Says - bloomberg.com']</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>GALAXYSURF</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Galaxy Surfactants Limited</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>2508.4</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2412.5</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2508.4</v>
+      </c>
+      <c r="H44" t="n">
+        <v>2391.2</v>
+      </c>
+      <c r="I44" t="n">
+        <v>2090.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>2508.4</v>
+      </c>
+      <c r="K44" t="n">
+        <v>632628</v>
+      </c>
+      <c r="L44" t="n">
+        <v>20</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: Specialty Chemical Stock Skyrockets After Reporting 168% Profit Growth - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>['20% Upper Circuit: Specialty Chemical Stock Skyrockets After Reporting 168% Profit Growth - Trade Brains', 'Awfis Q1 Profit Jumps 139% to ₹23.9 Cr - HDFC Sky', 'Galaxy Surfactants approves ₹22 final dividend at 40th AGM - scanx.trade', 'Galaxy Surfactants Ltd. Share Price at Fresh 52-Week High - Univest', '7 Stocks That Have Hit the 20% Upper Circuit Today; Are You Holding Any? - Trade Brains']</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>KOHINOOR</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="F45" t="n">
+        <v>23.11</v>
+      </c>
+      <c r="G45" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="H45" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="I45" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="J45" t="n">
+        <v>27.72</v>
+      </c>
+      <c r="K45" t="n">
+        <v>982184</v>
+      </c>
+      <c r="L45" t="n">
+        <v>20</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>['Kohinoor Foods to Review Quarterly Results and Mull Fundraising at August Board Meeting - TipRanks', 'Kohinoor Foods reports consolidated net profit of Rs 2.10 crore in the June 2026 quarter - Business Standard', 'Kohinoor Textile Mills OKs 48.36MW BESS, solar add-on - Profit by Pakistan Today', 'Kohinoor Foods Ltd Locks at Upper Circuit With 20% Gain — Buyers Queue, Sellers Absent - MarketsMojo', 'Kohinoor falcon among confirmed cases; new H5 reporting framework - theislanderonline.com.au']</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="F46" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="G46" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="H46" t="n">
+        <v>11</v>
+      </c>
+      <c r="I46" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="J46" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="K46" t="n">
+        <v>952278</v>
+      </c>
+      <c r="L46" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K47" t="n">
+        <v>8857331</v>
+      </c>
+      <c r="L47" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>['20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains', 'Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Tarsons Products Limited</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="F48" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="G48" t="n">
+        <v>375</v>
+      </c>
+      <c r="H48" t="n">
+        <v>311.9</v>
+      </c>
+      <c r="I48" t="n">
+        <v>312.7</v>
+      </c>
+      <c r="J48" t="n">
+        <v>371.1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>9830521</v>
+      </c>
+      <c r="L48" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Tarsons Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>['Tarsons Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade', 'Tarsons Products Q1 Results: Consolidated net loss widens to ₹14.44 million - scanx.trade', 'Tarsons Products Ltd (BOM:543399) (Q1 2027) Earnings Call Highlights: Record Revenue and ... - Yahoo! Finance Canada', 'Tarsons Products reports consolidated net loss of Rs 1.44 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FINKURVE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>73.98</v>
+      </c>
+      <c r="F49" t="n">
+        <v>63.7</v>
+      </c>
+      <c r="G49" t="n">
+        <v>75.39</v>
+      </c>
+      <c r="H49" t="n">
+        <v>62.19</v>
+      </c>
+      <c r="I49" t="n">
+        <v>62.83</v>
+      </c>
+      <c r="J49" t="n">
+        <v>73.98</v>
+      </c>
+      <c r="K49" t="n">
+        <v>812183</v>
+      </c>
+      <c r="L49" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>['Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Finkurve Financial Services Q1 Results: Net profit up 66% YoY - scanx.trade', 'Price to earnings forward of Finkurve Financial Services Ltd. – NSE:FINKURVE - TradingView', 'Finkurve Financial Services standalone net profit rises 65.82% in the June 2026 quarter - Business Standard', 'Finkurve Financial Services delivers strong Q1 FY27 performance; AUM grows 134.5 percent YoY to INR 1,270.4 Cr and PAT rises 65.8 percent YoY - businessnewsthisweek.com']</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>APEX</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Apex Frozen Foods Limited</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>425</v>
+      </c>
+      <c r="F50" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="G50" t="n">
+        <v>441.2</v>
+      </c>
+      <c r="H50" t="n">
+        <v>403.15</v>
+      </c>
+      <c r="I50" t="n">
+        <v>367.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>425</v>
+      </c>
+      <c r="K50" t="n">
+        <v>9316207</v>
+      </c>
+      <c r="L50" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Apex Capital and Finance Q1 Results: Net profit rises 73% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>['Apex Capital and Finance Q1 Results: Net profit rises 73% YoY - scanx.trade', 'Apex Frozen Foods shares hit up to 20% upper circuit after 144% jump in Q1 net profit - Moneycontrol.com', 'Apex Frozen Foods shares hit 20% upper circuit after Q1 profit more than doubles - CNBC TV18', 'Apex Frozen Foods standalone net profit rises 138.13% in the June 2026 quarter - Business Standard', 'Maha Rashtra Apex Corporation consolidated net profit declines 85.41% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>XTRANET</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>173</v>
+      </c>
+      <c r="F51" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="G51" t="n">
+        <v>176.78</v>
+      </c>
+      <c r="H51" t="n">
+        <v>148.5</v>
+      </c>
+      <c r="I51" t="n">
+        <v>150.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>173</v>
+      </c>
+      <c r="K51" t="n">
+        <v>2182519</v>
+      </c>
+      <c r="L51" t="n">
+        <v>15.03</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Price to earnings ratio of Xtranet Technologies Limited – NSE:XTRANET - TradingView</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>['Price to earnings ratio of Xtranet Technologies Limited – NSE:XTRANET - TradingView', 'Xtranet Technologies (XTRA) Stock Forecast &amp; Price Target - Investing.com', 'Xtranet Technologies Limited Revenue Breakdown – NSE:XTRANET - TradingView', 'Xtranet Technologies Limited Income Statement – NSE:XTRANET - TradingView', 'Xtranet Technologies infuses ₹15.25 Cr into Xtratrust Digisign - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>MOTISONS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers Limited</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="F52" t="n">
+        <v>14.76</v>
+      </c>
+      <c r="G52" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="H52" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="I52" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="J52" t="n">
+        <v>16.72</v>
+      </c>
+      <c r="K52" t="n">
+        <v>410441404</v>
+      </c>
+      <c r="L52" t="n">
+        <v>14.36</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>["Motisons Jewellers shares jump 5% on heavy volumes after Q1 results: Here's what the numbers showed - Business Upturn", 'Motisons Jewellers standalone net profit rises 37.61% in the June 2026 quarter - Business Standard', 'Motisons Jewellers Q1FY27 net profit rises 38% to ₹110.5 crore - scanx.trade', 'Motisons Jewellers Share Price Up 10.65%: Stock Analysis - Univest', 'Vodafone Idea, Motisons, LEAP India Among Top NSE Movers - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>AVTNPL</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AVT Natural Products Limited</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>81.14</v>
+      </c>
+      <c r="F53" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="G53" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="H53" t="n">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="I53" t="n">
+        <v>71.31</v>
+      </c>
+      <c r="J53" t="n">
+        <v>81.14</v>
+      </c>
+      <c r="K53" t="n">
+        <v>2546303</v>
+      </c>
+      <c r="L53" t="n">
+        <v>13.78</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>AVT Natural Products Share Price Rise: Price, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>['AVT Natural Products Share Price Rise: Price, Valuation View - Univest']</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TVSSRICHAK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Limited</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>4464</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4028.9</v>
+      </c>
+      <c r="G54" t="n">
+        <v>4628</v>
+      </c>
+      <c r="H54" t="n">
+        <v>3960</v>
+      </c>
+      <c r="I54" t="n">
+        <v>3994.9</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4464</v>
+      </c>
+      <c r="K54" t="n">
+        <v>711409</v>
+      </c>
+      <c r="L54" t="n">
+        <v>11.74</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>TVS Srichakra Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>['TVS Srichakra Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'TVS Srichakra Ltd. Share Price Today: Market Cap Context - Univest', 'TVS Srichakra Limited Opens Three New Exclusive Retail Stores In Mehsana, Noida, And Bareilly - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>BALUFORGE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries Limited</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>496</v>
+      </c>
+      <c r="F55" t="n">
+        <v>450</v>
+      </c>
+      <c r="G55" t="n">
+        <v>506.9</v>
+      </c>
+      <c r="H55" t="n">
+        <v>449.15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>446.25</v>
+      </c>
+      <c r="J55" t="n">
+        <v>496</v>
+      </c>
+      <c r="K55" t="n">
+        <v>8980616</v>
+      </c>
+      <c r="L55" t="n">
+        <v>11.15</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Balu Forge Industries announces strong Q1 FY27 results with aerospace sector entry - Business Upturn</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>['Balu Forge Industries announces strong Q1 FY27 results with aerospace sector entry - Business Upturn', 'Balu Forge Industries Q1 FY27: Net Profit Rises 15.9% YoY; Board Approves $60 Million Fundraise - Trade Brains', 'Balu Forge Fund Utilization Report - InvestyWise', 'Balu Forge: No Deviation in Preferential Issue Fund Use for Q2 2026 - InvestyWise', 'Balu Forge secures Rs 496.80 crore preferential issue to fund expansion - Business Upturn']</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>RGL</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Renaissance Global Limited</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="F56" t="n">
+        <v>115</v>
+      </c>
+      <c r="G56" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="H56" t="n">
+        <v>115</v>
+      </c>
+      <c r="I56" t="n">
+        <v>111.14</v>
+      </c>
+      <c r="J56" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>5684564</v>
+      </c>
+      <c r="L56" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Renaissance Global Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>['Renaissance Global Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Should You Be Adding Renaissance Global (NSE:RGL) To Your Watchlist Today? - simplywall.st', 'RGL Is Building a Training Camp for First-Time Competitive TF2 Players - Signups Close August 8 - happygamer.com', 'Renaissance Global Q1 Consolidated Net Profit Rises To 254M Rupees From 64M YoY - Sahi', 'Renaissance Global Share Price Today: Price Rise Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>JNKINDIA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>JNK India Limited</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>458.55</v>
+      </c>
+      <c r="F57" t="n">
+        <v>429.85</v>
+      </c>
+      <c r="G57" t="n">
+        <v>459.95</v>
+      </c>
+      <c r="H57" t="n">
+        <v>425</v>
+      </c>
+      <c r="I57" t="n">
+        <v>413.15</v>
+      </c>
+      <c r="J57" t="n">
+        <v>458.55</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1481681</v>
+      </c>
+      <c r="L57" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>JNKINDIA: Revenue and profit surged in Q1 FY 2027, with strong order book and diversification underway - TradingView</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>['JNKINDIA: Revenue and profit surged in Q1 FY 2027, with strong order book and diversification underway - TradingView', 'JNKINDIA: Revenue up 80.6% YoY; order book at INR 1,801 cr; diversification on track - TradingView', 'JNKINDIA: Q1FY27 delivered 80.6% YoY income growth and robust margins, with strong order visibility - TradingView', 'JNK India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'JNK India Q1 Results: Net profit surges 1,059% YoY to ₹96.25 million - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MARKSANS</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Marksans Pharma Limited</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="F58" t="n">
+        <v>301.15</v>
+      </c>
+      <c r="G58" t="n">
+        <v>336.6</v>
+      </c>
+      <c r="H58" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="I58" t="n">
+        <v>303.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>335.85</v>
+      </c>
+      <c r="K58" t="n">
+        <v>20243407</v>
+      </c>
+      <c r="L58" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Marksans Pharma Q1 Results: Shares jump 11% after profit nearly triples, margin expands - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>['Marksans Pharma Q1 Results: Shares jump 11% after profit nearly triples, margin expands - CNBC TV18', 'Earnings call transcript: Marksans Pharma posts strong Q1 2026 profit, misses revenue view - Investing.com', 'Marksans Pharma Q1 results: Net profit jumps 174% YoY to Rs 159 crore, revenue rises 36% - Business Upturn', 'Marksans Pharma Q1 results: Net profit jumps 169% to Rs 157.1 crore, revenue rises 36% - Business Upturn', 'Marksans Pharma Stock Jumps 11% After Net Profit Jumps 2.5x, Revenue Surges 36% - NDTV Profit']</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>1176</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1069.7</v>
+      </c>
+      <c r="G59" t="n">
+        <v>1190</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1058.2</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1064.4</v>
+      </c>
+      <c r="J59" t="n">
+        <v>1176</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1436038</v>
+      </c>
+      <c r="L59" t="n">
+        <v>10.48</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Q1 FY27 Results: Revenue Surges 46.7% YoY to ₹355 Crore, Returns to Profit - DredgeWire</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>['Dredging Corporation of India Q1 FY27 Results: Revenue Surges 46.7% YoY to ₹355 Crore, Returns to Profit - DredgeWire']</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HMAAGRO</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="F60" t="n">
+        <v>23</v>
+      </c>
+      <c r="G60" t="n">
+        <v>25.34</v>
+      </c>
+      <c r="H60" t="n">
+        <v>22</v>
+      </c>
+      <c r="I60" t="n">
+        <v>21.91</v>
+      </c>
+      <c r="J60" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="K60" t="n">
+        <v>11840343</v>
+      </c>
+      <c r="L60" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>HMA Agro Industries Q1 Results: Earnings Call Scheduled for Aug 14 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>['HMA Agro Industries Q1 Results: Earnings Call Scheduled for Aug 14 - scanx.trade', 'HMA Agro Industries Ltd. Share Price Rise: Price Analysis - Univest', 'HMA Agro Industries reports ₹21,103.19 million revenue for Q1 FY 2026-2027 - Business Upturn', 'HMA Agro Publishes Investor Presentation for June 2026 Quarter - TipRanks', 'HMA Agro Industries Releases Q1 FY2026 Investor Presentation - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LGEINDIA</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LG Electronics India Limited</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>1736.1</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1620</v>
+      </c>
+      <c r="G61" t="n">
+        <v>1736.1</v>
+      </c>
+      <c r="H61" t="n">
+        <v>1611</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1578.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>1736.1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>9832158</v>
+      </c>
+      <c r="L61" t="n">
+        <v>10</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>LG ELECTRONICS INDIA LTD Share Price - Live NSE: LGEINDIA Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>['LG ELECTRONICS INDIA LTD Share Price - Live NSE: LGEINDIA Stock Price &amp; Chart - Upstox', 'LG Electronics India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'LG Electronics Q1 results: Net profit rises to ₹652 crore; revenue jumps 15% on volume, value-led growth - Upstox', 'LG Electronics India Q1 FY27: Net Profit Rises 27.2% YoY to ₹652.9 Cr; Stock Jumps 8% - Trade Brains', "LG Electronics India's quarterly profit rises on strong summer appliance sales - marketscreener.com"]</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2942,7 +4151,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4472,7 +5681,6 @@
       <c r="L25" t="n">
         <v>-5.66</v>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4529,7 +5737,6 @@
       <c r="L26" t="n">
         <v>-5.83</v>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4586,7 +5793,6 @@
       <c r="L27" t="n">
         <v>-6.16</v>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4765,7 +5971,6 @@
       <c r="L30" t="n">
         <v>-6.89</v>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4822,7 +6027,6 @@
       <c r="L31" t="n">
         <v>-7.04</v>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5001,7 +6205,6 @@
       <c r="L34" t="n">
         <v>-7.73</v>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5058,7 +6261,6 @@
       <c r="L35" t="n">
         <v>-8.26</v>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5237,7 +6439,6 @@
       <c r="L38" t="n">
         <v>-9.99</v>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5355,7 +6556,6 @@
       <c r="L40" t="n">
         <v>-17.16</v>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5412,7 +6612,6 @@
       <c r="L41" t="n">
         <v>-20.58</v>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5424,8 +6623,1216 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LGHL</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Laxmi Goldorna House Limited</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>181</v>
+      </c>
+      <c r="F42" t="n">
+        <v>198</v>
+      </c>
+      <c r="G42" t="n">
+        <v>199.81</v>
+      </c>
+      <c r="H42" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="I42" t="n">
+        <v>196.44</v>
+      </c>
+      <c r="J42" t="n">
+        <v>181</v>
+      </c>
+      <c r="K42" t="n">
+        <v>53218</v>
+      </c>
+      <c r="L42" t="n">
+        <v>-7.86</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Lion Group Holding Ltd (LGHL) Earnings Forecast: Future EPS &amp; Revenue Growth Estimates - TradingKey</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>['Lion Group Holding Ltd (LGHL) Earnings Forecast: Future EPS &amp; Revenue Growth Estimates - TradingKey', 'LGHL Stock In Focus As Insider Ownership Shifts - StocksToTrade', 'LGHL Stock Tracks Insider Ownership Shift As Volatility Builds - StocksToTrade']</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GOCLCORP</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>GOCL Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>396</v>
+      </c>
+      <c r="F43" t="n">
+        <v>417.55</v>
+      </c>
+      <c r="G43" t="n">
+        <v>418.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>394.1</v>
+      </c>
+      <c r="I43" t="n">
+        <v>430.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>396</v>
+      </c>
+      <c r="K43" t="n">
+        <v>148404</v>
+      </c>
+      <c r="L43" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>GOCL Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>['GOCL Corporation Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LEAPIND</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LEAP India Limited</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>146</v>
+      </c>
+      <c r="F44" t="n">
+        <v>165.9</v>
+      </c>
+      <c r="G44" t="n">
+        <v>167</v>
+      </c>
+      <c r="H44" t="n">
+        <v>143</v>
+      </c>
+      <c r="I44" t="n">
+        <v>159</v>
+      </c>
+      <c r="J44" t="n">
+        <v>146</v>
+      </c>
+      <c r="K44" t="n">
+        <v>92916431</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Basic earnings per share (basic EPS) of LEAP India Limited – NSE:LEAP - TradingView</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>['Basic earnings per share (basic EPS) of LEAP India Limited – NSE:LEAP - TradingView', 'LEAP INDIA LIMITED Share Price - Upstox', 'Operating margin % of LEAP India Limited – NSE:LEAP - TradingView', 'LEAP India Limited Revenue Breakdown – NSE:LEAP - TradingView', 'Listing ceremony of Leap India Limited - Live Broadcast by NSE India | X - t.co']</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TARMAT</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Tarmat Limited</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="F45" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="G45" t="n">
+        <v>69.65000000000001</v>
+      </c>
+      <c r="H45" t="n">
+        <v>57.44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="J45" t="n">
+        <v>59.22</v>
+      </c>
+      <c r="K45" t="n">
+        <v>613433</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>['Tarmat Ltd. Share Price News: Price Action, Fundamentals - Univest', 'Tarmat Ltd announces demise of promoter group member holding 4.19% stake - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MAHAPEXLTD</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Maha Rashtra Apex Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="F46" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="G46" t="n">
+        <v>53.8</v>
+      </c>
+      <c r="H46" t="n">
+        <v>49.25</v>
+      </c>
+      <c r="I46" t="n">
+        <v>54.74</v>
+      </c>
+      <c r="J46" t="n">
+        <v>50.1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>73053</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-8.48</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Maha Rashtra Apex Corporation Share Price Today After Fall - Univest</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>['Maha Rashtra Apex Corporation Share Price Today After Fall - Univest']</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ZOTA</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Zota Health Care LImited</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1231.3</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1236.1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1050.3</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1241.3</v>
+      </c>
+      <c r="J47" t="n">
+        <v>1135</v>
+      </c>
+      <c r="K47" t="n">
+        <v>399730</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-8.56</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Zota Health Care Ltd Says June-Quarter Consol Net Loss 435.6 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>['Zota Health Care Ltd Says June-Quarter Consol Net Loss 435.6 Million Rupees - TradingView', 'Q1 Results: Tata Motors PV, Solar Industries, LG Electronics, Max Healthcare, General Insurance, Page Industries, others to declare earnings on August 13 - Dailyhunt', "Zota Health's Davaindia Network crosses 2,825 stores as revenue jumps 68% in Q1 FY27 - Indian Pharma Post", 'Zota Health Care Ltd is Rated Strong Sell - MarketsMojo', 'Costain revenues up, margins steady - Trending Now Infrastructure']</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>FINOPB</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Fino Payments Bank Limited</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>149.46</v>
+      </c>
+      <c r="F48" t="n">
+        <v>158</v>
+      </c>
+      <c r="G48" t="n">
+        <v>158</v>
+      </c>
+      <c r="H48" t="n">
+        <v>149</v>
+      </c>
+      <c r="I48" t="n">
+        <v>163.7</v>
+      </c>
+      <c r="J48" t="n">
+        <v>149.46</v>
+      </c>
+      <c r="K48" t="n">
+        <v>1323230</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-8.699999999999999</v>
+      </c>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Limited</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="F49" t="n">
+        <v>399</v>
+      </c>
+      <c r="G49" t="n">
+        <v>399</v>
+      </c>
+      <c r="H49" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="I49" t="n">
+        <v>410</v>
+      </c>
+      <c r="J49" t="n">
+        <v>374.25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>1033788</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-8.720000000000001</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>['Asian Energy Services Files June-Quarter Unaudited Results with SEBI - TipRanks', 'Asian Energy Services Share Price Today: Fall and Valuation - Univest', 'Asian Energy Services Q1 FY27 PAT Rises 129 Per Cent - Construction World', 'Asian Energy Services secures ₹131.39 crore from convertible warrants - Business Upturn']</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>KERNEX</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems (India) Limited</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>2046</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2225</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2340</v>
+      </c>
+      <c r="H50" t="n">
+        <v>2001</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2242.7</v>
+      </c>
+      <c r="J50" t="n">
+        <v>2046</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1262801</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-8.77</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>['Kernex Microsystems Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Kernex Microsystems Q1 profit jumps nearly 15-fold to ₹109.8 crore as Kavach orders drive sharp revenue growth - Business Upturn', 'Kernex Microsystems (India) consolidated net profit rises 1372.52% in the June 2026 quarter - Business Standard', 'Kernex Microsystems Q1FY27 net profit rises 13.7x to ₹10,984.57 lakh - scanx.trade', 'Kernex Microsystems (India) Ltd Says June-Quarter Consol Net Profit 1.10 Billion Rupees - TradingView']</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ARDEE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ardee Industries Limited</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="F51" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="G51" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="H51" t="n">
+        <v>58.61</v>
+      </c>
+      <c r="I51" t="n">
+        <v>64.87</v>
+      </c>
+      <c r="J51" t="n">
+        <v>59.09</v>
+      </c>
+      <c r="K51" t="n">
+        <v>22017200</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Ardee Industries Limited Earnings and Revenue – BSE:ARDEE - TradingView</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>['Ardee Industries Limited Earnings and Revenue – BSE:ARDEE - TradingView', 'Gross profit of Ardee Industries Limited – BSE:ARDEE - TradingView', 'CapEx per share of Ardee Industries Limited – NSE:ARDEE - TradingView', 'Operating income of Ardee Industries Limited – NSE:ARDEE - TradingView', 'Non-operating income (total) of Ardee Industries Limited – NSE:ARDEE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SWELECTES</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Swelect Energy Systems Limited</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>617.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>663</v>
+      </c>
+      <c r="G52" t="n">
+        <v>667.95</v>
+      </c>
+      <c r="H52" t="n">
+        <v>613</v>
+      </c>
+      <c r="I52" t="n">
+        <v>681.25</v>
+      </c>
+      <c r="J52" t="n">
+        <v>617.9</v>
+      </c>
+      <c r="K52" t="n">
+        <v>83509</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-9.300000000000001</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Swelect Energy Systems Share Price: 8.02% Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>['Swelect Energy Systems Share Price: 8.02% Fall Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>THAKDEV</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Thakkers Developers Limited</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>141.51</v>
+      </c>
+      <c r="F53" t="n">
+        <v>153</v>
+      </c>
+      <c r="G53" t="n">
+        <v>153</v>
+      </c>
+      <c r="H53" t="n">
+        <v>141.51</v>
+      </c>
+      <c r="I53" t="n">
+        <v>156.12</v>
+      </c>
+      <c r="J53" t="n">
+        <v>141.51</v>
+      </c>
+      <c r="K53" t="n">
+        <v>4</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-9.359999999999999</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Thakker's Developers Ltd. Revenue Breakdown – NSE:THAKDEV - TradingView</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>["Thakker's Developers Ltd. Revenue Breakdown – NSE:THAKDEV - TradingView"]</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>REGENCERAM</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Limited</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="F54" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="G54" t="n">
+        <v>43.99</v>
+      </c>
+      <c r="H54" t="n">
+        <v>35.5</v>
+      </c>
+      <c r="I54" t="n">
+        <v>40.33</v>
+      </c>
+      <c r="J54" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="K54" t="n">
+        <v>29386</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-9.4</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Regency Ceramics Q1 Results: Revenue up 173% YoY, net loss narrows - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>['Regency Ceramics Q1 Results: Revenue up 173% YoY, net loss narrows - scanx.trade', 'Regency Ceramics Ltd. Share Price Fall and Stock Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>ABM International Limited</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="F55" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="G55" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="H55" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="I55" t="n">
+        <v>69.37</v>
+      </c>
+      <c r="J55" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="K55" t="n">
+        <v>23052</v>
+      </c>
+      <c r="L55" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CPCAP</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CP Capital Limited</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="F56" t="n">
+        <v>139.35</v>
+      </c>
+      <c r="G56" t="n">
+        <v>142</v>
+      </c>
+      <c r="H56" t="n">
+        <v>125</v>
+      </c>
+      <c r="I56" t="n">
+        <v>140.18</v>
+      </c>
+      <c r="J56" t="n">
+        <v>126.1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>72907</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-10.04</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>CP Capital Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>['CP Capital Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'CP Capital Q1 Results: Standalone PAT up 102% QoQ to ₹11.5 crore - scanx.trade', 'Career Point Ltd. Share Price Today Falls 9%: Key Metrics - Univest']</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HARRMALAYA</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Harrisons Malayalam Limited</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="F57" t="n">
+        <v>209.07</v>
+      </c>
+      <c r="G57" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>197.49</v>
+      </c>
+      <c r="I57" t="n">
+        <v>222.68</v>
+      </c>
+      <c r="J57" t="n">
+        <v>199.4</v>
+      </c>
+      <c r="K57" t="n">
+        <v>56164</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-10.45</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Harrisons Malayalam Share Price Today: Fall, Valuation View - Univest</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>['Harrisons Malayalam Share Price Today: Fall, Valuation View - Univest']</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ESSARSHPNG</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Essar Shipping Limited</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="F58" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="G58" t="n">
+        <v>19.94</v>
+      </c>
+      <c r="H58" t="n">
+        <v>17.24</v>
+      </c>
+      <c r="I58" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="J58" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1168596</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-10.58</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Essar Shipping Board Clears Q1 Results, Approves Sale of Essar Tug III - TipRanks</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>['Essar Shipping Board Clears Q1 Results, Approves Sale of Essar Tug III - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>GENESYS</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>185.95</v>
+      </c>
+      <c r="F59" t="n">
+        <v>209.45</v>
+      </c>
+      <c r="G59" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="H59" t="n">
+        <v>173.65</v>
+      </c>
+      <c r="I59" t="n">
+        <v>211.3</v>
+      </c>
+      <c r="J59" t="n">
+        <v>185.95</v>
+      </c>
+      <c r="K59" t="n">
+        <v>1572472</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-12</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd. (GENESYS) Share Price Falls 8.41%: What Today’s Move Shows - Univest</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>['Genesys International Corporation Ltd. (GENESYS) Share Price Falls 8.41%: What Today’s Move Shows - Univest', 'Genesys Targets 30% Emissions Cut Using Procurement Strategy - Procurement Magazine', 'Lawsuit filed against former Genesys doctor, hospital - MLive.com', '2026-2027 YCS Advanced &amp; Genesys Prizing - YGOrganization', 'Lawsuit filed against former Genesys doctor, hospital - NewsBreak: Local News &amp; Alerts']</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COCKERILL</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>John Cockerill India Limited</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>8549</v>
+      </c>
+      <c r="F60" t="n">
+        <v>8624</v>
+      </c>
+      <c r="G60" t="n">
+        <v>9040</v>
+      </c>
+      <c r="H60" t="n">
+        <v>8222</v>
+      </c>
+      <c r="I60" t="n">
+        <v>10101.5</v>
+      </c>
+      <c r="J60" t="n">
+        <v>8549</v>
+      </c>
+      <c r="K60" t="n">
+        <v>115890</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-15.37</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: John Cockerill India Q2 2026 revenue jumps, stock rises 4.7% - Investing.com</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>['Earnings call transcript: John Cockerill India Q2 2026 revenue jumps, stock rises 4.7% - Investing.com', 'COCKERILL: Strong revenue growth and robust order backlog drive improved profitability and future outlook - TradingView', 'John Cockerill India reports standalone net loss of Rs 4.58 crore in the June 2026 quarter - Business Standard', 'John Cockerill India Q2 CY26 Concall: ₹8,000 Crore Revenue Target Intact, Order Book at ₹4,500 Crore; JVD Order Worth €50–100 Million May Land This Year - Business Upturn', 'John Cockerill India Limited Announces Cessation of Marc Dumont as Key Managerial Personnel, Effective July 31, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-08-14 18:02:38 IST</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>GENESYS-RE</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited-RE</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>130</v>
+      </c>
+      <c r="F61" t="n">
+        <v>141</v>
+      </c>
+      <c r="G61" t="n">
+        <v>141</v>
+      </c>
+      <c r="H61" t="n">
+        <v>114</v>
+      </c>
+      <c r="I61" t="n">
+        <v>161.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>130</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1288813</v>
+      </c>
+      <c r="L61" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$61</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2972,7 +2972,6 @@
       <c r="L42" t="n">
         <v>40</v>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3212,7 +3211,6 @@
       <c r="L46" t="n">
         <v>19.94</v>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4139,8 +4137,1196 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HINDADH</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Hindustan Adhesives Limited</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="F62" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="G62" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="H62" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="I62" t="n">
+        <v>279.65</v>
+      </c>
+      <c r="J62" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="K62" t="n">
+        <v>2138</v>
+      </c>
+      <c r="L62" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>COMPEAU</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Competent Automobiles Company Limited</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>414</v>
+      </c>
+      <c r="F63" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="G63" t="n">
+        <v>414</v>
+      </c>
+      <c r="H63" t="n">
+        <v>314.3</v>
+      </c>
+      <c r="I63" t="n">
+        <v>353</v>
+      </c>
+      <c r="J63" t="n">
+        <v>414</v>
+      </c>
+      <c r="K63" t="n">
+        <v>2</v>
+      </c>
+      <c r="L63" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>OSWALSEEDS</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>ShreeOswal Seeds And Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="F64" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="G64" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H64" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="I64" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="J64" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="K64" t="n">
+        <v>522882</v>
+      </c>
+      <c r="L64" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>UFLEX</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>UFLEX Limited</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>563.05</v>
+      </c>
+      <c r="F65" t="n">
+        <v>555</v>
+      </c>
+      <c r="G65" t="n">
+        <v>586.05</v>
+      </c>
+      <c r="H65" t="n">
+        <v>545</v>
+      </c>
+      <c r="I65" t="n">
+        <v>488.4</v>
+      </c>
+      <c r="J65" t="n">
+        <v>563.05</v>
+      </c>
+      <c r="K65" t="n">
+        <v>518457</v>
+      </c>
+      <c r="L65" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Uflex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>['Uflex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Uflex Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'UFlex Publishes Q1 FY2026 Unaudited Financial Results - TipRanks', 'Uflex consolidated net profit rises 629.63% in the June 2026 quarter - Business Standard', 'Uflex June-Quarter Consol Net Profit 4.23 Billion Rupees - TradingView']</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>2874673</v>
+      </c>
+      <c r="L66" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>['20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains', 'Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KEEPLEARN</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Limited</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F67" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G67" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H67" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I67" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J67" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K67" t="n">
+        <v>19342</v>
+      </c>
+      <c r="L67" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>DSJ Keep Learning Q1 Results: Net profit rises 66% YoY to ₹10 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>['DSJ Keep Learning Q1 Results: Net profit rises 66% YoY to ₹10 lakh - scanx.trade', 'DSJ Keep Learning Posts Q1 FY27 Unaudited Results in Line with SEBI Norms - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SHANTI-RE</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited-RE</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="F68" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="G68" t="n">
+        <v>28.1</v>
+      </c>
+      <c r="H68" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I68" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="J68" t="n">
+        <v>26.33</v>
+      </c>
+      <c r="K68" t="n">
+        <v>28655</v>
+      </c>
+      <c r="L68" t="n">
+        <v>11.95</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>['Shanti Gold International Ltd. Share Price Live Today - CNBC TV18']</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PURVA</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Puravankara Limited</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>243.27</v>
+      </c>
+      <c r="F69" t="n">
+        <v>234.01</v>
+      </c>
+      <c r="G69" t="n">
+        <v>244.7</v>
+      </c>
+      <c r="H69" t="n">
+        <v>232.11</v>
+      </c>
+      <c r="I69" t="n">
+        <v>218.21</v>
+      </c>
+      <c r="J69" t="n">
+        <v>243.27</v>
+      </c>
+      <c r="K69" t="n">
+        <v>1897292</v>
+      </c>
+      <c r="L69" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Puravankara expects Purva Ruby sale closure in 30 days - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>['Puravankara expects Purva Ruby sale closure in 30 days - scanx.trade', 'Panchang Today, August 14, 2026: Shukla Dwitiya under Purva Phalguni Nakshatra, auspicious and inauspicious timings | Astrology - Hindustan Times', 'Premiere: Inley Dip - Kalindi - Purva Soul Records - Electronic Groove', 'Panchang Today, August 2, 2026: Krishna Chaturthi under Purva Bhadrapada Nakshatra | Astrology - Hindustan Times', 'General Insurance Corporation of India consolidated net profit declines 31.10% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MLKFOOD</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Milkfood Limited</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="F70" t="n">
+        <v>89</v>
+      </c>
+      <c r="G70" t="n">
+        <v>89</v>
+      </c>
+      <c r="H70" t="n">
+        <v>88</v>
+      </c>
+      <c r="I70" t="n">
+        <v>80.03</v>
+      </c>
+      <c r="J70" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="K70" t="n">
+        <v>359</v>
+      </c>
+      <c r="L70" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Milkfood Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>['Milkfood Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MANBRO</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Manbro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="F71" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="G71" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="H71" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="I71" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="J71" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>50</v>
+      </c>
+      <c r="L71" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - Univest</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>['Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - Univest', 'KD Green Industries net profit up 81% in Q1FY27; approves ₹15 crore investment - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>LKPSEC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LKP Securities Limited</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="F72" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G72" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="H72" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="I72" t="n">
+        <v>15.38</v>
+      </c>
+      <c r="J72" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="K72" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>MODTHREAD</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Modern Threads (India) Limited</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="F73" t="n">
+        <v>52</v>
+      </c>
+      <c r="G73" t="n">
+        <v>54</v>
+      </c>
+      <c r="H73" t="n">
+        <v>51.89</v>
+      </c>
+      <c r="I73" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="J73" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="K73" t="n">
+        <v>3495</v>
+      </c>
+      <c r="L73" t="n">
+        <v>9.609999999999999</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>CREATIVEYE</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Creative Eye Limited</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="F74" t="n">
+        <v>6</v>
+      </c>
+      <c r="G74" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="H74" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J74" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="K74" t="n">
+        <v>209</v>
+      </c>
+      <c r="L74" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FINKURVE</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="F75" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>82</v>
+      </c>
+      <c r="H75" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="I75" t="n">
+        <v>72.73999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="K75" t="n">
+        <v>164420</v>
+      </c>
+      <c r="L75" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>['Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Finkurve Financial Q1 Results: Revenue surges 89% YoY, net profit up 66% - scanx.trade', 'Finkurve Financial Services Q1 Results: Net profit up 66% YoY - scanx.trade', 'Finkurve Financial Services standalone net profit rises 65.82% in the June 2026 quarter - Business Standard', 'Finkurve Financial Services Reports Q1 Standalone Net Profit of 84M Rupees, Revenue Up at 751M Rupees - Sahi']</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DCMFINSERV</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="F76" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="G76" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H76" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I76" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J76" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="K76" t="n">
+        <v>363</v>
+      </c>
+      <c r="L76" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>['DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>IPCALAB</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>IPCA Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>1886</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1805.9</v>
+      </c>
+      <c r="G77" t="n">
+        <v>1914.9</v>
+      </c>
+      <c r="H77" t="n">
+        <v>1805.9</v>
+      </c>
+      <c r="I77" t="n">
+        <v>1734.2</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1886</v>
+      </c>
+      <c r="K77" t="n">
+        <v>544175</v>
+      </c>
+      <c r="L77" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>IPCALAB: Net profit surged 80% year-over-year on strong revenue and margin expansion across key segments - TradingView</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>['IPCALAB: Net profit surged 80% year-over-year on strong revenue and margin expansion across key segments - TradingView', 'IPCALAB: Revenue up 21% and EBITDA margin to 22.88%, with FY27 growth guidance raised to 14%-16% - TradingView', 'IPCALAB: FY27 revenue growth guidance raised to 14%-16% with EBITDA margin at 23% on strong business momentum - TradingView', 'Ipca Laboratories Q1 FY27 Results: Net Profit Jumps 72.5% to ₹402 Crore, EBITDA Surges 61% as Margin Expands to 24% - Business Upturn', 'Earnings call transcript: Ipca Laboratories beats Q1 2026 estimates, lifts outlook - Investing.com']</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SWARNSAR</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Swarnsarita Jewels India Limited</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="F78" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="G78" t="n">
+        <v>36.95</v>
+      </c>
+      <c r="H78" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="I78" t="n">
+        <v>33.38</v>
+      </c>
+      <c r="J78" t="n">
+        <v>36.3</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1735</v>
+      </c>
+      <c r="L78" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Swarnsarita Jewels Q1 FY27 Profit Surges - InvestyWise</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>['Swarnsarita Jewels Q1 FY27 Profit Surges - InvestyWise', 'Swarnsarita Jewels posts 59% PAT surge in FY26 on revenue growth - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>AIROLAM</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Airo Lam limited</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="F79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="I79" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="J79" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="K79" t="n">
+        <v>54</v>
+      </c>
+      <c r="L79" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>ITL</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>ITL Industries Limited</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="F80" t="n">
+        <v>369</v>
+      </c>
+      <c r="G80" t="n">
+        <v>369</v>
+      </c>
+      <c r="H80" t="n">
+        <v>338</v>
+      </c>
+      <c r="I80" t="n">
+        <v>329.8</v>
+      </c>
+      <c r="J80" t="n">
+        <v>357.95</v>
+      </c>
+      <c r="K80" t="n">
+        <v>108</v>
+      </c>
+      <c r="L80" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>ITL Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>['ITL Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'ITL Industries net profit up 31% to ₹3.00 crore in Q1FY27 - scanx.trade', 'InterLink Labs Phase 1 ITL Reverse Auction Buyback is Now Live - Binance', 'Interlinks Auction Buyback News: ITL Holders Can Now Bid - Coin Gabbar', 'ITL To Set Up 25-Acre Global R&amp;D Centre In Greater Noida - Autocar Professional']</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HINDALUMI</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Hind Aluminium Industries Limited</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="F81" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="G81" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="H81" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="I81" t="n">
+        <v>98.56</v>
+      </c>
+      <c r="J81" t="n">
+        <v>106.95</v>
+      </c>
+      <c r="K81" t="n">
+        <v>8</v>
+      </c>
+      <c r="L81" t="n">
+        <v>8.51</v>
+      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4151,7 +5337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7034,7 +8220,6 @@
       <c r="L48" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7457,7 +8642,6 @@
       <c r="L55" t="n">
         <v>-9.99</v>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7819,7 +9003,6 @@
       <c r="L61" t="n">
         <v>-19.4</v>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7831,8 +9014,1200 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>AHLUCONT</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts (India) Limited</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>792.1</v>
+      </c>
+      <c r="F62" t="n">
+        <v>800</v>
+      </c>
+      <c r="G62" t="n">
+        <v>805</v>
+      </c>
+      <c r="H62" t="n">
+        <v>786.3</v>
+      </c>
+      <c r="I62" t="n">
+        <v>837.35</v>
+      </c>
+      <c r="J62" t="n">
+        <v>792.1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>15038</v>
+      </c>
+      <c r="L62" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FISCHER</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Fischer Medical Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="F63" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="G63" t="n">
+        <v>37.64</v>
+      </c>
+      <c r="H63" t="n">
+        <v>35.62</v>
+      </c>
+      <c r="I63" t="n">
+        <v>38.64</v>
+      </c>
+      <c r="J63" t="n">
+        <v>36.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>151034</v>
+      </c>
+      <c r="L63" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Fischer Medical Ventures Q1 Consolidated Net Profit Declines To ₹3.8 Crore From ₹5 Crore YoY - Sahi</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>['Fischer Medical Ventures Q1 Consolidated Net Profit Declines To ₹3.8 Crore From ₹5 Crore YoY - Sahi', 'Jenna Fischer Joins Outpouring Of Support For ‘The Office’ Star Lucy Davis After She Revealed Terminal Cancer Diagnosis - IMDb', 'Fischer: One building to bring them all and on Main Street unite them - TelegraphHerald.com', 'Villa Madonna Academy dedicates new Chase and Cole Fischer STEM wing - Northern Kentucky Tribune', "Here's Why Jenna Fischer Had To Film Her Firing Over 30 Times On The Office - Yahoo"]</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>SHRJAGP</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Shri Jagdamba Polymers Limited</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>715.4</v>
+      </c>
+      <c r="F64" t="n">
+        <v>801.25</v>
+      </c>
+      <c r="G64" t="n">
+        <v>801.25</v>
+      </c>
+      <c r="H64" t="n">
+        <v>715.4</v>
+      </c>
+      <c r="I64" t="n">
+        <v>761.5</v>
+      </c>
+      <c r="J64" t="n">
+        <v>715.4</v>
+      </c>
+      <c r="K64" t="n">
+        <v>64</v>
+      </c>
+      <c r="L64" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REMSONSIND</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Remsons Industries Limited</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="F65" t="n">
+        <v>86.28</v>
+      </c>
+      <c r="G65" t="n">
+        <v>86.31</v>
+      </c>
+      <c r="H65" t="n">
+        <v>82.23</v>
+      </c>
+      <c r="I65" t="n">
+        <v>88.25</v>
+      </c>
+      <c r="J65" t="n">
+        <v>82.88</v>
+      </c>
+      <c r="K65" t="n">
+        <v>32139</v>
+      </c>
+      <c r="L65" t="n">
+        <v>-6.08</v>
+      </c>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Primo Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="G66" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H66" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="I66" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="J66" t="n">
+        <v>24</v>
+      </c>
+      <c r="K66" t="n">
+        <v>56550</v>
+      </c>
+      <c r="L66" t="n">
+        <v>-6.32</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Primo Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>['Primo Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Primo Service Solutions Public Company Limited Reports Earnings Results for the Second Quarter and Six Months Ended June 30, 2026 - marketscreener.com', 'Primo Brands Corp reports results for the quarter ended June 30 - Earnings Summary - TradingView', 'Primo Chemicals consolidated net profit rises 14.71% in the June 2026 quarter - Business Standard', 'Primo Chemicals Reports Q1 Revenue Of 1.4B Rupees With 36M Net Profit - Sahi']</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KOTHARIPET</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Kothari Petrochemicals Limited</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>134.44</v>
+      </c>
+      <c r="F67" t="n">
+        <v>138.88</v>
+      </c>
+      <c r="G67" t="n">
+        <v>140.33</v>
+      </c>
+      <c r="H67" t="n">
+        <v>133.01</v>
+      </c>
+      <c r="I67" t="n">
+        <v>143.92</v>
+      </c>
+      <c r="J67" t="n">
+        <v>134.44</v>
+      </c>
+      <c r="K67" t="n">
+        <v>49027</v>
+      </c>
+      <c r="L67" t="n">
+        <v>-6.59</v>
+      </c>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>RADAAN</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Radaan Mediaworks India Limited</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F68" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="G68" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="I68" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J68" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="K68" t="n">
+        <v>4125</v>
+      </c>
+      <c r="L68" t="n">
+        <v>-6.86</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Radaan Mediaworks: வருமானம் உயர்ந்தும் 'கவலை அளிக்கும்' தணிக்கை அறிக்கை - முதலீட்டாளர்கள் என்ன செய்ய வேண்டும்? - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>["Radaan Mediaworks: வருமானம் உயர்ந்தும் 'கவலை அளிக்கும்' தணிக்கை அறிக்கை - முதலீட்டாளர்கள் என்ன செய்ய வேண்டும்? - Whalesbook", 'Radaan Mediaworks Q1 FY27: ఆదాయం పెరిగినా.. కంపెనీ మనుగడపై ఆడిటర్ల అనుమానం! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>PRAKASH</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Prakash Industries Limited</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="F69" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>129.99</v>
+      </c>
+      <c r="H69" t="n">
+        <v>126.19</v>
+      </c>
+      <c r="I69" t="n">
+        <v>137.68</v>
+      </c>
+      <c r="J69" t="n">
+        <v>128.14</v>
+      </c>
+      <c r="K69" t="n">
+        <v>167065</v>
+      </c>
+      <c r="L69" t="n">
+        <v>-6.93</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Prakash Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>['Prakash Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Prakash Pipes Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Vishnu Prakash Q1 Results FY27: Net Loss Rs 39 Cr, Revenue Rs 137 - Univest', 'Prakash Steelage Q1 Results: Net profit falls 59% YoY to ₹16.35 lakh - scanx.trade', 'Prakash Pipes Convenes Board Meeting to Review Q1 FY27 Financial Results - Sahi']</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="F70" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="G70" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="H70" t="n">
+        <v>321.25</v>
+      </c>
+      <c r="I70" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="J70" t="n">
+        <v>322.25</v>
+      </c>
+      <c r="K70" t="n">
+        <v>23048</v>
+      </c>
+      <c r="L70" t="n">
+        <v>-7.11</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Thomas Scott India Q1 Results: Earnings Call Scheduled for Aug 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>['Thomas Scott India Q1 Results: Earnings Call Scheduled for Aug 17 - scanx.trade', 'Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks', 'Thomas Scott (India) Reports Q1 Revenue Of ₹65.8 Crore, Net Profit At ₹5.4 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NSLNISP</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NMDC Steel Limited</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="F71" t="n">
+        <v>43</v>
+      </c>
+      <c r="G71" t="n">
+        <v>43.78</v>
+      </c>
+      <c r="H71" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="I71" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="J71" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="K71" t="n">
+        <v>3831251</v>
+      </c>
+      <c r="L71" t="n">
+        <v>-7.26</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>NSLNISP: Q1 FY27 revenue grew year-over-year, with net profit at ₹50.51 crore and no loan defaults - TradingView</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>['NSLNISP: Q1 FY27 revenue grew year-over-year, with net profit at ₹50.51 crore and no loan defaults - TradingView', 'NMDC Steel Q1 Results: नफ्यात तब्बल **97%** वाढ, शेअरमधील गुंतवणूकदारांचे लक्ष सरकारी निर्गुंतवणुकीवर - Whalesbook', 'NMDC Steel Q1 Profit Surges 97% to ₹50.5 Crore Amid Divestment Drive - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SIKA</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Sika Interplant Systems Limited</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1018.9</v>
+      </c>
+      <c r="F72" t="n">
+        <v>1040.1</v>
+      </c>
+      <c r="G72" t="n">
+        <v>1048.9</v>
+      </c>
+      <c r="H72" t="n">
+        <v>1009.1</v>
+      </c>
+      <c r="I72" t="n">
+        <v>1098.8</v>
+      </c>
+      <c r="J72" t="n">
+        <v>1018.9</v>
+      </c>
+      <c r="K72" t="n">
+        <v>13915</v>
+      </c>
+      <c r="L72" t="n">
+        <v>-7.27</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Sika Interplant Systems consolidated net profit declines 18.84% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>['Sika Interplant Systems consolidated net profit declines 18.84% in the June 2026 quarter - Business Standard', 'Sika stock holds steady as guidance lift points to recovery - ad-hoc-news.de', 'Berenberg: Sika FY26 Guidance Lift Signals Broad-based Sector Recovery; Buy Rating Kept - marketscreener.com', 'Sika Interplant Systems Ltd. Share Price Live Today - CNBC TV18', 'Sika Interplant Systems Ltd is Rated Hold - MarketsMojo']</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SAATVIKGL</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Saatvik Green Energy Limited</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>392.45</v>
+      </c>
+      <c r="F73" t="n">
+        <v>401</v>
+      </c>
+      <c r="G73" t="n">
+        <v>401</v>
+      </c>
+      <c r="H73" t="n">
+        <v>384.7</v>
+      </c>
+      <c r="I73" t="n">
+        <v>427.4</v>
+      </c>
+      <c r="J73" t="n">
+        <v>392.45</v>
+      </c>
+      <c r="K73" t="n">
+        <v>83117</v>
+      </c>
+      <c r="L73" t="n">
+        <v>-8.18</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>SAATVIKGL: Moderate Q1 FY27 results, but Odisha ramp-up and strong order book support positive outlook - TradingView</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>['SAATVIKGL: Moderate Q1 FY27 results, but Odisha ramp-up and strong order book support positive outlook - TradingView', 'SAATVIKGL: Q1 FY27 saw lower revenue and profit, but robust orders and expansion drive future growth - TradingView', 'SAATVIKGL: Revenue and profit fell significantly year-over-year amid cost pressures and strategic investments - TradingView', 'SAATVIKGL: Odisha facility nears ramp-up as order book hits 6.35 GW; margins to improve with integration - TradingView', 'Saatvik Green Energy Q1 Profit Drops 95 Percent Revenue Declines - sekbernews.id']</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TURTLEMINT</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Turtlemint Fintech Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="F74" t="n">
+        <v>130</v>
+      </c>
+      <c r="G74" t="n">
+        <v>130</v>
+      </c>
+      <c r="H74" t="n">
+        <v>124.32</v>
+      </c>
+      <c r="I74" t="n">
+        <v>137.44</v>
+      </c>
+      <c r="J74" t="n">
+        <v>125.44</v>
+      </c>
+      <c r="K74" t="n">
+        <v>228270</v>
+      </c>
+      <c r="L74" t="n">
+        <v>-8.73</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Turtlemint Q1 loss narrows to ₹38 crore as revenue jumps 40% - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>['Turtlemint Q1 loss narrows to ₹38 crore as revenue jumps 40% - CNBC TV18', 'Turtlemint revenue up 40% in Q1, losses narrow - The Economic Times', 'Turtlemint Fintech Solutions reports consolidated net loss of Rs 37.78 crore in the June 2026 quarter - Business Standard', 'Turtlemint Fintech Q1 Revenue Rises To ₹2.94B; Net Loss Narrows To ₹378M YoY - Sahi', 'Turtlemint Q1: Loss Declines 19% YoY To ₹38 Cr, Revenue Up 40% - Inc42']</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>ORCHPHARMA</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Orchid Pharma Limited</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>951.3</v>
+      </c>
+      <c r="F75" t="n">
+        <v>960</v>
+      </c>
+      <c r="G75" t="n">
+        <v>989.95</v>
+      </c>
+      <c r="H75" t="n">
+        <v>951</v>
+      </c>
+      <c r="I75" t="n">
+        <v>1045.65</v>
+      </c>
+      <c r="J75" t="n">
+        <v>951.3</v>
+      </c>
+      <c r="K75" t="n">
+        <v>28477</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-9.02</v>
+      </c>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DCAL</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Dishman Carbogen Amcis Limited</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>172.95</v>
+      </c>
+      <c r="F76" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="G76" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="H76" t="n">
+        <v>171.66</v>
+      </c>
+      <c r="I76" t="n">
+        <v>190.66</v>
+      </c>
+      <c r="J76" t="n">
+        <v>172.95</v>
+      </c>
+      <c r="K76" t="n">
+        <v>299711</v>
+      </c>
+      <c r="L76" t="n">
+        <v>-9.289999999999999</v>
+      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>ABM International Limited</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="F77" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="G77" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="H77" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="I77" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="J77" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="K77" t="n">
+        <v>1903</v>
+      </c>
+      <c r="L77" t="n">
+        <v>-9.98</v>
+      </c>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>POEL</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>POCL Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>146</v>
+      </c>
+      <c r="F78" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>150.2</v>
+      </c>
+      <c r="H78" t="n">
+        <v>146</v>
+      </c>
+      <c r="I78" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="J78" t="n">
+        <v>146</v>
+      </c>
+      <c r="K78" t="n">
+        <v>1752</v>
+      </c>
+      <c r="L78" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Van der Poel and Evenepoel train together for their "Project Canada" - Brujulabike.com</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>['Van der Poel and Evenepoel train together for their "Project Canada" - Brujulabike.com', "Nobody Expected Paris To End Like This | Van Der Poel's Greatest Tour Victory! The Punisher One Last Kill (73rLmpAk41) - Mshale", 'Remco Evenepoel launches ‘Project Canada’ with Mathieu van der Poel - Canadian Cycling Magazine', 'Van der Poel rides with Evenepoel before MTB World Championships - IDLprocycling.com', 'Mathieu van der Poel targets mountain bikes and Montreal - Canadian Cycling Magazine']</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Schneider Electric Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1226.3</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1219</v>
+      </c>
+      <c r="G79" t="n">
+        <v>1255</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1185</v>
+      </c>
+      <c r="I79" t="n">
+        <v>1369.2</v>
+      </c>
+      <c r="J79" t="n">
+        <v>1226.3</v>
+      </c>
+      <c r="K79" t="n">
+        <v>532960</v>
+      </c>
+      <c r="L79" t="n">
+        <v>-10.44</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>Schneider Electric Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>['Schneider Electric Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Schneider Electric Infra Q1 profit falls 70% as higher costs squeeze margins; orders hit record high - CNBC TV18', 'Schneider Electric Infrastructure Q1 Net Profit Drops To ₹12.4 Cr As Revenue Rises To ₹650 Cr - Sahi', 'Schneider Electric Infrastructure standalone net profit declines 69.84% in the June 2026 quarter - Business Standard', 'Schneider Electric Infrastructure Q1 Revenue Rises To 6.5B Rupees; Net Profit Drops To 124M - Sahi']</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SOLEX</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Solex Energy Limited</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>780.1</v>
+      </c>
+      <c r="F80" t="n">
+        <v>801</v>
+      </c>
+      <c r="G80" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="H80" t="n">
+        <v>770.3</v>
+      </c>
+      <c r="I80" t="n">
+        <v>879.85</v>
+      </c>
+      <c r="J80" t="n">
+        <v>780.1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>23339</v>
+      </c>
+      <c r="L80" t="n">
+        <v>-11.34</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Solex Energy Q1FY27 net profit falls 67% to ₹82.56M; EBITDA margin slips - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>['Solex Energy Q1FY27 net profit falls 67% to ₹82.56M; EBITDA margin slips - scanx.trade', 'Solex Energy June-Quarter Consol Net Profit 79.8 Million Rupees - TradingView', 'Solex Energy soars on bagging work order worth Rs 42.47 crore - Investment Guru India', 'Solex energy wins Rs 42.47 crore work order from private power company - scanx.trade', 'Solex Energy (BOM:544862) Shiller PE Ratio : (As of Aug. 15, 2026) - GuruFocus']</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-17 09:21:18 IST</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>166.42</v>
+      </c>
+      <c r="F81" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="G81" t="n">
+        <v>185</v>
+      </c>
+      <c r="H81" t="n">
+        <v>165</v>
+      </c>
+      <c r="I81" t="n">
+        <v>200.59</v>
+      </c>
+      <c r="J81" t="n">
+        <v>166.42</v>
+      </c>
+      <c r="K81" t="n">
+        <v>2403411</v>
+      </c>
+      <c r="L81" t="n">
+        <v>-17.03</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Q1 Results: Profit Slumps 57% As Margin Shrinks; Revenue Falls 32% - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>['Zaggle Prepaid Q1 Results: Profit Slumps 57% As Margin Shrinks; Revenue Falls 32% - NDTV Profit', 'Zaggle Q1 profit falls 33% despite 28% revenue growth as acquisition costs weigh on margins - CNBC TV18', 'ZAGGLE: Revenue rose but profit margins narrowed amid higher costs; strategic investments continue - TradingView', 'Zaggle profit falls 32.9% to 17.53cr, revenue up 27.5% - NewsBytes', 'Zaggle Prepaid Ocean Services Limited Enters Amendment Agreement With APAC Financial Services Private Limited - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O81"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$81</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$81</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$101</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4182,7 +4182,6 @@
       <c r="L62" t="n">
         <v>19.99</v>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4239,7 +4238,6 @@
       <c r="L63" t="n">
         <v>17.28</v>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4296,7 +4294,6 @@
       <c r="L64" t="n">
         <v>16.87</v>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4780,7 +4777,6 @@
       <c r="L72" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4837,7 +4833,6 @@
       <c r="L73" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr">
         <is>
           <t>[]</t>
@@ -4894,7 +4889,6 @@
       <c r="L74" t="n">
         <v>9.35</v>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5195,7 +5189,6 @@
       <c r="L79" t="n">
         <v>8.720000000000001</v>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5313,7 +5306,6 @@
       <c r="L81" t="n">
         <v>8.51</v>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5325,8 +5317,1220 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SHANTI-RE</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited-RE</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="F82" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="G82" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="H82" t="n">
+        <v>23.66</v>
+      </c>
+      <c r="I82" t="n">
+        <v>23.52</v>
+      </c>
+      <c r="J82" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="K82" t="n">
+        <v>130863</v>
+      </c>
+      <c r="L82" t="n">
+        <v>39.97</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>['Shanti Gold International Ltd. Share Price Live Today - CNBC TV18']</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="F83" t="n">
+        <v>86</v>
+      </c>
+      <c r="G83" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="H83" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="I83" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="J83" t="n">
+        <v>92.17</v>
+      </c>
+      <c r="K83" t="n">
+        <v>719068</v>
+      </c>
+      <c r="L83" t="n">
+        <v>20</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>['【4901.T FY2026 Q1 Earnings Call】Bio CDMO Losses Balloon to ¥70 Billion, BI Partial IPO Planned; Revenue Hits Record on Semiconductor Materials but Operating Profit Slides 32% - finance.biggo.com', 'Three H-1B rejections later, an Indian techie secures O-1 ‘extraordinary ability’ Visa - livemint.com', 'Rupiah Gains Ahead of Key BI Policy Meeting - TradingView', 'Xi qi bi ren (1997) - IMDb', 'Noh Seul-bi Reveals Idol Plastic Surgery: "I Had Surgery at That Same Hospital... Pretty Much All Celebrities Do It" - 스포츠조선']</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>PAKKA</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PAKKA LIMITED</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="F84" t="n">
+        <v>77.3</v>
+      </c>
+      <c r="G84" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="H84" t="n">
+        <v>75.89</v>
+      </c>
+      <c r="I84" t="n">
+        <v>74.40000000000001</v>
+      </c>
+      <c r="J84" t="n">
+        <v>89.28</v>
+      </c>
+      <c r="K84" t="n">
+        <v>1787278</v>
+      </c>
+      <c r="L84" t="n">
+        <v>20</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Pakka Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>['Pakka Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com', 'Pakka Q1 Results: Net profit falls 4% YoY to ₹3.07 lakh - scanx.trade', 'Pakka reports consolidated net profit of Rs 5.89 crore in the June 2026 quarter - Business Standard', 'Pakka Limited Confirms No Deviation in Preferential Issue Fund Use - tipranks.com', 'Pakka Limited Discloses SEBI Warning Over Disclosure Lapses - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HINDADH</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Hindustan Adhesives Limited</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="F85" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="G85" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="H85" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="I85" t="n">
+        <v>279.65</v>
+      </c>
+      <c r="J85" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="K85" t="n">
+        <v>6463</v>
+      </c>
+      <c r="L85" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: Stock Skyrockets After Reporting 1,044% QoQ Net Profit Growth in Q1 - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>['20% Upper Circuit: Stock Skyrockets After Reporting 1,044% QoQ Net Profit Growth in Q1 - Trade Brains']</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UFLEX</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UFLEX Limited</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>586.05</v>
+      </c>
+      <c r="F86" t="n">
+        <v>555</v>
+      </c>
+      <c r="G86" t="n">
+        <v>586.05</v>
+      </c>
+      <c r="H86" t="n">
+        <v>545</v>
+      </c>
+      <c r="I86" t="n">
+        <v>488.4</v>
+      </c>
+      <c r="J86" t="n">
+        <v>586.05</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3734414</v>
+      </c>
+      <c r="L86" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Uflex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>['Uflex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Uflex shares surge 16% after Q1 profit zooms 630% YoY - The Economic Times', 'UFlex Shares Surge 17% After 630% Profit Jump — But Can These Margins Last? - NiftyTrader', 'UFLEX announces Q1 FY27 results with revenue of ₹53,972 million and PAT of ₹4,233 million - businessupturn.com', 'UFLEX: Q1 FY27 saw robust revenue and profit growth, with new recycling operations and ongoing tax appeals - TradingView']</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MODTHREAD</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Modern Threads (India) Limited</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="F87" t="n">
+        <v>52</v>
+      </c>
+      <c r="G87" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="H87" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="I87" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="J87" t="n">
+        <v>57.63</v>
+      </c>
+      <c r="K87" t="n">
+        <v>192105</v>
+      </c>
+      <c r="L87" t="n">
+        <v>19.37</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>Modern Threads (India) Ltd. (MODTHREAD) Share Price Rises 20% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>['Modern Threads (India) Ltd. (MODTHREAD) Share Price Rises 20% Today - Univest', 'Modern Threads Q1 Results: Net profit up 9,800% YoY to ₹588 lakh - scanx.trade', 'Volume Gainers, August 17, 2026, 11:30 AM IST - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K88" t="n">
+        <v>5686531</v>
+      </c>
+      <c r="L88" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>['20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains', 'Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>DHATRE</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Limited</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="F89" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="G89" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H89" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="I89" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J89" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K89" t="n">
+        <v>95719</v>
+      </c>
+      <c r="L89" t="n">
+        <v>17.21</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Dhatre Udyog Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>['Dhatre Udyog Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Dhatre Udyog Q1 Results: Net Loss Widens To ₹29.28 Lakh As Revenue Drops - scanx.trade', 'Dhatre Udyog: Approves Q1 FY27 Unaudited Results with Net Loss - InvestyWise', 'Dhatre Udyog reports standalone net loss of Rs 0.29 crore in the June 2026 quarter - Business Standard', 'Dhatre Udyog Q1FY26 net profit hits ₹573 lakh on OCI surge - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PREMIERPOL</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Premier Polyfilm Limited</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="F90" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="G90" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="H90" t="n">
+        <v>74.05</v>
+      </c>
+      <c r="I90" t="n">
+        <v>73.55</v>
+      </c>
+      <c r="J90" t="n">
+        <v>85.45</v>
+      </c>
+      <c r="K90" t="n">
+        <v>3454869</v>
+      </c>
+      <c r="L90" t="n">
+        <v>16.18</v>
+      </c>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SHERVANI</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>337</v>
+      </c>
+      <c r="F91" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="G91" t="n">
+        <v>352</v>
+      </c>
+      <c r="H91" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="I91" t="n">
+        <v>294</v>
+      </c>
+      <c r="J91" t="n">
+        <v>337</v>
+      </c>
+      <c r="K91" t="n">
+        <v>226</v>
+      </c>
+      <c r="L91" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>['Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard', 'Shervani Industrial Syndicate posts profit; appoints new Executive Director - Whalesbook', 'Delhi High Court Orders Meta To Takedown AI Videos Linking Former Union Minister Saleem Iqbal Shervani To ... - livelaw.in', 'Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com', 'Shervani Industrial Syndicate Ltd is Rated Strong Sell - marketsmojo.com']</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SUMEDHA</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Sumedha Fiscal Services Limited</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>45</v>
+      </c>
+      <c r="F92" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="G92" t="n">
+        <v>47</v>
+      </c>
+      <c r="H92" t="n">
+        <v>39</v>
+      </c>
+      <c r="I92" t="n">
+        <v>39.27</v>
+      </c>
+      <c r="J92" t="n">
+        <v>45</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1004</v>
+      </c>
+      <c r="L92" t="n">
+        <v>14.59</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Sumedha Fiscal publishes Q1FY26 results in newspapers, net profit rises 14% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>['Sumedha Fiscal publishes Q1FY26 results in newspapers, net profit rises 14% - scanx.trade', 'Sumedha Fiscal Services Q1 Results: లాభాల బాట పట్టిన కంపెనీ.. కానీ ఆదాయంలో తగ్గుదల! - Whalesbook', 'Sumedha Fiscal Services consolidated net profit rises 13.75% in the June 2026 quarter - Business Standard', 'Sumedha Fiscal Services Turns Profitable With ₹3.24 Crore Net Profit - Whalesbook', 'Prayan Animation strengthens global ambitions with Sumedha Saraogi - animationxpress.com']</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KHAICHEM</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Limited</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="F93" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="G93" t="n">
+        <v>60.5</v>
+      </c>
+      <c r="H93" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I93" t="n">
+        <v>52.37</v>
+      </c>
+      <c r="J93" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="K93" t="n">
+        <v>1627884</v>
+      </c>
+      <c r="L93" t="n">
+        <v>14.38</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>['Khaitan Chemicals &amp; Fertilizers Ltd. (KHAICHEM) Share Price Rises 10.63% as Stock Enters Top Gainers Today - Univest']</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ASIANENE</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Limited</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="F94" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="G94" t="n">
+        <v>432</v>
+      </c>
+      <c r="H94" t="n">
+        <v>372</v>
+      </c>
+      <c r="I94" t="n">
+        <v>374.4</v>
+      </c>
+      <c r="J94" t="n">
+        <v>427.8</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1788634</v>
+      </c>
+      <c r="L94" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Asian Energy Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>['Asian Energy Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Asian Energy Services Files June-Quarter Unaudited Results with SEBI - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>VIKRAMSOLR</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Vikram Solar Limited</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="F95" t="n">
+        <v>163</v>
+      </c>
+      <c r="G95" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="H95" t="n">
+        <v>161.47</v>
+      </c>
+      <c r="I95" t="n">
+        <v>160.15</v>
+      </c>
+      <c r="J95" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="K95" t="n">
+        <v>65091295</v>
+      </c>
+      <c r="L95" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Vikram Solar’s Q1 FY27 Profit Falls Despite 38% Revenue Growth - TaiyangNews</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>['Vikram Solar’s Q1 FY27 Profit Falls Despite 38% Revenue Growth - TaiyangNews', 'Vikram Solar Limited Enhances Proposed Wafer and Ingot Manufacturing Facility Capacity At Gangaikondan Site - marketscreener.com', 'Vikram Solar Launches 6 GW Solar Module Plant in Gangaikondan, Tamil Nadu - Saur Energy']</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>EXPLEOSOL</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Expleo Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>923.85</v>
+      </c>
+      <c r="F96" t="n">
+        <v>830</v>
+      </c>
+      <c r="G96" t="n">
+        <v>945.9</v>
+      </c>
+      <c r="H96" t="n">
+        <v>829.7</v>
+      </c>
+      <c r="I96" t="n">
+        <v>815.95</v>
+      </c>
+      <c r="J96" t="n">
+        <v>923.85</v>
+      </c>
+      <c r="K96" t="n">
+        <v>6142838</v>
+      </c>
+      <c r="L96" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Expleo Solutions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>['Expleo Solutions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Expleo Solutions files Q1FY27 results with BSE and NSE - scanx.trade', 'Expleo Solutions Files Q1 FY27 Earnings Presentation With Indian Exchanges - tipranks.com', 'Expleo Solutions Publishes Q1 FY2026 Unaudited Results in Newspapers - tipranks.com', 'Expleo Solutions Ltd. Share Price Today: Price Rise Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>DOLPHIN</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Dolphin Offshore Enterprises (India) Limited</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="F97" t="n">
+        <v>515</v>
+      </c>
+      <c r="G97" t="n">
+        <v>585.6</v>
+      </c>
+      <c r="H97" t="n">
+        <v>500</v>
+      </c>
+      <c r="I97" t="n">
+        <v>508.1</v>
+      </c>
+      <c r="J97" t="n">
+        <v>573.75</v>
+      </c>
+      <c r="K97" t="n">
+        <v>274715</v>
+      </c>
+      <c r="L97" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Dolphin Entertainment Inc reports results for the quarter ended June 30 - Earnings Summary - TradingView</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>['Dolphin Entertainment Inc reports results for the quarter ended June 30 - Earnings Summary - TradingView', 'Dolphin Entertainment earnings missed by $0.16, revenue fell short of estimates - Investing.com', 'Dolphin Offshore Enterprises (India) Ltd. (DOLPHIN) Share Price Rises 8.22% Today - Univest', 'Dolphin Points Emerge As Must See Destinations For Visitors To Varanasi - ETV Bharat', 'REG - Brewin Dolphin W.M. DCC Energy PLC - Form 8.3 - DCC Energy plc 170826 - TradingView']</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>KAYA</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Kaya Limited</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>335</v>
+      </c>
+      <c r="F98" t="n">
+        <v>296.85</v>
+      </c>
+      <c r="G98" t="n">
+        <v>349</v>
+      </c>
+      <c r="H98" t="n">
+        <v>290.8</v>
+      </c>
+      <c r="I98" t="n">
+        <v>296.85</v>
+      </c>
+      <c r="J98" t="n">
+        <v>335</v>
+      </c>
+      <c r="K98" t="n">
+        <v>173026</v>
+      </c>
+      <c r="L98" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Kaya Limited NRC approves 75,000 stock options under ESOS Scheme-VI - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>['Kaya Limited NRC approves 75,000 stock options under ESOS Scheme-VI - scanx.trade', 'Kaya Limited shareholders approve FY26 financials and director reappointments - scanx.trade', 'Scholastic director Kaya Henderson sells $130,812 in stock By Investing.com - Investing.com India', 'Hayden Panettiere dies at 36: ‘Heroes’ and ‘Nashville’ star leaves behind daughter Kaya - Storyboard18', 'About Hayden Panettiere and her daughter Kaya Klitschko: Why did the ‘Nashville’ star give up her custody - The Times of India']</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ALPHAGEO</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Alphageo (India) Limited</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>340</v>
+      </c>
+      <c r="F99" t="n">
+        <v>314</v>
+      </c>
+      <c r="G99" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="H99" t="n">
+        <v>302.42</v>
+      </c>
+      <c r="I99" t="n">
+        <v>301.36</v>
+      </c>
+      <c r="J99" t="n">
+        <v>340</v>
+      </c>
+      <c r="K99" t="n">
+        <v>229452</v>
+      </c>
+      <c r="L99" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Alphageo Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>['Alphageo Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Alphageo Q1 Results: Net profit rises 1,286% YoY to ₹127 crore - scanx.trade', 'Alphageo (India) consolidated net profit rises 1660.49% in the June 2026 quarter - Business Standard', 'Alphageo Q1FY27 net profit turns to ₹148.58 crore gain - scanx.trade', 'Alphageo (India) fixes Sept 11 record date for FY26 dividend - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MANORAMA</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Manorama Industries Limited</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1955</v>
+      </c>
+      <c r="F100" t="n">
+        <v>1775</v>
+      </c>
+      <c r="G100" t="n">
+        <v>2043</v>
+      </c>
+      <c r="H100" t="n">
+        <v>1745.5</v>
+      </c>
+      <c r="I100" t="n">
+        <v>1737.1</v>
+      </c>
+      <c r="J100" t="n">
+        <v>1955</v>
+      </c>
+      <c r="K100" t="n">
+        <v>7248199</v>
+      </c>
+      <c r="L100" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>Manorama Industries shares surge over 8% after strong Q1 results - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>['Manorama Industries shares surge over 8% after strong Q1 results - The Economic Times', 'MANORAMA: Q1 FY2027 delivered robust revenue and profit growth, with strong margins and strategic global expansion - TradingView', 'MANORAMA: Q1 FY27 delivered strong revenue and profit growth, with strategic expansion and stable margins - TradingView', 'Manorama Industries consolidated net profit rises 67.58% in the June 2026 quarter - Business Standard', "Manorama Industries Ltd leads gainers in 'A' group - Business Standard"]</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>LATTEYS</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Latteys Industries Limited</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="F101" t="n">
+        <v>20.99</v>
+      </c>
+      <c r="G101" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="H101" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="I101" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="J101" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="K101" t="n">
+        <v>651587</v>
+      </c>
+      <c r="L101" t="n">
+        <v>12</v>
+      </c>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O81"/>
+  <autoFilter ref="A1:O101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5337,7 +6541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9059,7 +10263,6 @@
       <c r="L62" t="n">
         <v>-5.4</v>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9177,7 +10380,6 @@
       <c r="L64" t="n">
         <v>-6.05</v>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9234,7 +10436,6 @@
       <c r="L65" t="n">
         <v>-6.08</v>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9352,7 +10553,6 @@
       <c r="L67" t="n">
         <v>-6.59</v>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9836,7 +11036,6 @@
       <c r="L75" t="n">
         <v>-9.02</v>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9893,7 +11092,6 @@
       <c r="L76" t="n">
         <v>-9.289999999999999</v>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9950,7 +11148,6 @@
       <c r="L77" t="n">
         <v>-9.98</v>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10206,8 +11403,1212 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Limited</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>603</v>
+      </c>
+      <c r="F82" t="n">
+        <v>662</v>
+      </c>
+      <c r="G82" t="n">
+        <v>662</v>
+      </c>
+      <c r="H82" t="n">
+        <v>588.1</v>
+      </c>
+      <c r="I82" t="n">
+        <v>653.4</v>
+      </c>
+      <c r="J82" t="n">
+        <v>603</v>
+      </c>
+      <c r="K82" t="n">
+        <v>2791511</v>
+      </c>
+      <c r="L82" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>['Shreeji Shipping Global Ltd. (SHREEJISPG) Share Price Hits 52-Week High - Univest', 'Shreeji Shipping Q1 Results: Net Profit Rises 19% YoY To ₹443 Crore - scanx.trade', 'Shreeji Shipping Global Q1 FY27: Net Profit Rises 19% YoY to ₹44.29 Cr - Trade Brains']</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>POEL</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>POCL Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>150</v>
+      </c>
+      <c r="F83" t="n">
+        <v>150.1</v>
+      </c>
+      <c r="G83" t="n">
+        <v>154</v>
+      </c>
+      <c r="H83" t="n">
+        <v>145</v>
+      </c>
+      <c r="I83" t="n">
+        <v>162.6</v>
+      </c>
+      <c r="J83" t="n">
+        <v>150</v>
+      </c>
+      <c r="K83" t="n">
+        <v>57496</v>
+      </c>
+      <c r="L83" t="n">
+        <v>-7.75</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>Nobody Expected Paris To End Like This | Van Der Poel's Greatest Tour Victory! The Punisher One Last Kill (73rLmpAk41) - Mshale</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>["Nobody Expected Paris To End Like This | Van Der Poel's Greatest Tour Victory! The Punisher One Last Kill (73rLmpAk41) - Mshale", 'Van der Poel and Evenepoel train together for their "Project Canada" - Brujulabike.com', 'Remco Evenepoel launches ‘Project Canada’ with Mathieu van der Poel - Canadian Cycling Magazine', 'Van der Poel rides with Evenepoel before MTB World Championships - IDLprocycling.com', 'Mathieu van der Poel targets mountain bikes and Montreal - Canadian Cycling Magazine']</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>CUPID</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Cupid Limited</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="F84" t="n">
+        <v>294.51</v>
+      </c>
+      <c r="G84" t="n">
+        <v>295.35</v>
+      </c>
+      <c r="H84" t="n">
+        <v>235.11</v>
+      </c>
+      <c r="I84" t="n">
+        <v>293.88</v>
+      </c>
+      <c r="J84" t="n">
+        <v>270.9</v>
+      </c>
+      <c r="K84" t="n">
+        <v>59146915</v>
+      </c>
+      <c r="L84" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Cupid Q1 Results: Profit Nearly Triples As Margin Widens; Revenue Up 2.6x - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>['Cupid Q1 Results: Profit Nearly Triples As Margin Widens; Revenue Up 2.6x - NDTV Profit', 'Cupid Limited Revises Earnings Guidance for Fy2027 - marketscreener.com', 'Cupid net profit jumps 194% YoY to ₹44 crore in Q1 as margins expand sharply; raises FY27 guidance - livemint.com', 'Cupid Limited Delivers Strong Q1 FY27 Performance with 159% YoY Operating Income Growth, 194% YoY Net Profit Growth - Big News Network.com', 'Cupid Limited corrects typographical error in Q1FY27 audit report label - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>ESSARSHPNG</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Essar Shipping Limited</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>17.88</v>
+      </c>
+      <c r="G85" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="H85" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="I85" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="J85" t="n">
+        <v>16.1</v>
+      </c>
+      <c r="K85" t="n">
+        <v>1260890</v>
+      </c>
+      <c r="L85" t="n">
+        <v>-7.95</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Essar Shipping Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>['Essar Shipping Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Essar Shipping Board Clears Q1 Results, Approves Sale of Essar Tug III - tipranks.com']</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TIJARIA</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Limited</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="F86" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="G86" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5.42</v>
+      </c>
+      <c r="I86" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="J86" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="K86" t="n">
+        <v>288047</v>
+      </c>
+      <c r="L86" t="n">
+        <v>-8.130000000000001</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>['Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times', 'Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade', 'Tijaria Polypipes appoints new independent director, renews auditor at 20th AGM - scanx.trade', 'Bhatia Communications &amp; Retail (India) standalone net profit rises 90.50% in the June 2026 quarter - Business Standard', 'Samor Reality reports standalone net loss of Rs 0.09 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgears Limited</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>299</v>
+      </c>
+      <c r="F87" t="n">
+        <v>305</v>
+      </c>
+      <c r="G87" t="n">
+        <v>315.85</v>
+      </c>
+      <c r="H87" t="n">
+        <v>294</v>
+      </c>
+      <c r="I87" t="n">
+        <v>325.6</v>
+      </c>
+      <c r="J87" t="n">
+        <v>299</v>
+      </c>
+      <c r="K87" t="n">
+        <v>7957</v>
+      </c>
+      <c r="L87" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>PARNAXLAB</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Parnax Lab Limited</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="F88" t="n">
+        <v>108.03</v>
+      </c>
+      <c r="G88" t="n">
+        <v>120.05</v>
+      </c>
+      <c r="H88" t="n">
+        <v>108.03</v>
+      </c>
+      <c r="I88" t="n">
+        <v>129.35</v>
+      </c>
+      <c r="J88" t="n">
+        <v>118.55</v>
+      </c>
+      <c r="K88" t="n">
+        <v>1206</v>
+      </c>
+      <c r="L88" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Parnax Lab Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>['Parnax Lab Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PRIMO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Primo Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="F89" t="n">
+        <v>24.15</v>
+      </c>
+      <c r="G89" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H89" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="I89" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="J89" t="n">
+        <v>23.36</v>
+      </c>
+      <c r="K89" t="n">
+        <v>384904</v>
+      </c>
+      <c r="L89" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Primo Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>['Primo Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Primo Service Solutions Public Company Limited Reports Earnings Results for the Second Quarter and Six Months Ended June 30, 2026 - marketscreener.com', 'Primo Chemicals consolidated net profit rises 14.71% in the June 2026 quarter - Business Standard', 'Primo Chemicals Reports Q1 Revenue Of 1.4B Rupees With 36M Net Profit - Sahi', 'PRMB: Primo Brands Corporation - Options Chain - Zacks Investment Research']</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>KAPSTON</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>534</v>
+      </c>
+      <c r="F90" t="n">
+        <v>593.9</v>
+      </c>
+      <c r="G90" t="n">
+        <v>593.9</v>
+      </c>
+      <c r="H90" t="n">
+        <v>495.75</v>
+      </c>
+      <c r="I90" t="n">
+        <v>588.4</v>
+      </c>
+      <c r="J90" t="n">
+        <v>534</v>
+      </c>
+      <c r="K90" t="n">
+        <v>271846</v>
+      </c>
+      <c r="L90" t="n">
+        <v>-9.25</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Kapston Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>['Kapston Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Kapston Services consolidated net profit rises 38.50% in the June 2026 quarter - Business Standard', 'Kapston Q1 Net Profit Jumps 38.5% to ₹8.49 Crore, Revenue Up 15.8% - Sahi', 'Kapston Services Share Price Today: Price Fall Analysis - Univest', 'Kapston Home Services Pvt. Ltd. Launches Consumer App in Hyderabad - Telangana Today']</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MEDICAMEQ</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Medicamen Biotech Limited</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>218</v>
+      </c>
+      <c r="F91" t="n">
+        <v>232</v>
+      </c>
+      <c r="G91" t="n">
+        <v>238.89</v>
+      </c>
+      <c r="H91" t="n">
+        <v>215</v>
+      </c>
+      <c r="I91" t="n">
+        <v>240.45</v>
+      </c>
+      <c r="J91" t="n">
+        <v>218</v>
+      </c>
+      <c r="K91" t="n">
+        <v>59925</v>
+      </c>
+      <c r="L91" t="n">
+        <v>-9.34</v>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>ABM International Limited</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="F92" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="G92" t="n">
+        <v>59.44</v>
+      </c>
+      <c r="H92" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="I92" t="n">
+        <v>62.44</v>
+      </c>
+      <c r="J92" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="K92" t="n">
+        <v>7666</v>
+      </c>
+      <c r="L92" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Limited</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="F93" t="n">
+        <v>81.84999999999999</v>
+      </c>
+      <c r="G93" t="n">
+        <v>82</v>
+      </c>
+      <c r="H93" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="I93" t="n">
+        <v>82.36</v>
+      </c>
+      <c r="J93" t="n">
+        <v>74.13</v>
+      </c>
+      <c r="K93" t="n">
+        <v>202685</v>
+      </c>
+      <c r="L93" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SCHNEIDER</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Schneider Electric Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1232.2</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1219</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1255</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1185</v>
+      </c>
+      <c r="I94" t="n">
+        <v>1369.2</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1232.2</v>
+      </c>
+      <c r="K94" t="n">
+        <v>2282209</v>
+      </c>
+      <c r="L94" t="n">
+        <v>-10.01</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>Schneider Electric Infrastructure Share Price Slumps Over 12% After Q1 Results. What Should Investors Do? - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>['Schneider Electric Infrastructure Share Price Slumps Over 12% After Q1 Results. What Should Investors Do? - NDTV Profit', 'Schneider Electric Infrastructure Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Schneider Electric Infra Q1 profit falls 70% as higher costs squeeze margins; orders hit record high - CNBC TV18', 'Schneider Electric Infrastructure shares drop 11% after Q1 profit plunges 70%, margins halve - CNBC TV18', 'Transcript : Schneider Electric Infrastructure Limited, Q1 2027 Earnings Call, Aug 17, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SOLEX</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Solex Energy Limited</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>790</v>
+      </c>
+      <c r="F95" t="n">
+        <v>801</v>
+      </c>
+      <c r="G95" t="n">
+        <v>829.8</v>
+      </c>
+      <c r="H95" t="n">
+        <v>770.3</v>
+      </c>
+      <c r="I95" t="n">
+        <v>879.85</v>
+      </c>
+      <c r="J95" t="n">
+        <v>790</v>
+      </c>
+      <c r="K95" t="n">
+        <v>144123</v>
+      </c>
+      <c r="L95" t="n">
+        <v>-10.21</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>Solex Energy Q1 FY27 Profit Falls 67% YoY, Revenue Up 0.47% - Saur Energy</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>['Solex Energy Q1 FY27 Profit Falls 67% YoY, Revenue Up 0.47% - Saur Energy', 'Solex Energy Q1FY27 net profit falls 67% to ₹82.56M; EBITDA margin slips - scanx.trade', 'Solex Energy Q1 FY27 Revenue Rises 1.8%, Profit Falls 67% - TaiyangNews', 'Solex Energy consolidated net profit declines 66.98% in the June 2026 quarter - Business Standard', 'Solex Energy Q1 Profit Down 66% To Rs 8.26 Cr; Signs Rs 4,000 Cr Gujarat MoU - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="F96" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="G96" t="n">
+        <v>59</v>
+      </c>
+      <c r="H96" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="I96" t="n">
+        <v>57</v>
+      </c>
+      <c r="J96" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="K96" t="n">
+        <v>1308</v>
+      </c>
+      <c r="L96" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>['KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>KERNEX</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems (India) Limited</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1788.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>2001</v>
+      </c>
+      <c r="G97" t="n">
+        <v>2041.4</v>
+      </c>
+      <c r="H97" t="n">
+        <v>1711.7</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2024.2</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1788.3</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1555993</v>
+      </c>
+      <c r="L97" t="n">
+        <v>-11.65</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>Kernex Microsystems Q1 profit jumps nearly 15-fold to ₹109.8 crore as Kavach orders drive sharp revenue growth - businessupturn.com</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>['Kernex Microsystems Q1 profit jumps nearly 15-fold to ₹109.8 crore as Kavach orders drive sharp revenue growth - businessupturn.com', 'Kernex Microsystems (India) Ltd Says June-Quarter Consol Net Profit 1.10 Billion Rupees - TradingView', 'Kernex Microsystems to complete CLW-II order by November 2026 - scanx.trade', 'Kernex Microsystems (India) secures Rs 15.90 crore order amid ongoing CLW project - businessupturn.com', 'Kernex Microsystems (India) Share Price Target 2027 to 2030: Anal - Univest']</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>PRISMX</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Prismx Global Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>922092</v>
+      </c>
+      <c r="L98" t="n">
+        <v>-13.79</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Prismx Global Ventures consolidated net profit declines 75.17% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>['Prismx Global Ventures consolidated net profit declines 75.17% in the June 2026 quarter - Business Standard', 'Prismx Global Ventures Q1 net profit falls 75% to ₹37.36 lakhs - scanx.trade', 'Price to sales forward of Prismx Global Ventures Ltd. – BSE:PRISMX - TradingView', 'Prismx Global Standalone June 2026 Net Sales at Rs 0.23 crore, down 95.83% Y-o-Y - Moneycontrol.com', 'C &amp; C Constructions reports consolidated net loss of Rs 1.48 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>295</v>
+      </c>
+      <c r="F99" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="G99" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="I99" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="J99" t="n">
+        <v>295</v>
+      </c>
+      <c r="K99" t="n">
+        <v>335204</v>
+      </c>
+      <c r="L99" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>Thomas Scott India Q1 Results: Earnings Call Scheduled for Aug 17 - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>['Thomas Scott India Q1 Results: Earnings Call Scheduled for Aug 17 - scanx.trade', 'Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - tipranks.com', 'Thomas Scott (India) Reports Q1 Revenue Of ₹65.8 Crore, Net Profit At ₹5.4 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NGL Fine-Chem Limited</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>2901</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3489.9</v>
+      </c>
+      <c r="G100" t="n">
+        <v>3490</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2801.1</v>
+      </c>
+      <c r="I100" t="n">
+        <v>3454</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2901</v>
+      </c>
+      <c r="K100" t="n">
+        <v>58561</v>
+      </c>
+      <c r="L100" t="n">
+        <v>-16.01</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>NGL Fine Chem Q1 Results: Net profit up 99% YoY to ₹18.40 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>['NGL Fine Chem Q1 Results: Net profit up 99% YoY to ₹18.40 crore - scanx.trade', 'NGL Fine Chem Q1 Results: Net profit jumps 115% YoY to ₹1,645.13 lakh - scanx.trade', 'NGL Fine-Chem Share Price Today: 8.02% Fall, Key Metrics - Univest']</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2026-08-17 16:29:36 IST</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>160.48</v>
+      </c>
+      <c r="F101" t="n">
+        <v>182.4</v>
+      </c>
+      <c r="G101" t="n">
+        <v>185</v>
+      </c>
+      <c r="H101" t="n">
+        <v>160.48</v>
+      </c>
+      <c r="I101" t="n">
+        <v>200.59</v>
+      </c>
+      <c r="J101" t="n">
+        <v>160.48</v>
+      </c>
+      <c r="K101" t="n">
+        <v>12084279</v>
+      </c>
+      <c r="L101" t="n">
+        <v>-20</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>['Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit', 'Zaggle Prepaid Q1 Results: Profit Slumps 57% As Margin Shrinks; Revenue Falls 32% - NDTV Profit', 'Zaggle Q1 profit falls 33% despite 28% revenue growth as acquisition costs weigh on margins - CNBC TV18', 'Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st', 'Zaggle Prepaid Ocean Services Limited Enters Amendment Agreement With APAC Financial Services Private Limited - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O81"/>
+  <autoFilter ref="A1:O101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$101</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$101</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5850,7 +5850,6 @@
       <c r="L90" t="n">
         <v>16.18</v>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6517,7 +6516,6 @@
       <c r="L101" t="n">
         <v>12</v>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6529,8 +6527,1192 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ODYCORP</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Odyssey Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="F102" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="G102" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="H102" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="I102" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J102" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="K102" t="n">
+        <v>5996</v>
+      </c>
+      <c r="L102" t="n">
+        <v>8.24</v>
+      </c>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>PACIFICI</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="F103" t="n">
+        <v>146</v>
+      </c>
+      <c r="G103" t="n">
+        <v>146</v>
+      </c>
+      <c r="H103" t="n">
+        <v>111.15</v>
+      </c>
+      <c r="I103" t="n">
+        <v>136</v>
+      </c>
+      <c r="J103" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="K103" t="n">
+        <v>112</v>
+      </c>
+      <c r="L103" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SGLRES</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SGL Resources Limited</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="F104" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G104" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="H104" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I104" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J104" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="K104" t="n">
+        <v>27639</v>
+      </c>
+      <c r="L104" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>SGL Resources Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>['SGL Resources Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="F105" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G105" t="n">
+        <v>18</v>
+      </c>
+      <c r="H105" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="I105" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="J105" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="K105" t="n">
+        <v>11564</v>
+      </c>
+      <c r="L105" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>['Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard', 'SBEC Systems (India) consolidated net profit declines 13.64% in the June 2026 quarter - Business Standard', 'Parnax Lab consolidated net profit declines 86.85% in the June 2026 quarter - Business Standard', 'Amrapali Industries consolidated net profit rises 930.56% in the June 2026 quarter - Business Standard', 'Fedders Holding consolidated net profit declines 34.26% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>QUINTEGRA</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="H106" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I106" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J106" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K106" t="n">
+        <v>79092</v>
+      </c>
+      <c r="L106" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>Quintegra Solutions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>['Quintegra Solutions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Quintegra Solutions reports standalone net loss of Rs 0.05 crore in the June 2026 quarter - Business Standard', 'Quintegra Solutions posts $828k net loss in FY26; AGM scheduled for Sept 9 - scanx.trade', 'Genus Paper &amp; Boards standalone net profit declines 15.38% in the June 2026 quarter - Business Standard', 'K.P. Energy consolidated net profit rises 2.60% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>VGL</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VARVEE GLOBAL LIMITED</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="F107" t="n">
+        <v>59</v>
+      </c>
+      <c r="G107" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="H107" t="n">
+        <v>57</v>
+      </c>
+      <c r="I107" t="n">
+        <v>58.66</v>
+      </c>
+      <c r="J107" t="n">
+        <v>61.24</v>
+      </c>
+      <c r="K107" t="n">
+        <v>14150</v>
+      </c>
+      <c r="L107" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>VGL:ASX Announcement - Vista Group raises revenue guidance as market share expands - 03 Aug 2026 - Market Index</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>['VGL:ASX Announcement - Vista Group raises revenue guidance as market share expands - 03 Aug 2026 - Market Index', 'Vista Group (VGL)—HOYTS ANZ Contract Upgrade Announcement - Smartkarma', 'Vista Group (ASX:VGL) Gains as Cinema Software Guidance Lifts Market Confidence - Kalkine', 'Vista (ASX:VGL) Financial Software Guidance Reflects Cloud Services Growth - Kalkine Media', 'VGL: SaaS revenue surges 38% as cloud migration and marquee client wins drive upgraded 2026 outlook - TradingView']</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>AIROLAM</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Airo Lam limited</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>90</v>
+      </c>
+      <c r="F108" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="G108" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="H108" t="n">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="I108" t="n">
+        <v>87.29000000000001</v>
+      </c>
+      <c r="J108" t="n">
+        <v>90</v>
+      </c>
+      <c r="K108" t="n">
+        <v>8937</v>
+      </c>
+      <c r="L108" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>Airo Lam Ltd. Share Price Rise: Technicals and Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>['Airo Lam Ltd. Share Price Rise: Technicals and Valuation - Univest']</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SILLYMONKS</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Silly Monks Entertainment Limited</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="F109" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="G109" t="n">
+        <v>16.47</v>
+      </c>
+      <c r="H109" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="I109" t="n">
+        <v>15.63</v>
+      </c>
+      <c r="J109" t="n">
+        <v>16.07</v>
+      </c>
+      <c r="K109" t="n">
+        <v>10141</v>
+      </c>
+      <c r="L109" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>JMA</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Jullundur Motor Agency (Delhi) Limited</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="F110" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="G110" t="n">
+        <v>89.98999999999999</v>
+      </c>
+      <c r="H110" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="I110" t="n">
+        <v>87.84</v>
+      </c>
+      <c r="J110" t="n">
+        <v>89.79000000000001</v>
+      </c>
+      <c r="K110" t="n">
+        <v>14284</v>
+      </c>
+      <c r="L110" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>There's A Lot To Like About Jullundur Motor Agency (Delhi)'s (NSE:JMA) Upcoming ₹3.00 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>["There's A Lot To Like About Jullundur Motor Agency (Delhi)'s (NSE:JMA) Upcoming ₹3.00 Dividend - simplywall.st", 'JMA, Saudi HMG discuss recruitment of Jordanian doctors - وكالة الانباء الاردنية', 'Level 5 Emergency Warning for heavy rain : JMA news conference | NHK WORLD-JAPAN News - nhk.or.jp', 'JMA alert system misses issuing early forecast for Chiba rainbands - 朝日新聞', 'JMA vs Brentwood! - Yahoo']</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>THEMISMED</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Themis Medicare Limited</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="F111" t="n">
+        <v>103.1</v>
+      </c>
+      <c r="G111" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="H111" t="n">
+        <v>102.15</v>
+      </c>
+      <c r="I111" t="n">
+        <v>104.85</v>
+      </c>
+      <c r="J111" t="n">
+        <v>106.99</v>
+      </c>
+      <c r="K111" t="n">
+        <v>61527</v>
+      </c>
+      <c r="L111" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Themis Medicare updates Company Secretary and RTA contact emails - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>['Themis Medicare updates Company Secretary and RTA contact emails - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ISHANCH</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Ishan Dyes and Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="F112" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="G112" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="H112" t="n">
+        <v>46</v>
+      </c>
+      <c r="I112" t="n">
+        <v>48.17</v>
+      </c>
+      <c r="J112" t="n">
+        <v>48.98</v>
+      </c>
+      <c r="K112" t="n">
+        <v>45269</v>
+      </c>
+      <c r="L112" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MAKERSL</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Makers Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>157</v>
+      </c>
+      <c r="F113" t="n">
+        <v>164.6</v>
+      </c>
+      <c r="G113" t="n">
+        <v>171.95</v>
+      </c>
+      <c r="H113" t="n">
+        <v>150.05</v>
+      </c>
+      <c r="I113" t="n">
+        <v>156.1</v>
+      </c>
+      <c r="J113" t="n">
+        <v>157</v>
+      </c>
+      <c r="K113" t="n">
+        <v>315</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Makers Laboratories Ltd – NSE:MAKERSL - TradingView</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>['Total common shares outstanding of Makers Laboratories Ltd – NSE:MAKERSL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>KIRLPNU</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Kirloskar Pneumatic Company Limited</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>1533.3</v>
+      </c>
+      <c r="F114" t="n">
+        <v>1550</v>
+      </c>
+      <c r="G114" t="n">
+        <v>1552</v>
+      </c>
+      <c r="H114" t="n">
+        <v>1514.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>1524.7</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1533.3</v>
+      </c>
+      <c r="K114" t="n">
+        <v>112018</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>BRIGHTBR</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Bright Brothers Limited</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="F115" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="G115" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="H115" t="n">
+        <v>210</v>
+      </c>
+      <c r="I115" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="J115" t="n">
+        <v>240.7</v>
+      </c>
+      <c r="K115" t="n">
+        <v>2713</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Bright Brothers net profit rises 18.6% in Q1FY26 on revenue surge - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>['Bright Brothers net profit rises 18.6% in Q1FY26 on revenue surge - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OPTIFIN</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Optimus Finance Limited</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="F116" t="n">
+        <v>11.98</v>
+      </c>
+      <c r="G116" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="H116" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="I116" t="n">
+        <v>11.85</v>
+      </c>
+      <c r="J116" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="K116" t="n">
+        <v>16464</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Optimus Finance Ltd Dividends – NSE:OPTIFIN - TradingView</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>['Optimus Finance Ltd Dividends – NSE:OPTIFIN - TradingView']</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TGBHOTELS</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>TGB Banquets And Hotels Limited</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="F117" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="G117" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="H117" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="I117" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K117" t="n">
+        <v>28287</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>LASA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Lasa Supergenerics Limited</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="F118" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="G118" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="H118" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="I118" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="J118" t="n">
+        <v>7.37</v>
+      </c>
+      <c r="K118" t="n">
+        <v>26290</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Call for proposals for the LASA2027 Congress - clacso.org</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>['Call for proposals for the LASA2027 Congress - clacso.org', 'Bastrop vs Liberal Arts and Science Academy (LASA) Football - Nov 5, 2026 - Sports Illustrated', 'Priti International standalone net profit declines 53.85% in the June 2026 quarter - Business Standard', "Cricket match squads | GER vs ISR, 9th Match, ICC Men's T20 World Cup Sub Regional Europe Qualifier C 2026 - Cricbuzz", "Cricket match squads | CZE vs ISR, 15th Match, ICC Men's T20 World Cup Sub Regional Europe Qualifier C 2026 - Cricbuzz"]</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>MKEXIM</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>M.K. Exim (India) Limited</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="F119" t="n">
+        <v>58.65</v>
+      </c>
+      <c r="G119" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="H119" t="n">
+        <v>45.7</v>
+      </c>
+      <c r="I119" t="n">
+        <v>56.12</v>
+      </c>
+      <c r="J119" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="K119" t="n">
+        <v>2523</v>
+      </c>
+      <c r="L119" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>EBIX</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>EBIX Limited</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="F120" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="G120" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H120" t="n">
+        <v>16.14</v>
+      </c>
+      <c r="I120" t="n">
+        <v>16.98</v>
+      </c>
+      <c r="J120" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="K120" t="n">
+        <v>32196</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-1.41</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Half Yearly Results, Half yearly Earnings for Justride Enterprises - The Economic Times</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>['Half Yearly Results, Half yearly Earnings for Justride Enterprises - The Economic Times', 'Enterprise value to revenue forward of Ebix, Inc. – LS:765778 - TradingView', 'Delhi High Court enforces foreign arbitral award worth over ₹104 crore against Ebix Cash - The News Mill', 'EBIX Travels Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs']</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AMBICAAGAR</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Ambica Agarbathies &amp; Aroma industries Limited</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="F121" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="G121" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="H121" t="n">
+        <v>23.2</v>
+      </c>
+      <c r="I121" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="J121" t="n">
+        <v>24.47</v>
+      </c>
+      <c r="K121" t="n">
+        <v>16928</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O101"/>
+  <autoFilter ref="A1:O121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6541,7 +7723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11753,7 +12935,6 @@
       <c r="L87" t="n">
         <v>-8.17</v>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11993,7 +13174,6 @@
       <c r="L91" t="n">
         <v>-9.34</v>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12050,7 +13230,6 @@
       <c r="L92" t="n">
         <v>-9.99</v>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12107,7 +13286,6 @@
       <c r="L93" t="n">
         <v>-9.99</v>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12607,8 +13785,1220 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SHERVANI</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>337</v>
+      </c>
+      <c r="F102" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="G102" t="n">
+        <v>352</v>
+      </c>
+      <c r="H102" t="n">
+        <v>300.05</v>
+      </c>
+      <c r="I102" t="n">
+        <v>294</v>
+      </c>
+      <c r="J102" t="n">
+        <v>337</v>
+      </c>
+      <c r="K102" t="n">
+        <v>226</v>
+      </c>
+      <c r="L102" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>['Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard', 'Shervani Industrial Syndicate posts profit; appoints new Executive Director - Whalesbook', 'Delhi High Court Orders Meta To Takedown AI Videos Linking Former Union Minister Saleem Iqbal Shervani To ... - Live Law', 'Return on assets % of Shervani Industrial Syndicate Limited – NSE:SHERVANI - TradingView', 'Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>LAXMIINDIA</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Laxmi India Finance Limited</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="F103" t="n">
+        <v>124.9</v>
+      </c>
+      <c r="G103" t="n">
+        <v>138.9</v>
+      </c>
+      <c r="H103" t="n">
+        <v>124.51</v>
+      </c>
+      <c r="I103" t="n">
+        <v>124.38</v>
+      </c>
+      <c r="J103" t="n">
+        <v>132.3</v>
+      </c>
+      <c r="K103" t="n">
+        <v>634526</v>
+      </c>
+      <c r="L103" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>LAXMI INDIA FINANCE LTD Share Price News and Price Action - Univest</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>['LAXMI INDIA FINANCE LTD Share Price News and Price Action - Univest', 'Laxmi India Finance Share: லாபம் **70%** உயர்வு! முதலீட்டாளர்கள் கவனிக்க வேண்டியவை - Whalesbook', 'Laxmi India Finance posts 70% YoY PAT growth to Rs 16.4 crore in Q1 FY27 - Whalesbook', 'Laxmi India Finance: तिमाहीत नफ्यात **70%** वाढ, AUM मध्ये **28%** ची भरारी! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>DCI</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Dc Infotech And Communication Limited</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="F104" t="n">
+        <v>360</v>
+      </c>
+      <c r="G104" t="n">
+        <v>396.55</v>
+      </c>
+      <c r="H104" t="n">
+        <v>339.55</v>
+      </c>
+      <c r="I104" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="J104" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="K104" t="n">
+        <v>108521</v>
+      </c>
+      <c r="L104" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>Indonesian Stocks Near Bull Market as DCI Indonesia Profit Jumps 19% - CryptoRank</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>['Indonesian Stocks Near Bull Market as DCI Indonesia Profit Jumps 19% - CryptoRank', 'Donaldson Company Inc (DCI) Earnings Forecast: Future EPS &amp; Revenue Growth Estimates - tradingkey.com', 'Donaldson Company, Inc. to Issue Quarterly Dividend of $0.32 (NYSE:DCI) - MarketBeat', '64,958 Shares in Donaldson Company, Inc. $DCI Bought by SFE Investment Counsel - MarketBeat', 'Ribbon’s CEO says DCI is one of the most encouraging growth opportunities - Lightwave Online']</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>DCMFINSERV</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F105" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="G105" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="H105" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="J105" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="K105" t="n">
+        <v>8717</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>['DCM Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>ARTNIRMAN</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Art Nirman Limited</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="F106" t="n">
+        <v>41.27</v>
+      </c>
+      <c r="G106" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="H106" t="n">
+        <v>41.11</v>
+      </c>
+      <c r="I106" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="J106" t="n">
+        <v>41.16</v>
+      </c>
+      <c r="K106" t="n">
+        <v>507</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ALFREDHE</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Alfred Herbert India Limited</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3005</v>
+      </c>
+      <c r="F107" t="n">
+        <v>3599</v>
+      </c>
+      <c r="G107" t="n">
+        <v>3599</v>
+      </c>
+      <c r="H107" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I107" t="n">
+        <v>2999.8</v>
+      </c>
+      <c r="J107" t="n">
+        <v>3005</v>
+      </c>
+      <c r="K107" t="n">
+        <v>17</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>Alfred Herbert (India) Ltd. Dividends – NSE:ALFREDHE - TradingView</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>['Alfred Herbert (India) Ltd. Dividends – NSE:ALFREDHE - TradingView', 'Total common shares outstanding of Alfred Herbert (India) Ltd. – NSE:ALFREDHE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GTECJAINX</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>G-TEC JAINX EDUCATION LIMITED</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>29</v>
+      </c>
+      <c r="F108" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="G108" t="n">
+        <v>30.43</v>
+      </c>
+      <c r="H108" t="n">
+        <v>27.73</v>
+      </c>
+      <c r="I108" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="J108" t="n">
+        <v>29</v>
+      </c>
+      <c r="K108" t="n">
+        <v>20348</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>MERCANTILE</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Mercantile Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="F109" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="G109" t="n">
+        <v>24.99</v>
+      </c>
+      <c r="H109" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="I109" t="n">
+        <v>24.07</v>
+      </c>
+      <c r="J109" t="n">
+        <v>24.01</v>
+      </c>
+      <c r="K109" t="n">
+        <v>4104</v>
+      </c>
+      <c r="L109" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>Mercantile Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>['Mercantile Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Avon Mercantile Q1 Results: Net profit rises 45% YoY to ₹26.10 lakh - scanx.trade', 'Bangladesh Bank, Mercantile Bank sign agri-development refinancing agreement - The Business Standard', 'BB, MERCANTILE BANK SIGN AGRIDEVELOPMENT REFINANCING deal - The Financial Express', 'Sobhagya Mercantile Q1FY27 revenue falls 21% to ₹414 crore - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>RMDRIP</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>R M Drip and Sprinklers Systems Limited</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F110" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="G110" t="n">
+        <v>18</v>
+      </c>
+      <c r="H110" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="I110" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="J110" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1839666</v>
+      </c>
+      <c r="L110" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>R M Drip and Sprinklers Systems Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>['R M Drip and Sprinklers Systems Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SINTERCOM</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>81</v>
+      </c>
+      <c r="F111" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="G111" t="n">
+        <v>84.09999999999999</v>
+      </c>
+      <c r="H111" t="n">
+        <v>78.01000000000001</v>
+      </c>
+      <c r="I111" t="n">
+        <v>82.45999999999999</v>
+      </c>
+      <c r="J111" t="n">
+        <v>81</v>
+      </c>
+      <c r="K111" t="n">
+        <v>2322</v>
+      </c>
+      <c r="L111" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>['Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard', 'Axita Cotton standalone net profit rises 122.98% in the June 2026 quarter - Business Standard', 'Parvati Sweetners and Power reports standalone net profit of Rs 0.32 crore in the June 2026 quarter - Business Standard', 'Bliss GVS Pharma consolidated net profit rises 16.40% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>ASHIKAG</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Ashika Global Securities Limited</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>435</v>
+      </c>
+      <c r="F112" t="n">
+        <v>447.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>450</v>
+      </c>
+      <c r="H112" t="n">
+        <v>426</v>
+      </c>
+      <c r="I112" t="n">
+        <v>443.2</v>
+      </c>
+      <c r="J112" t="n">
+        <v>435</v>
+      </c>
+      <c r="K112" t="n">
+        <v>17233</v>
+      </c>
+      <c r="L112" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>Ashika Global Securities Limited Reports Record Quarterly Performance for Q1 2027 - The Tribune</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>['Ashika Global Securities Limited Reports Record Quarterly Performance for Q1 2027 - The Tribune']</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>DJML</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DJ Mediaprint &amp; Logistics Limited</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="F113" t="n">
+        <v>114</v>
+      </c>
+      <c r="G113" t="n">
+        <v>114</v>
+      </c>
+      <c r="H113" t="n">
+        <v>104.25</v>
+      </c>
+      <c r="I113" t="n">
+        <v>106.78</v>
+      </c>
+      <c r="J113" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="K113" t="n">
+        <v>231759</v>
+      </c>
+      <c r="L113" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>DJ Mediaprint &amp; Logistics Ltd. (DJML) Share Price Falls by 8.38% - Univest</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>['DJ Mediaprint &amp; Logistics Ltd. (DJML) Share Price Falls by 8.38% - Univest']</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PANORAMA</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Panorama Studios International Limited</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="F114" t="n">
+        <v>49</v>
+      </c>
+      <c r="G114" t="n">
+        <v>51</v>
+      </c>
+      <c r="H114" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="I114" t="n">
+        <v>47.46</v>
+      </c>
+      <c r="J114" t="n">
+        <v>45.94</v>
+      </c>
+      <c r="K114" t="n">
+        <v>126785</v>
+      </c>
+      <c r="L114" t="n">
+        <v>-3.2</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>After tax other income/expense of Panorama Studios International Ltd – NSE:PANORAMA - TradingView</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>['After tax other income/expense of Panorama Studios International Ltd – NSE:PANORAMA - TradingView', 'Moneycontrol Pro Panorama | Growth ignored - Moneycontrol.com', 'BBC seeks subpoenas for Trump family members in Panorama lawsuit - The Business Standard', 'Moneycontrol Pro Panorama | The Bombay House boardroom tussle - Moneycontrol.com', 'Panorama Auto Trust 2023-3 Class A Notes Interest Rate Set at 5.7625% p.a. - Kalkine']</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>The Indian Wood Products Company Limited</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="F115" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="G115" t="n">
+        <v>36.39</v>
+      </c>
+      <c r="H115" t="n">
+        <v>33.31</v>
+      </c>
+      <c r="I115" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="J115" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="K115" t="n">
+        <v>4475</v>
+      </c>
+      <c r="L115" t="n">
+        <v>-3.29</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>Responsive Playbooks and the IWP Inflection - news.stocktradersdaily.com</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>['Responsive Playbooks and the IWP Inflection - news.stocktradersdaily.com', 'Should iShares Russell Mid-Cap Growth ETF (IWP) Be on Your Investing Radar? - Yahoo Finance', 'iwp-barbara-duffield - The Imprint', 'The IWP Internship Experience: Rogen Mclean - The Institute of World Politics', 'The IWP Internship Experience: Isabel Leong - The Institute of World Politics']</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SONAL</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Sonal Mercantile Limited</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="F116" t="n">
+        <v>94</v>
+      </c>
+      <c r="G116" t="n">
+        <v>94</v>
+      </c>
+      <c r="H116" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="I116" t="n">
+        <v>90.98</v>
+      </c>
+      <c r="J116" t="n">
+        <v>87.15000000000001</v>
+      </c>
+      <c r="K116" t="n">
+        <v>14</v>
+      </c>
+      <c r="L116" t="n">
+        <v>-4.21</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>Sonal Mercantile Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>['Sonal Mercantile Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Sonal Adhesives Q1 Results: Net loss narrows 58% QoQ to ₹2.42 lakh - scanx.trade', 'Sonal Adhesives standalone net profit declines 48.89% in the June 2026 quarter - Business Standard', "Niroshan Dickwella and Sonal Dinusha resisted India's attack - Cricinfo", 'India Ahead Despite Sonal’s Century - Revsportz']</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SIKKO</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Sikko Industries Limited</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F117" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="G117" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="H117" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="I117" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="J117" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K117" t="n">
+        <v>515265</v>
+      </c>
+      <c r="L117" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Sikko Industries (NSE:SIKKO) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>['Sikko Industries (NSE:SIKKO) Ticks All The Boxes When It Comes To Earnings Growth - simplywall.st', 'Sikko Industries Ltd. Share Price Rise: NSE Stock Analysis - Univest', 'Sikko Industries Ltd Locks at Lower Circuit With 4.9% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', '#aadivasisong | Aadivasi No Sikko | Arjun R Meda | 9 August Aadivasi Divas Song | #aadhavarjuna Provincial Life Satisfaction Canada (rYOss5lvOd) - Mshale', 'Midwest consolidated net profit rises 26.67% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>BPLPHARMA</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Bharat Parenterals Limited</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1260.1</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1400</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1619</v>
+      </c>
+      <c r="H118" t="n">
+        <v>1125.7</v>
+      </c>
+      <c r="I118" t="n">
+        <v>1349.5</v>
+      </c>
+      <c r="J118" t="n">
+        <v>1260.1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>27</v>
+      </c>
+      <c r="L118" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Free float of Bharat Parenterals Ltd. – NSE:BPLPHARMA - TradingView</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>['Free float of Bharat Parenterals Ltd. – NSE:BPLPHARMA - TradingView', 'Bharat Parenterals Ltd. Share Price: 52-Week High Focus - Univest', 'Bharat Parenter Consolidated June 2026 Net Sales at Rs 93.74 crore, down 19.19% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="F119" t="n">
+        <v>56.83</v>
+      </c>
+      <c r="G119" t="n">
+        <v>59</v>
+      </c>
+      <c r="H119" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="I119" t="n">
+        <v>57</v>
+      </c>
+      <c r="J119" t="n">
+        <v>51.01</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1308</v>
+      </c>
+      <c r="L119" t="n">
+        <v>-10.51</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>['KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>PRISMX</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Prismx Global Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K120" t="n">
+        <v>922092</v>
+      </c>
+      <c r="L120" t="n">
+        <v>-13.79</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>Prismx Global Ventures consolidated net profit declines 75.17% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>['Prismx Global Ventures consolidated net profit declines 75.17% in the June 2026 quarter - Business Standard', 'Prismx Global Ventures Q1 net profit falls 75% to ₹37.36 lakhs - scanx.trade', 'Price to sales forward of Prismx Global Ventures Ltd. – BSE:PRISMX - TradingView', 'Prismx Global Standalone June 2026 Net Sales at Rs 0.23 crore, down 95.83% Y-o-Y - Moneycontrol.com', 'Greenlam Industries reports consolidated net profit of Rs 21.31 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-18 09:14:57 IST</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>295</v>
+      </c>
+      <c r="F121" t="n">
+        <v>326.95</v>
+      </c>
+      <c r="G121" t="n">
+        <v>335.2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>293.35</v>
+      </c>
+      <c r="I121" t="n">
+        <v>346.9</v>
+      </c>
+      <c r="J121" t="n">
+        <v>295</v>
+      </c>
+      <c r="K121" t="n">
+        <v>335204</v>
+      </c>
+      <c r="L121" t="n">
+        <v>-14.96</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>['Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks', 'Thomas Scott India releases Q1 FY27 earnings call audio recording - scanx.trade', 'Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks', 'Thomas Scott (India) Reports Q1 Revenue Of ₹65.8 Crore, Net Profit At ₹5.4 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O101"/>
+  <autoFilter ref="A1:O121"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$121</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$121</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$141</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6572,7 +6572,6 @@
       <c r="L102" t="n">
         <v>8.24</v>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6629,7 +6628,6 @@
       <c r="L103" t="n">
         <v>6.99</v>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6779,7 +6777,6 @@
           <t>QUINTEGRA</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
       <c r="E106" t="n">
         <v>1.39</v>
       </c>
@@ -6987,7 +6984,6 @@
       <c r="L109" t="n">
         <v>2.82</v>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7166,7 +7162,6 @@
       <c r="L112" t="n">
         <v>1.68</v>
       </c>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7284,7 +7279,6 @@
       <c r="L114" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7463,7 +7457,6 @@
       <c r="L117" t="n">
         <v>-0.52</v>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7581,7 +7574,6 @@
       <c r="L119" t="n">
         <v>-1.19</v>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7699,7 +7691,6 @@
       <c r="L121" t="n">
         <v>-1.85</v>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7711,8 +7702,1224 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="F122" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="G122" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="H122" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="I122" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="J122" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="K122" t="n">
+        <v>4545</v>
+      </c>
+      <c r="L122" t="n">
+        <v>20</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>['Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard', 'SBEC Systems (India) consolidated net profit declines 13.64% in the June 2026 quarter - Business Standard', 'Parnax Lab consolidated net profit declines 86.85% in the June 2026 quarter - Business Standard', 'Amrapali Industries consolidated net profit rises 930.56% in the June 2026 quarter - Business Standard', 'Fedders Holding consolidated net profit declines 34.26% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SUPTANERY</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Super Tannery Limited</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="G123" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H123" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="I123" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="J123" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="K123" t="n">
+        <v>578158</v>
+      </c>
+      <c r="L123" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Super Tannery Ltd. Income Statement – NSE:SUPTANERY - TradingView</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>['Super Tannery Ltd. Income Statement – NSE:SUPTANERY - TradingView', 'Super Tannery Ltd. Statistics – NSE:SUPTANERY - TradingView', 'Non-controlling/minority interest of Super Tannery Ltd. – NSE:SUPTANERY - TradingView']</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>SUBEXLTD</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Subex Limited</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="F124" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="G124" t="n">
+        <v>16.93</v>
+      </c>
+      <c r="H124" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="I124" t="n">
+        <v>14.11</v>
+      </c>
+      <c r="J124" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="K124" t="n">
+        <v>44677415</v>
+      </c>
+      <c r="L124" t="n">
+        <v>16.87</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Subex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>['Subex Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Subex Ltd. Share Price Gain: Price Action and Valuation - Univest']</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Prabha Energy Limited</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>189</v>
+      </c>
+      <c r="F125" t="n">
+        <v>164.31</v>
+      </c>
+      <c r="G125" t="n">
+        <v>196.05</v>
+      </c>
+      <c r="H125" t="n">
+        <v>163</v>
+      </c>
+      <c r="I125" t="n">
+        <v>163.38</v>
+      </c>
+      <c r="J125" t="n">
+        <v>189</v>
+      </c>
+      <c r="K125" t="n">
+        <v>5359104</v>
+      </c>
+      <c r="L125" t="n">
+        <v>15.68</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Prabha Energy Turns Profitable, Proposes Rs 150 Crore QIP - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>['Prabha Energy Turns Profitable, Proposes Rs 150 Crore QIP - Whalesbook', 'PRABHA ENERGY Share Price Gain: Technicals and Valuation - Univest', 'Prabha Dhakal: From Nurse to Parliamentarian, Discusses Governance and Public Welfare - Ratopati', 'Nritya Prabha Season 4 Set to Bring 446 Dancers to Faridabad - Hindustan Metro', 'Prabha Energy Consolidated June 2026 Net Sales at Rs 1.69 crore, up 49.32% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>HINDADH</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Hindustan Adhesives Limited</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="F126" t="n">
+        <v>372.9</v>
+      </c>
+      <c r="G126" t="n">
+        <v>402.65</v>
+      </c>
+      <c r="H126" t="n">
+        <v>361</v>
+      </c>
+      <c r="I126" t="n">
+        <v>335.55</v>
+      </c>
+      <c r="J126" t="n">
+        <v>384.1</v>
+      </c>
+      <c r="K126" t="n">
+        <v>246790</v>
+      </c>
+      <c r="L126" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>Hindustan Adhesives Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>['Hindustan Adhesives Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Return on assets % of Hindustan Adhesives Limited – NSE:HINDADH - TradingView', 'Hindustan Adhesives Limited Statistics – NSE:HINDADH - TradingView', '20% Upper Circuit: Stock Skyrockets After Reporting 1,044% QoQ Net Profit Growth in Q1 - Trade Brains']</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AARNAV</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Limited</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="F127" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="G127" t="n">
+        <v>36.04</v>
+      </c>
+      <c r="H127" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="I127" t="n">
+        <v>31.23</v>
+      </c>
+      <c r="J127" t="n">
+        <v>35.74</v>
+      </c>
+      <c r="K127" t="n">
+        <v>220800</v>
+      </c>
+      <c r="L127" t="n">
+        <v>14.44</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Aarnav Fashions Share Price News: Technicals, Valuation - Univest</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>['Aarnav Fashions Share Price News: Technicals, Valuation - Univest']</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Yasho Industries Limited</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4949</v>
+      </c>
+      <c r="F128" t="n">
+        <v>4400</v>
+      </c>
+      <c r="G128" t="n">
+        <v>4994</v>
+      </c>
+      <c r="H128" t="n">
+        <v>4399.9</v>
+      </c>
+      <c r="I128" t="n">
+        <v>4362.3</v>
+      </c>
+      <c r="J128" t="n">
+        <v>4949</v>
+      </c>
+      <c r="K128" t="n">
+        <v>240192</v>
+      </c>
+      <c r="L128" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Yasho Industries posts Q1 FY27 earnings call transcript for investors - TipRanks</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>['Yasho Industries posts Q1 FY27 earnings call transcript for investors - TipRanks', 'After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express', 'Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com', 'Yasho Ind. Consolidated June 2026 Net Sales at Rs 307.74 crore, up 54.93% Y-o-Y - Moneycontrol.com', 'Yasho Ind. Standalone June 2026 Net Sales at Rs 314.09 crore, up 58.73% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>ABINFRA</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>A B Infrabuild Limited</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="F129" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="G129" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="H129" t="n">
+        <v>10.98</v>
+      </c>
+      <c r="I129" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="J129" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="K129" t="n">
+        <v>25170295</v>
+      </c>
+      <c r="L129" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>GENESYS-RE</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Limited-RE</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>122</v>
+      </c>
+      <c r="F130" t="n">
+        <v>109</v>
+      </c>
+      <c r="G130" t="n">
+        <v>128</v>
+      </c>
+      <c r="H130" t="n">
+        <v>108</v>
+      </c>
+      <c r="I130" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="J130" t="n">
+        <v>122</v>
+      </c>
+      <c r="K130" t="n">
+        <v>335699</v>
+      </c>
+      <c r="L130" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Genesys International Corporation Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>['Genesys International Corporation Ltd. Share Price Live Today - CNBC TV18']</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>ICIL</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Indo Count Industries Limited</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>435.9</v>
+      </c>
+      <c r="F131" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="G131" t="n">
+        <v>462</v>
+      </c>
+      <c r="H131" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="I131" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="J131" t="n">
+        <v>435.9</v>
+      </c>
+      <c r="K131" t="n">
+        <v>25217573</v>
+      </c>
+      <c r="L131" t="n">
+        <v>12.14</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Indo Count Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>['Indo Count Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Indo Count Industries Q1 Results: Earnings call scheduled for Aug 13 - scanx.trade', 'Bharti Airtel Q1 Results: Net profit jumps 35% YoY to ₹10,012 crore - scanx.trade', 'Indo Count Industries Q1 Results: Audio of investor call uploaded - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>350</v>
+      </c>
+      <c r="F132" t="n">
+        <v>317.95</v>
+      </c>
+      <c r="G132" t="n">
+        <v>351.3</v>
+      </c>
+      <c r="H132" t="n">
+        <v>316.9</v>
+      </c>
+      <c r="I132" t="n">
+        <v>313.02</v>
+      </c>
+      <c r="J132" t="n">
+        <v>350</v>
+      </c>
+      <c r="K132" t="n">
+        <v>5070310</v>
+      </c>
+      <c r="L132" t="n">
+        <v>11.81</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>['Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - Univest', 'Ind-Swift Labs releases Q1FY27 earnings call audio recording - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SIGACHI</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Limited</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="F133" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="G133" t="n">
+        <v>30.09</v>
+      </c>
+      <c r="H133" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="I133" t="n">
+        <v>26.35</v>
+      </c>
+      <c r="J133" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="K133" t="n">
+        <v>10361044</v>
+      </c>
+      <c r="L133" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>['Sigachi Industries Q1 Results: Net profit rebounds to ₹8.14 crore - scanx.trade', 'Sigachi Industries Q1 Results: Net profit turns positive to ₹814 lakh - scanx.trade', 'Sigachi Ind Q1 Results FY27: PAT Rs 8 Cr, Revenue Rs 121 crore - Univest', 'Sigachi posts Q1 FY 2026-27 earnings call audio on website - TipRanks', 'Sigachi Laboratories standalone net profit rises 0.92% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>MACPOWER</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Limited</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>1981.1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H134" t="n">
+        <v>1782.5</v>
+      </c>
+      <c r="I134" t="n">
+        <v>1781.4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1981.1</v>
+      </c>
+      <c r="K134" t="n">
+        <v>190829</v>
+      </c>
+      <c r="L134" t="n">
+        <v>11.21</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Macpower CNC Machines Ltd. Share Price News and Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>['Macpower CNC Machines Ltd. Share Price News and Analysis - Univest', 'Macpower CNC Machines Ltd is Rated Hold - MarketsMojo']</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>DHABRIYA</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Limited</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>560.1</v>
+      </c>
+      <c r="F135" t="n">
+        <v>509</v>
+      </c>
+      <c r="G135" t="n">
+        <v>586.9</v>
+      </c>
+      <c r="H135" t="n">
+        <v>499.2</v>
+      </c>
+      <c r="I135" t="n">
+        <v>504.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>560.1</v>
+      </c>
+      <c r="K135" t="n">
+        <v>122906</v>
+      </c>
+      <c r="L135" t="n">
+        <v>11.05</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>['Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade', 'Dhabriya Polywood consolidated net profit rises 35.47% in the June 2026 quarter - Business Standard', 'Dhabriya Polywood wins Rs 10.63 crore work order from Indian Company - scanx.trade', 'Dhabriya Polywood Q1FY27 PAT up 35% to ₹8.86 crore; EBITDA margin expands - scanx.trade', 'Dhabriya Polywood Ltd Hits All-Time High of Rs 545 as Momentum Builds Across Timeframes - MarketsMojo']</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>JINDRILL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Jindal Drilling And Industries Limited</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>648.85</v>
+      </c>
+      <c r="F136" t="n">
+        <v>587.1</v>
+      </c>
+      <c r="G136" t="n">
+        <v>673.55</v>
+      </c>
+      <c r="H136" t="n">
+        <v>587.1</v>
+      </c>
+      <c r="I136" t="n">
+        <v>586.2</v>
+      </c>
+      <c r="J136" t="n">
+        <v>648.85</v>
+      </c>
+      <c r="K136" t="n">
+        <v>17885822</v>
+      </c>
+      <c r="L136" t="n">
+        <v>10.69</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>Jindal Drilling &amp; Industries Ltd. (JINDRILL) Share Price Rises 8.82% in Today’s Move - Univest</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>['Jindal Drilling &amp; Industries Ltd. (JINDRILL) Share Price Rises 8.82% in Today’s Move - Univest']</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>REGAAL</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Regaal Resources Limited</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>100</v>
+      </c>
+      <c r="F137" t="n">
+        <v>90.28</v>
+      </c>
+      <c r="G137" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="H137" t="n">
+        <v>88.65000000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>90.45999999999999</v>
+      </c>
+      <c r="J137" t="n">
+        <v>100</v>
+      </c>
+      <c r="K137" t="n">
+        <v>2975990</v>
+      </c>
+      <c r="L137" t="n">
+        <v>10.55</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Regaal Resources Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>['Regaal Resources Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Regaal Resources Q1 Results: Earnings call audio uploaded for investors - scanx.trade', 'Regaal Resources posts 47% rise in Q1 profit on higher margins - Moneycontrol.com', 'REGAAL RESOURCES LIMITED Share Price: Price Rise Analysis - Univest', 'Regaal Resources Limited: क्षमता विस्तार आणि नफ्यात वाढ! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="F138" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="G138" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="H138" t="n">
+        <v>36.4</v>
+      </c>
+      <c r="I138" t="n">
+        <v>37.01</v>
+      </c>
+      <c r="J138" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="K138" t="n">
+        <v>3330020</v>
+      </c>
+      <c r="L138" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>PVP Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>['PVP Ventures Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'PVP Ventures share price rises on Q1 profit jump, revenue doubles - Business Upturn', 'PVP Ventures Q1 FY27 Results: Revenue grew to Rs 46 Cr, PAT new - Univest', 'PVP Ventures consolidated net profit rises 4065.52% in the June 2026 quarter - Business Standard', 'PVP Ventures Limited Announces Change in Designation of Dr. Ellen Jane Feehan as Chief Executive Officer - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DHOOTTRANS</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Dhoot Transmission Limited</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="F139" t="n">
+        <v>1170</v>
+      </c>
+      <c r="G139" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="H139" t="n">
+        <v>1165</v>
+      </c>
+      <c r="I139" t="n">
+        <v>1187.05</v>
+      </c>
+      <c r="J139" t="n">
+        <v>1305.75</v>
+      </c>
+      <c r="K139" t="n">
+        <v>9337722</v>
+      </c>
+      <c r="L139" t="n">
+        <v>10</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Diluted earnings per share (diluted EPS) of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>['Diluted earnings per share (diluted EPS) of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView', 'Basic earnings per share (basic EPS) of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView', 'Dhoot Transmission Limited Dividends – NSE:DHOOTTRANS - TradingView', 'EBITDA per share of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView', 'EBITDA margin % of Dhoot Transmission Limited – NSE:DHOOTTRANS - TradingView']</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>INDO-MIM Limited</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="F140" t="n">
+        <v>910</v>
+      </c>
+      <c r="G140" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="H140" t="n">
+        <v>905</v>
+      </c>
+      <c r="I140" t="n">
+        <v>866.15</v>
+      </c>
+      <c r="J140" t="n">
+        <v>952.75</v>
+      </c>
+      <c r="K140" t="n">
+        <v>10246021</v>
+      </c>
+      <c r="L140" t="n">
+        <v>10</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>['IndoMIM Share Price Today - Indo-MIM Ltd. Stock Price Live NSE/BSE - HDFC Sky', 'INDOMIM Share Price Today - Indo-MIM Stock Analysis - Equitypandit', 'INDOMIM Historical Data - Equitypandit', 'INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks', 'INDO-MIM Board Clears Quarterly Results, Governance Moves and ESOP Plan - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>PARAS</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Paras Defence and Space Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>1527.3</v>
+      </c>
+      <c r="F141" t="n">
+        <v>1385</v>
+      </c>
+      <c r="G141" t="n">
+        <v>1527.3</v>
+      </c>
+      <c r="H141" t="n">
+        <v>1384.7</v>
+      </c>
+      <c r="I141" t="n">
+        <v>1388.5</v>
+      </c>
+      <c r="J141" t="n">
+        <v>1527.3</v>
+      </c>
+      <c r="K141" t="n">
+        <v>5405217</v>
+      </c>
+      <c r="L141" t="n">
+        <v>10</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Paras Defence Q1 results: Net profit grows 40% YoY; board fixes record date for dividend payout - Upstox</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>['Paras Defence Q1 results: Net profit grows 40% YoY; board fixes record date for dividend payout - Upstox', 'Paras Defence Q1 Results: Defence tech firm posts 43% profit growth; shares fall - CNBC TV18', 'Five Stocks To Buy Today: HDFC Bank, Bharti Airtel, Paras Defence And More | August 18 - ndtvprofit.com', 'Paras Defence, Zen Tech, other defence shares rise up to 8% as MoD notifies sixth Positive Indigenisation... - Moneycontrol.com', 'Defence stocks fire up! Paras Defence, GRSE, other stocks jump up to 10% as govt notifies 6th indigenisati - The Economic Times']</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O121"/>
+  <autoFilter ref="A1:O141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7723,7 +8930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O121"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14074,7 +15281,6 @@
       <c r="L106" t="n">
         <v>0.22</v>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14192,7 +15398,6 @@
       <c r="L108" t="n">
         <v>0.03</v>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr">
         <is>
           <t>[]</t>
@@ -14997,8 +16202,1220 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>ASIANTNE</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="F122" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="G122" t="n">
+        <v>9.69</v>
+      </c>
+      <c r="H122" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="I122" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="J122" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="K122" t="n">
+        <v>3285</v>
+      </c>
+      <c r="L122" t="n">
+        <v>-6.37</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>['Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TARSONS</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Tarsons Products Limited</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>338</v>
+      </c>
+      <c r="F123" t="n">
+        <v>365</v>
+      </c>
+      <c r="G123" t="n">
+        <v>365</v>
+      </c>
+      <c r="H123" t="n">
+        <v>332</v>
+      </c>
+      <c r="I123" t="n">
+        <v>361.5</v>
+      </c>
+      <c r="J123" t="n">
+        <v>338</v>
+      </c>
+      <c r="K123" t="n">
+        <v>1199370</v>
+      </c>
+      <c r="L123" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>Tarsons Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>['Tarsons Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Tarsons Products Q1 Results: Earnings call audio uploaded - scanx.trade', 'Tarsons Products reports consolidated net loss of Rs 1.44 crore in the June 2026 quarter - Business Standard', 'Tarsons Products के नतीजे: रेवेन्यू में **21%** की बढ़त, पर मार्जिन पर दबाव जारी - Whalesbook', 'Tarsons Products: రెవెన్యూలో దూకుడు.. కానీ మార్జిన్లపై ఒత్తిడి.. పంచ్లా ప్లాంట్ ఆలస్యం! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AUSTENG</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Austin Engineering Company Limited</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="F124" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="G124" t="n">
+        <v>126.75</v>
+      </c>
+      <c r="H124" t="n">
+        <v>110</v>
+      </c>
+      <c r="I124" t="n">
+        <v>122.87</v>
+      </c>
+      <c r="J124" t="n">
+        <v>114.3</v>
+      </c>
+      <c r="K124" t="n">
+        <v>776</v>
+      </c>
+      <c r="L124" t="n">
+        <v>-6.97</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>Gross profit of Austin Engineering Co. Ltd. – NSE:AUSTENG - TradingView</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>['Gross profit of Austin Engineering Co. Ltd. – NSE:AUSTENG - TradingView']</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>GKB</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>GKB Ophthalmics Limited</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="F125" t="n">
+        <v>69</v>
+      </c>
+      <c r="G125" t="n">
+        <v>69</v>
+      </c>
+      <c r="H125" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="I125" t="n">
+        <v>65</v>
+      </c>
+      <c r="J125" t="n">
+        <v>60.46</v>
+      </c>
+      <c r="K125" t="n">
+        <v>1217</v>
+      </c>
+      <c r="L125" t="n">
+        <v>-6.98</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>GKB Ophthalmics Ltd.: Q1 FY27 Standalone Results Show ₹73.94 Lakh Loss - InvestyWise</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>['GKB Ophthalmics Ltd.: Q1 FY27 Standalone Results Show ₹73.94 Lakh Loss - InvestyWise', 'GKB Ophthalmics Q1 FY27: Consolidated Profit Rs 1.85 Cr, Standalone Loss Rs 0.50 Cr - Whalesbook', 'GKB Deep Clean delivers speed, simplicity and superior results - Turf Matters', 'GKB Ophthalmics reports consolidated net profit of Rs 1.01 crore in the June 2026 quarter - Business Standard', 'GKB Hockeyschule 2016 Dell Stock (0n7jspI2ri) - Mshale']</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>ODYCORP</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Odyssey Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="F126" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="G126" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="H126" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="I126" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="J126" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="K126" t="n">
+        <v>12996</v>
+      </c>
+      <c r="L126" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>PRAXIS</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Limited</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="F127" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="G127" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="I127" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="J127" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="K127" t="n">
+        <v>554400</v>
+      </c>
+      <c r="L127" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>Praxis Home Retail Share Price Today: Price Fall Analysis - Univest</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>['Praxis Home Retail Share Price Today: Price Fall Analysis - Univest', 'Praxis Precision Medicines stock hits 52-week high at 388.27 USD - Investing.com India', 'Raymond James raises Praxis Precision Medicines price target on pipeline outlook - Investing.com India', 'Praxis Precision price target raised to $945 from $765 at Raymond James - TipRanks', 'Hotelogix and Praxis Services partner to strengthen centralised reservations and revenue management for India’s midscale hotel chains - BW Hotelier']</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SVGLOBAL</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>133</v>
+      </c>
+      <c r="F128" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="G128" t="n">
+        <v>143.5</v>
+      </c>
+      <c r="H128" t="n">
+        <v>115.55</v>
+      </c>
+      <c r="I128" t="n">
+        <v>143.61</v>
+      </c>
+      <c r="J128" t="n">
+        <v>133</v>
+      </c>
+      <c r="K128" t="n">
+        <v>21</v>
+      </c>
+      <c r="L128" t="n">
+        <v>-7.39</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>['Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView', 'S V Global Mill Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>MLKFOOD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Milkfood Limited</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="F129" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="G129" t="n">
+        <v>85.90000000000001</v>
+      </c>
+      <c r="H129" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="I129" t="n">
+        <v>81.44</v>
+      </c>
+      <c r="J129" t="n">
+        <v>75.25</v>
+      </c>
+      <c r="K129" t="n">
+        <v>23394</v>
+      </c>
+      <c r="L129" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>Milkfood Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>['Milkfood Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Operating margin % of Milkfood Ltd. – NSE:MLKFOOD - TradingView', 'Non-controlling/minority interest of Milkfood Ltd. – NSE:MLKFOOD - TradingView']</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>THOMASCOTT</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Limited</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="F130" t="n">
+        <v>293</v>
+      </c>
+      <c r="G130" t="n">
+        <v>297.15</v>
+      </c>
+      <c r="H130" t="n">
+        <v>276</v>
+      </c>
+      <c r="I130" t="n">
+        <v>301.1</v>
+      </c>
+      <c r="J130" t="n">
+        <v>278.1</v>
+      </c>
+      <c r="K130" t="n">
+        <v>360674</v>
+      </c>
+      <c r="L130" t="n">
+        <v>-7.64</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>['Thomas Scott (India) Ltd. (THOMASCOTT) Share Price Falls 8.36% Today; Textile Micro Cap Among Top Decliners - Univest', 'Thomas Scott (India) Limited posts Q1 FY 2026-27 earnings call recording for investors - TipRanks', 'Thomas Scott India releases Q1 FY27 earnings call audio recording - scanx.trade', 'Thomas Scott (India) Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks', 'Thomas Scott (India) Reports Q1 Revenue Of ₹65.8 Crore, Net Profit At ₹5.4 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>KANPRPLA</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Limited</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>242.3</v>
+      </c>
+      <c r="F131" t="n">
+        <v>263</v>
+      </c>
+      <c r="G131" t="n">
+        <v>266.39</v>
+      </c>
+      <c r="H131" t="n">
+        <v>240.5</v>
+      </c>
+      <c r="I131" t="n">
+        <v>262.85</v>
+      </c>
+      <c r="J131" t="n">
+        <v>242.3</v>
+      </c>
+      <c r="K131" t="n">
+        <v>54440</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>Kanpur Plastipack Q1 Results: Net profit surges 112% YoY - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>['Kanpur Plastipack Q1 Results: Net profit surges 112% YoY - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>DCMSIL</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DCM Shriram International Limited</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="F132" t="n">
+        <v>74</v>
+      </c>
+      <c r="G132" t="n">
+        <v>75.48999999999999</v>
+      </c>
+      <c r="H132" t="n">
+        <v>67.16</v>
+      </c>
+      <c r="I132" t="n">
+        <v>74.26000000000001</v>
+      </c>
+      <c r="J132" t="n">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>208275</v>
+      </c>
+      <c r="L132" t="n">
+        <v>-7.89</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>['DCMSIL Share Price Today - DCM Shriram International Ltd. Stock Price Live NSE/BSE - Univest']</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>S&amp;SPOWER</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>S&amp;S Power Switchgears Limited</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="F133" t="n">
+        <v>296</v>
+      </c>
+      <c r="G133" t="n">
+        <v>296</v>
+      </c>
+      <c r="H133" t="n">
+        <v>270</v>
+      </c>
+      <c r="I133" t="n">
+        <v>297.7</v>
+      </c>
+      <c r="J133" t="n">
+        <v>274.05</v>
+      </c>
+      <c r="K133" t="n">
+        <v>10586</v>
+      </c>
+      <c r="L133" t="n">
+        <v>-7.94</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>JUBLCPL</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Jubilant Agri and Consumer Products Limited</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>2153</v>
+      </c>
+      <c r="F134" t="n">
+        <v>2362.4</v>
+      </c>
+      <c r="G134" t="n">
+        <v>2397.9</v>
+      </c>
+      <c r="H134" t="n">
+        <v>2142</v>
+      </c>
+      <c r="I134" t="n">
+        <v>2342.4</v>
+      </c>
+      <c r="J134" t="n">
+        <v>2153</v>
+      </c>
+      <c r="K134" t="n">
+        <v>16482</v>
+      </c>
+      <c r="L134" t="n">
+        <v>-8.09</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>Jubilant Agri and Consumer Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>['Jubilant Agri and Consumer Products Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Jubilant Agri and Consumer Products Reports Q1 Revenue of ₹520 Crore, Net Profit at ₹46.1 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>PANCHMAHQ</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Panchmahal Steel Limited</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>286.85</v>
+      </c>
+      <c r="F135" t="n">
+        <v>331</v>
+      </c>
+      <c r="G135" t="n">
+        <v>331</v>
+      </c>
+      <c r="H135" t="n">
+        <v>275</v>
+      </c>
+      <c r="I135" t="n">
+        <v>315</v>
+      </c>
+      <c r="J135" t="n">
+        <v>286.85</v>
+      </c>
+      <c r="K135" t="n">
+        <v>81</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-8.94</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>Cash flow from operating activities of Panchmahal Steel Ltd – NSE:PANCHMAHQ - TradingView</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>['Cash flow from operating activities of Panchmahal Steel Ltd – NSE:PANCHMAHQ - TradingView']</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AHLUCONT</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Ahluwalia Contracts (India) Limited</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>710</v>
+      </c>
+      <c r="F136" t="n">
+        <v>776</v>
+      </c>
+      <c r="G136" t="n">
+        <v>782.4</v>
+      </c>
+      <c r="H136" t="n">
+        <v>702.5</v>
+      </c>
+      <c r="I136" t="n">
+        <v>793.85</v>
+      </c>
+      <c r="J136" t="n">
+        <v>710</v>
+      </c>
+      <c r="K136" t="n">
+        <v>545925</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-10.56</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>AHLUCONT: Q1 FY27 saw strong revenue growth but sharp margin and profit decline due to cost pressures - TradingView</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>['AHLUCONT: Q1 FY27 saw strong revenue growth but sharp margin and profit decline due to cost pressures - TradingView', 'Ahluwalia Contracts Q1 Results: Net profit down 78% YoY to ₹114 lakh - scanx.trade', 'AHLUCONT: Q1 FY27 margins declined despite higher income, but order book growth remains robust - TradingView', 'AHLUCONT: PAT plunged 78% year-over-year as margins were hit by labor cost spikes and a disputed project billing - TradingView', 'Earnings call transcript: Ahluwalia Contracts posts Q1 FY27 miss as margins shrink - Investing.com']</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>HARDWYN</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Hardwyn India Limited</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="F137" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="G137" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="H137" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="I137" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="J137" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="K137" t="n">
+        <v>9633380</v>
+      </c>
+      <c r="L137" t="n">
+        <v>-12.51</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>['Hardwyn Q1 FY27 Results: Revenue fell to Rs 35 Cr, PAT -25% - Univest', 'Hardwyn India consolidated net profit declines 22.87% in the June 2026 quarter - Business Standard', 'Hardwyn India Reports Q1 Net Profit of ₹2.8 Crore on ₹34.6 Crore Revenue - Sahi', 'Hardwyn India net profit falls 22% to ₹28 million in Q1FY26 - scanx.trade', "Hardwyn India Ltd leads losers in 'B' group - Business Standard"]</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>NELCO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NELCO Limited</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>945</v>
+      </c>
+      <c r="F138" t="n">
+        <v>1092.3</v>
+      </c>
+      <c r="G138" t="n">
+        <v>1098</v>
+      </c>
+      <c r="H138" t="n">
+        <v>938.6</v>
+      </c>
+      <c r="I138" t="n">
+        <v>1081.5</v>
+      </c>
+      <c r="J138" t="n">
+        <v>945</v>
+      </c>
+      <c r="K138" t="n">
+        <v>2131064</v>
+      </c>
+      <c r="L138" t="n">
+        <v>-12.62</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>Stocks To Watch Today: Paytm, Manapurram Finance, PNB Housing Finance , Nelco And SPR Auto Tech - ndtvprofit.com</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>['Stocks To Watch Today: Paytm, Manapurram Finance, PNB Housing Finance , Nelco And SPR Auto Tech - ndtvprofit.com', 'Elveo Mobile announced that it has received funding from SES S.A., Nelco Limited - marketscreener.com', 'Nelco drops after $20 million investment in pre-revenue satellite firm - Business Standard', "Tata group's Nelco picks up minority stake in Elveo, invests $20 mn - Business Standard", 'Nelco invests $20 million in Lunar Holdco to expand satellite connectivity services - CNBC TV18']</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>KRISHIVAL</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Krishival Foods Limited</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="F139" t="n">
+        <v>403</v>
+      </c>
+      <c r="G139" t="n">
+        <v>403</v>
+      </c>
+      <c r="H139" t="n">
+        <v>350.6</v>
+      </c>
+      <c r="I139" t="n">
+        <v>408.3</v>
+      </c>
+      <c r="J139" t="n">
+        <v>355.5</v>
+      </c>
+      <c r="K139" t="n">
+        <v>170859</v>
+      </c>
+      <c r="L139" t="n">
+        <v>-12.93</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>Krishival Foods Q1 Results: Net profit rises 27% YoY to ₹560.29 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>['Krishival Foods Q1 Results: Net profit rises 27% YoY to ₹560.29 lakh - scanx.trade', 'Krishival Foods consolidated net profit rises 12.41% in the June 2026 quarter - Business Standard', 'Krishival Foods lists converted equity shares on NSE and BSE - scanx.trade', 'Krishival Foods Lists Newly Converted Equity Shares After Rights Issue - TipRanks', 'Krishival Foods Standalone June 2026 Net Sales at Rs 37.38 crore, up 9.79% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>SUMEDHA</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Sumedha Fiscal Services Limited</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>39</v>
+      </c>
+      <c r="F140" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="G140" t="n">
+        <v>45</v>
+      </c>
+      <c r="H140" t="n">
+        <v>36.6</v>
+      </c>
+      <c r="I140" t="n">
+        <v>45.01</v>
+      </c>
+      <c r="J140" t="n">
+        <v>39</v>
+      </c>
+      <c r="K140" t="n">
+        <v>6656</v>
+      </c>
+      <c r="L140" t="n">
+        <v>-13.35</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>Sumedha Fiscal publishes Q1FY26 results in newspapers, net profit rises 14% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>['Sumedha Fiscal publishes Q1FY26 results in newspapers, net profit rises 14% - scanx.trade', 'Sumedha Fiscal Services Q1 Results: లాభాల బాట పట్టిన కంపెనీ.. కానీ ఆదాయంలో తగ్గుదల! - Whalesbook', 'Sumedha Fiscal Services consolidated net profit rises 13.75% in the June 2026 quarter - Business Standard', 'Sumedha Fiscal Services Turns Profitable With ₹3.24 Crore Net Profit - Whalesbook', 'Sumedha Fiscal Standalone June 2026 Net Sales at Rs 22.24 crore, up 13.23% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-18 16:27:52 IST</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SHANTI-RE</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Limited-RE</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="F141" t="n">
+        <v>44</v>
+      </c>
+      <c r="G141" t="n">
+        <v>44</v>
+      </c>
+      <c r="H141" t="n">
+        <v>25.65</v>
+      </c>
+      <c r="I141" t="n">
+        <v>32.92</v>
+      </c>
+      <c r="J141" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="K141" t="n">
+        <v>178506</v>
+      </c>
+      <c r="L141" t="n">
+        <v>-15.52</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Shanti Gold International Ltd. Share Price Live Today - CNBC TV18</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>['Shanti Gold International Ltd. Share Price Live Today - CNBC TV18']</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O121"/>
+  <autoFilter ref="A1:O141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$161</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -8174,7 +8174,6 @@
       <c r="L129" t="n">
         <v>13.38</v>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8918,8 +8917,1216 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="F142" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G142" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="H142" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="I142" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="J142" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="K142" t="n">
+        <v>876</v>
+      </c>
+      <c r="L142" t="n">
+        <v>18.57</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>['Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView', 'Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard', 'SBEC Systems (India) consolidated net profit declines 13.64% in the June 2026 quarter - Business Standard', 'Parnax Lab consolidated net profit declines 86.85% in the June 2026 quarter - Business Standard', 'Amrapali Industries consolidated net profit rises 930.56% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>LEENEE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Lee &amp; Nee Softwares Exports Limited</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="F143" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H143" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="I143" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="J143" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="K143" t="n">
+        <v>598</v>
+      </c>
+      <c r="L143" t="n">
+        <v>14.78</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>Operating margin % of Lee &amp; Nee Softwares (Exports) Ltd – NSE:LEENEE - TradingView</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>['Operating margin % of Lee &amp; Nee Softwares (Exports) Ltd – NSE:LEENEE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>185.97</v>
+      </c>
+      <c r="F144" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="G144" t="n">
+        <v>190.94</v>
+      </c>
+      <c r="H144" t="n">
+        <v>183.29</v>
+      </c>
+      <c r="I144" t="n">
+        <v>165.88</v>
+      </c>
+      <c r="J144" t="n">
+        <v>185.97</v>
+      </c>
+      <c r="K144" t="n">
+        <v>2365683</v>
+      </c>
+      <c r="L144" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>['Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit', 'Zaggle Prepaid Q1 Results: Profit Slumps 57% As Margin Shrinks; Revenue Falls 32% - NDTV Profit', 'Zaggle Q1 profit falls 33% despite 28% revenue growth as acquisition costs weigh on margins - CNBC TV18', 'Why Are Zaggle Shares Down Today? Q1 Profit Falls 33% Despite 27.5% Revenue Growth; Dice Costs Hit Margins - Business Upturn', 'Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st']</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PANSARI</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Pansari Developers Limited</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>347</v>
+      </c>
+      <c r="F145" t="n">
+        <v>377</v>
+      </c>
+      <c r="G145" t="n">
+        <v>377</v>
+      </c>
+      <c r="H145" t="n">
+        <v>340</v>
+      </c>
+      <c r="I145" t="n">
+        <v>314.85</v>
+      </c>
+      <c r="J145" t="n">
+        <v>347</v>
+      </c>
+      <c r="K145" t="n">
+        <v>193</v>
+      </c>
+      <c r="L145" t="n">
+        <v>10.21</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Pansari Developers Share Price Target 2027 to 2030: Analyst Outlook - univest.in</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>['Pansari Developers Share Price Target 2027 to 2030: Analyst Outlook - univest.in', 'Price to sales forward of Pansari Developers Ltd. – NSE:PANSARI - TradingView', 'Monika Pansari: “She Matters” Strengthens the Focus on Women’s Cancer Prevention - Oncodaily', 'Pansari Developers Ltd is Rated Strong Sell - MarketsMojo', 'Spinaroo Commercial cites administrative oversight for delayed CS intimation - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="F146" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="G146" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="H146" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="I146" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="J146" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="K146" t="n">
+        <v>1610</v>
+      </c>
+      <c r="L146" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Return on equity % of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>['Return on equity % of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView', 'Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LKPSEC</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LKP Securities Limited</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="F147" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="G147" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="H147" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="I147" t="n">
+        <v>16.76</v>
+      </c>
+      <c r="J147" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="K147" t="n">
+        <v>3911</v>
+      </c>
+      <c r="L147" t="n">
+        <v>9.67</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>EBITDA margin % of LKP Securities Limited – NSE:LKPSEC - TradingView</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>['EBITDA margin % of LKP Securities Limited – NSE:LKPSEC - TradingView', 'LKP Securities shares permitted to trade on NSE from Aug 17 - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>CFEL</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Confidence Futuristic Energetech Limited</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="F148" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="G148" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="H148" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="I148" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="J148" t="n">
+        <v>31.63</v>
+      </c>
+      <c r="K148" t="n">
+        <v>1</v>
+      </c>
+      <c r="L148" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Equity in earnings of Confidence Futuristic Energetech Ltd. – NSE:CFEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>['Equity in earnings of Confidence Futuristic Energetech Ltd. – NSE:CFEL - TradingView', 'Confidence Futuristic Energetech Ltd. Statistics – NSE:CFEL - TradingView', 'Confidence Futuristic Energetech Q1 Results: Profit rises to ₹1.17 crore - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>MYSORPETRO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>125</v>
+      </c>
+      <c r="F149" t="n">
+        <v>116</v>
+      </c>
+      <c r="G149" t="n">
+        <v>125</v>
+      </c>
+      <c r="H149" t="n">
+        <v>116</v>
+      </c>
+      <c r="I149" t="n">
+        <v>114.93</v>
+      </c>
+      <c r="J149" t="n">
+        <v>125</v>
+      </c>
+      <c r="K149" t="n">
+        <v>1685</v>
+      </c>
+      <c r="L149" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>['Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView', 'Price to book ratio of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>196.88</v>
+      </c>
+      <c r="F150" t="n">
+        <v>190</v>
+      </c>
+      <c r="G150" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="H150" t="n">
+        <v>190</v>
+      </c>
+      <c r="I150" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="J150" t="n">
+        <v>196.88</v>
+      </c>
+      <c r="K150" t="n">
+        <v>9215095</v>
+      </c>
+      <c r="L150" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>['Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView', 'Basic earnings per share (basic EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView', 'Milky Mist Dairy Food Ltd. Earnings and Revenue – BSE:MILKYMIST - TradingView', 'Milky Mist Dairy Food Limited: Target Price Consensus and Analysts Recommendations | MILKYMIST | INE00IT01020 - marketscreener.com', 'EBITDA margin % of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView']</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>DUCON</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Limited</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="F151" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G151" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H151" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="I151" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="J151" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K151" t="n">
+        <v>162194</v>
+      </c>
+      <c r="L151" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Ducon Infratechnologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>['Ducon Infratechnologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Ducon Infratechnologies wins cooling system order for one of India’s largest aluminium smelters - CNBC TV18', "Ducon Infratechnologies wins contract with India's largest aluminium smelter - scanx.trade", 'Ducon Infratechnologies Wins Aluminium Smelter Order - Whalesbook', 'Ducon Infratechnologies Wins Forced Cooling Network Contract for Aluminium Plant - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>PAUSHAKLTD</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Paushak Limited</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>811.45</v>
+      </c>
+      <c r="F152" t="n">
+        <v>788</v>
+      </c>
+      <c r="G152" t="n">
+        <v>814.25</v>
+      </c>
+      <c r="H152" t="n">
+        <v>781.1</v>
+      </c>
+      <c r="I152" t="n">
+        <v>752.35</v>
+      </c>
+      <c r="J152" t="n">
+        <v>811.45</v>
+      </c>
+      <c r="K152" t="n">
+        <v>21753</v>
+      </c>
+      <c r="L152" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>SWARNSAR</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Swarnsarita Jewels India Limited</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="F153" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="G153" t="n">
+        <v>36.5</v>
+      </c>
+      <c r="H153" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="I153" t="n">
+        <v>33.98</v>
+      </c>
+      <c r="J153" t="n">
+        <v>36.49</v>
+      </c>
+      <c r="K153" t="n">
+        <v>435</v>
+      </c>
+      <c r="L153" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Book value per share of Swarnsarita Jewels India Limited – NSE:SWARNSAR - TradingView</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>['Book value per share of Swarnsarita Jewels India Limited – NSE:SWARNSAR - TradingView', 'Swarnsarita Jewels India Limited Income Statement – NSE:SWARNSAR - TradingView']</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>WILLAMAGOR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Williamson Magor &amp; Company Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F154" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="G154" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H154" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="I154" t="n">
+        <v>25.15</v>
+      </c>
+      <c r="J154" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K154" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" t="n">
+        <v>6.96</v>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>BBTCL</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>B&amp;B Triplewall Containers Limited</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>254.53</v>
+      </c>
+      <c r="F155" t="n">
+        <v>260</v>
+      </c>
+      <c r="G155" t="n">
+        <v>260</v>
+      </c>
+      <c r="H155" t="n">
+        <v>245.16</v>
+      </c>
+      <c r="I155" t="n">
+        <v>238.82</v>
+      </c>
+      <c r="J155" t="n">
+        <v>254.53</v>
+      </c>
+      <c r="K155" t="n">
+        <v>19893</v>
+      </c>
+      <c r="L155" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>B&amp;B Triplewall Containers Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>['B&amp;B Triplewall Containers Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'B&amp;B Triplewall Q1 Results: Plans 80% capacity expansion - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TPHQ</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I156" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J156" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K156" t="n">
+        <v>470247</v>
+      </c>
+      <c r="L156" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Teamo Productions HQ Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>['Teamo Productions HQ Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', '20% Upper Circuit: Stock Skyrockets After Reporting 811% YoY Increase in Net Profit - Trade Brains', 'Teamo Productions HQ Publishes Q1 FY27 Unaudited Results in Newspapers - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SELMC</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SEL Manufacturing Company Limited</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="F157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="G157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="I157" t="n">
+        <v>27.74</v>
+      </c>
+      <c r="J157" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="K157" t="n">
+        <v>10</v>
+      </c>
+      <c r="L157" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="F158" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="G158" t="n">
+        <v>110.6</v>
+      </c>
+      <c r="H158" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="I158" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="J158" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="K158" t="n">
+        <v>45863</v>
+      </c>
+      <c r="L158" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Indonesian Stocks Ease Ahead of BI Rate Decision - TradingView</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>['Indonesian Stocks Ease Ahead of BI Rate Decision - TradingView', 'Indonesia Stocks Slide 0.67% as Debt Concerns, BI Rate Outlook Weigh - Jakarta Globe', 'Three H-1B rejections later, an Indian techie secures O-1 ‘extraordinary ability’ Visa - livemint.com', 'Rupiah Softens as BI Policy Meeting Kicks Off - TradingView', 'Indonesian Rupiah holds weak footing ahead of looming BI policy decision - FXStreet']</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NGLFINE</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NGL Fine-Chem Limited</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>3203.8</v>
+      </c>
+      <c r="F159" t="n">
+        <v>3051.4</v>
+      </c>
+      <c r="G159" t="n">
+        <v>3206.6</v>
+      </c>
+      <c r="H159" t="n">
+        <v>3051.3</v>
+      </c>
+      <c r="I159" t="n">
+        <v>3023.5</v>
+      </c>
+      <c r="J159" t="n">
+        <v>3203.8</v>
+      </c>
+      <c r="K159" t="n">
+        <v>1062</v>
+      </c>
+      <c r="L159" t="n">
+        <v>5.96</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>NGL Fine Chem Q1 Results: Net profit up 99% YoY to ₹18.40 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>['NGL Fine Chem Q1 Results: Net profit up 99% YoY to ₹18.40 crore - scanx.trade', 'NGL Fine Chem Q1 Results: Net profit jumps 115% YoY to ₹1,645.13 lakh - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>RAILTEL</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Railtel Corporation Of India Limited</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>293.45</v>
+      </c>
+      <c r="F160" t="n">
+        <v>282.65</v>
+      </c>
+      <c r="G160" t="n">
+        <v>294.8</v>
+      </c>
+      <c r="H160" t="n">
+        <v>282.35</v>
+      </c>
+      <c r="I160" t="n">
+        <v>277.15</v>
+      </c>
+      <c r="J160" t="n">
+        <v>293.45</v>
+      </c>
+      <c r="K160" t="n">
+        <v>417563</v>
+      </c>
+      <c r="L160" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>RailTel shares in focus after ₹166.8-cr work order from EPFO - Moneycontrol.com</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>['RailTel shares in focus after ₹166.8-cr work order from EPFO - Moneycontrol.com', 'Stocks to watch: BPCL, RailTel, ONGC among shares in focus today; check list here - livemint.com', 'Stocks in news: ONGC, BPCL, RailTel Corporation, Exide Industries and Lohia Corp - The Economic Times', 'Stocks to watch: Swiggy, Manipal Health, Biocon, RailTel, Sammaan Capital - Business Standard', 'Stocks to Watch Today: Aster DM Quality Care, Jubilant Ingrevia, HG Infra, Atlanta Electricals, RailTel... - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>BONLON</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Bonlon Industries Limited</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="F161" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="G161" t="n">
+        <v>44.4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>44.27</v>
+      </c>
+      <c r="I161" t="n">
+        <v>41.86</v>
+      </c>
+      <c r="J161" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="K161" t="n">
+        <v>126</v>
+      </c>
+      <c r="L161" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Bonlon Industries Q1 Results: Net profit up 75% YoY to ₹175.28 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>['Bonlon Industries Q1 Results: Net profit up 75% YoY to ₹175.28 lakh - scanx.trade', 'Bonlon Industries standalone net profit declines 50.98% in the June 2026 quarter - Business Standard', 'Bonlon Industries Approves Fund Raising Up To 497.5 Million Rupees Via Rights Issue Of Equity Shares - TradingView', 'Bonlon Industries sets Aug 20 meeting to fix rights issue price - scanx.trade', 'Bonlon Industries Rights Issue: ఆగష్టు 20న కీలక సమావేశం - రూ.49.75 కోట్ల నిధుల సేకరణపై స్పష్టత! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O141"/>
+  <autoFilter ref="A1:O161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8930,7 +10137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O141"/>
+  <dimension ref="A1:O161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16491,7 +17698,6 @@
       <c r="L126" t="n">
         <v>-7.13</v>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr">
         <is>
           <t>[]</t>
@@ -16914,7 +18120,6 @@
       <c r="L133" t="n">
         <v>-7.94</v>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr">
         <is>
           <t>[]</t>
@@ -17414,8 +18619,1220 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TREEHOUSE</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Tree House Education &amp; Accessories Limited</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="F142" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="G142" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="H142" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="I142" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="J142" t="n">
+        <v>6.02</v>
+      </c>
+      <c r="K142" t="n">
+        <v>4</v>
+      </c>
+      <c r="L142" t="n">
+        <v>-4.29</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>Tate + Co designs treehouse to replace Wandsworth roundabout billboard - The Architects’ Journal</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>['Tate + Co designs treehouse to replace Wandsworth roundabout billboard - The Architects’ Journal', 'This Treehouse Is the Perfect Upstate New York Getaway - Matador Network', 'In China, ‘Hacks’ Is Called ‘the Diva and the Strawberry,’ and Fans Built a Whole Sims World Where the Characters Live Together in a Treehouse - Thought Catalog', 'Treehouses to Splashzones, Kalahari Has it All - TMJ4 News', 'Treehouse Masters Trailers &amp; Videos - TVGuide.com']</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>GANGAFORGE</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F143" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="G143" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H143" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="I143" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J143" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="K143" t="n">
+        <v>75035</v>
+      </c>
+      <c r="L143" t="n">
+        <v>-4.64</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>ONELIFECAP</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Onelife Capital Advisors Limited</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="F144" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="G144" t="n">
+        <v>33.5</v>
+      </c>
+      <c r="H144" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="I144" t="n">
+        <v>33.79</v>
+      </c>
+      <c r="J144" t="n">
+        <v>32.21</v>
+      </c>
+      <c r="K144" t="n">
+        <v>3221</v>
+      </c>
+      <c r="L144" t="n">
+        <v>-4.68</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>Onelife Capital Advisors Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>['Onelife Capital Advisors Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Onelife Capital Advisors Q1 Results: Files Q1FY26 financials with exchanges - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PRABHA</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Prabha Energy Limited</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>183.09</v>
+      </c>
+      <c r="F145" t="n">
+        <v>183.1</v>
+      </c>
+      <c r="G145" t="n">
+        <v>184.45</v>
+      </c>
+      <c r="H145" t="n">
+        <v>181.11</v>
+      </c>
+      <c r="I145" t="n">
+        <v>192.2</v>
+      </c>
+      <c r="J145" t="n">
+        <v>183.09</v>
+      </c>
+      <c r="K145" t="n">
+        <v>45075</v>
+      </c>
+      <c r="L145" t="n">
+        <v>-4.74</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Prabha Energy Turns Profitable, Proposes Rs 150 Crore QIP - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>['Prabha Energy Turns Profitable, Proposes Rs 150 Crore QIP - Whalesbook', 'PRABHA ENERGY Share Price Gain: Technicals and Valuation - univest.in', 'Prabha Dhakal: From Nurse to Parliamentarian, Discusses Governance and Public Welfare - Hamro Patro', 'Nritya Prabha Season 4 Set to Bring 446 Dancers to Faridabad - Hindustan Metro', 'Prabha Energy Consolidated June 2026 Net Sales at Rs 1.69 crore, up 49.32% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>ARROWGREEN</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Arrow Greentech Limited</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="F146" t="n">
+        <v>693.75</v>
+      </c>
+      <c r="G146" t="n">
+        <v>708</v>
+      </c>
+      <c r="H146" t="n">
+        <v>693.75</v>
+      </c>
+      <c r="I146" t="n">
+        <v>730.25</v>
+      </c>
+      <c r="J146" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="K146" t="n">
+        <v>17107</v>
+      </c>
+      <c r="L146" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>Arrow Greentech Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>['Arrow Greentech Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Arrow Greentech Q1 Results: Net profit rises 151% YoY to ₹27.43 crore - scanx.trade', 'Arrow Greentech Clears Q1 FY27 Results, Sets AGM and Key Appointments - TipRanks', 'Arrow Greentech Q1FY27 PAT rises 151% to ₹274 million on revenue surge - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>NORBTEAEXP</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Norben Tea &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="F147" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="G147" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="H147" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="I147" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="J147" t="n">
+        <v>63.51</v>
+      </c>
+      <c r="K147" t="n">
+        <v>2</v>
+      </c>
+      <c r="L147" t="n">
+        <v>-4.81</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Norben Tea Q1 Results: Net profit rises 13% YoY to ₹32.3 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>['Norben Tea Q1 Results: Net profit rises 13% YoY to ₹32.3 lakh - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>ASIANTNE</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>9</v>
+      </c>
+      <c r="F148" t="n">
+        <v>9</v>
+      </c>
+      <c r="G148" t="n">
+        <v>9</v>
+      </c>
+      <c r="H148" t="n">
+        <v>9</v>
+      </c>
+      <c r="I148" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="J148" t="n">
+        <v>9</v>
+      </c>
+      <c r="K148" t="n">
+        <v>150</v>
+      </c>
+      <c r="L148" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>['Asian Tea &amp; Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Return on equity % of Asian Tea &amp; Exports Ltd. – NSE:ASIANTNE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BURNPUR</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Limited</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="F149" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="G149" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="H149" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="I149" t="n">
+        <v>16.54</v>
+      </c>
+      <c r="J149" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="K149" t="n">
+        <v>371</v>
+      </c>
+      <c r="L149" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Ltd Locks at Lower Circuit With 5.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>['Burnpur Cement Ltd Locks at Lower Circuit With 5.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', 'Burnpur Cement Ltd Locks at Lower Circuit With 4.97% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', 'BURNPUR Share Price | Burnpur Cement Ltd Stock Analysis &amp; Recommendation - MarketsMojo', 'Revenue per share of Burnpur Cement Limited – NSE:BURNPUR - TradingView', 'Burnpur Cement Ltd re-designates Pawan Pareek as Whole-Time Director - Whispers in the Corridors']</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>ABMINTLLTD</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>ABM International Limited</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="F150" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="G150" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="H150" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="I150" t="n">
+        <v>53.39</v>
+      </c>
+      <c r="J150" t="n">
+        <v>50.73</v>
+      </c>
+      <c r="K150" t="n">
+        <v>778</v>
+      </c>
+      <c r="L150" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>KOTYARK</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Kotyark Industries Limited</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="F151" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="G151" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="H151" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="I151" t="n">
+        <v>36.36</v>
+      </c>
+      <c r="J151" t="n">
+        <v>34.55</v>
+      </c>
+      <c r="K151" t="n">
+        <v>4630</v>
+      </c>
+      <c r="L151" t="n">
+        <v>-4.98</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>Kotyark Industries Results: ઓડિટર બદલાતા પરિણામો જાહેર કરવામાં વિલંબ, રોકાણકારોની ચિંતા વધી - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>['Kotyark Industries Results: ઓડિટર બદલાતા પરિણામો જાહેર કરવામાં વિલંબ, રોકાણકારોની ચિંતા વધી - Whalesbook', 'Three Days Left Until Kotyark Industries Limited (NSE:KOTYARK) Trades Ex-Dividend - simplywall.st', 'Kotyark Industries Ltd Locks at Lower Circuit With 4.99% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', 'Kotyark Industries receives orders for supply of 1,662 KL of biodiesel - Business Standard', 'Kotyark Industries Limited Receives Letters of Intent from Bharat Petroleum Corporation Limited and Hindustan Petroleum Corporation Limited for Supply of Biodiesel - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>AUTOIND</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Autoline Industries Limited</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="F152" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="G152" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="H152" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="I152" t="n">
+        <v>88.7</v>
+      </c>
+      <c r="J152" t="n">
+        <v>84.27</v>
+      </c>
+      <c r="K152" t="n">
+        <v>10684</v>
+      </c>
+      <c r="L152" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Autoline Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>['Autoline Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>INDOTHAI</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="F153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="G153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="H153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="I153" t="n">
+        <v>69.56999999999999</v>
+      </c>
+      <c r="J153" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="K153" t="n">
+        <v>3140</v>
+      </c>
+      <c r="L153" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - univest.in</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>['Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - univest.in', 'Indo Thai Securities schedules NCLT hearing for demerger scheme on September 24 - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="F154" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="G154" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="H154" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="I154" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="J154" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="K154" t="n">
+        <v>627</v>
+      </c>
+      <c r="L154" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>['ONIXSOLAR Share Price Today - Onix Solar Energy Stock Analysis - Equitypandit', 'Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView', 'Onix Solar Energy Ltd. Balance Sheet – NSE:ONIXSOLAR - TradingView', 'Onix Solar Energy Ltd. Income Statement – NSE:ONIXSOLAR - TradingView']</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>RSDFIN</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>RSD Finance Limited</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="F155" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="G155" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="H155" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="I155" t="n">
+        <v>101.17</v>
+      </c>
+      <c r="J155" t="n">
+        <v>96.12</v>
+      </c>
+      <c r="K155" t="n">
+        <v>197</v>
+      </c>
+      <c r="L155" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>RSD Finance Ltd. (RSDFIN) Share Price Rises 9.98% Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>['RSD Finance Ltd. (RSDFIN) Share Price Rises 9.98% Today - univest.in']</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>NATIONSTD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="F156" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="G156" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="H156" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="I156" t="n">
+        <v>134</v>
+      </c>
+      <c r="J156" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="K156" t="n">
+        <v>2838</v>
+      </c>
+      <c r="L156" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Price Band Hitters, August 18, 2026, 3:00 PM IST - HDFC Sky</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>['Price Band Hitters, August 18, 2026, 3:00 PM IST - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>UEL</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Limited</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="F157" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="G157" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="H157" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="I157" t="n">
+        <v>211.36</v>
+      </c>
+      <c r="J157" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="K157" t="n">
+        <v>853</v>
+      </c>
+      <c r="L157" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>UEL. Dynamo vs Universitatea Cluj 0:0 - Динамо» Київ. Офіційний сайт</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>['UEL. Dynamo vs Universitatea Cluj 0:0 - Динамо» Київ. Офіційний сайт', 'Explained: UCL, UEL, UECL Knockout Stages Format｜Champions League｜Europa League｜Conference League Giancarlo Stanton (D4OKPIo24k) - Mshale', 'UEFA EUROPA LEAGUE WINNERS || SC FREIBURG 0-3 ASTON VILLA || #UEL Rafael Jodar (WjSboSpk52) - Mshale', 'Marseille 0-3 Atletico Madrid Griezmann Magical Double Hands Side UEL Champions|FOOTBALL NEWS 2018 Bitcoin (713AaOk7pu) - Mshale', 'Son, Maddison &amp; Ange React After Spurs UEL Win! | Hoffenheim Vs Tottenham | Post-Match Interviews Beckett Sennecke (y6fizeNqNq) - Mshale']</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>UNIVASTU</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Univastu India Limited</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="F158" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="G158" t="n">
+        <v>173.35</v>
+      </c>
+      <c r="H158" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="I158" t="n">
+        <v>176.89</v>
+      </c>
+      <c r="J158" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="K158" t="n">
+        <v>13261</v>
+      </c>
+      <c r="L158" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Univastu India consolidated net profit rises 281.61% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>['Univastu India consolidated net profit rises 281.61% in the June 2026 quarter - Business Standard', 'Univastu India Consolidated June 2026 Net Sales at Rs 103.72 crore, up 252.69% Y-o-Y - Moneycontrol.com', 'Univastu India Standalone June 2026 Net Sales at Rs 99.94 crore, up 296.11% Y-o-Y - Moneycontrol.com', 'Univastu India Ltd Hits All-Time High of Rs 158 as Momentum Builds Across Timeframes - MarketsMojo', 'Aryan Share &amp; Stock Brokers standalone net profit declines 78.45% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>ASTERDM</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>769.9</v>
+      </c>
+      <c r="F159" t="n">
+        <v>779.9</v>
+      </c>
+      <c r="G159" t="n">
+        <v>780.05</v>
+      </c>
+      <c r="H159" t="n">
+        <v>766.1</v>
+      </c>
+      <c r="I159" t="n">
+        <v>818</v>
+      </c>
+      <c r="J159" t="n">
+        <v>769.9</v>
+      </c>
+      <c r="K159" t="n">
+        <v>60149122</v>
+      </c>
+      <c r="L159" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>['Aster DM Quality Care Limited (NSE:ASTERDM) Released Earnings Last Week And Analysts Lifted Their Price Target To ₹898 - simplywall.st', 'Aster DM Quality Care Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'ASTERDM: Q1 FY 2027 saw 20% revenue and 30% EBITDA growth, with strong synergy and expansion outlook - TradingView', 'Aster DM Quality Care targets 10-15% EBITDA synergy post-merger - scanx.trade', 'Aster DM Quality Care Reports Strong Q1 FY27: Revenue Up 20 Per Cent to Rs 2,597 Cr, Operating EBITDA Up 30 Per Cent - Big News Network.com']</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>MOHITE</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Mohite Industries Limited</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="F160" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="G160" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H160" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="I160" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J160" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="K160" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L160" t="n">
+        <v>-9.800000000000001</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>['Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade', 'Mohite Industries reports consolidated net loss of Rs 2.46 crore in the June 2026 quarter - Business Standard', 'Book value per share of Mohite Industries Ltd. – NSE:MOHITE - TradingView', 'Mohite Industries Ltd. Income Statement – NSE:MOHITE - TradingView', 'SBEC Sugar reports consolidated net profit of Rs 9.15 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-19 09:16:31 IST</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SVGLOBAL</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>S V Global Mill Limited</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>118</v>
+      </c>
+      <c r="F161" t="n">
+        <v>118</v>
+      </c>
+      <c r="G161" t="n">
+        <v>118</v>
+      </c>
+      <c r="H161" t="n">
+        <v>118</v>
+      </c>
+      <c r="I161" t="n">
+        <v>133</v>
+      </c>
+      <c r="J161" t="n">
+        <v>118</v>
+      </c>
+      <c r="K161" t="n">
+        <v>1</v>
+      </c>
+      <c r="L161" t="n">
+        <v>-11.28</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>['Total common shares outstanding of S V Global Mill Ltd. – NSE:SVGLOBAL - TradingView', 'S V Global Mill Ltd. Balance Sheet – NSE:SVGLOBAL - TradingView', 'S V Global Mill Ltd. Statistics – NSE:SVGLOBAL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O141"/>
+  <autoFilter ref="A1:O161"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$161</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$181</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O161"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9572,7 +9572,6 @@
       <c r="L152" t="n">
         <v>7.86</v>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9690,7 +9689,6 @@
       <c r="L154" t="n">
         <v>6.96</v>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr">
         <is>
           <t>[]</t>
@@ -9869,7 +9867,6 @@
       <c r="L157" t="n">
         <v>6.34</v>
       </c>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10125,8 +10122,1220 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>CRSL</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="F162" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="G162" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H162" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="I162" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J162" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3004809</v>
+      </c>
+      <c r="L162" t="n">
+        <v>20</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>['Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com', 'Total liabilities of Cressanda Railway Solutions Ltd – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView', 'CRSL title race takes shape as leading trio pull clear - Herald.co.zw']</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>MYSORPETRO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="F163" t="n">
+        <v>116</v>
+      </c>
+      <c r="G163" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="H163" t="n">
+        <v>116</v>
+      </c>
+      <c r="I163" t="n">
+        <v>114.93</v>
+      </c>
+      <c r="J163" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="K163" t="n">
+        <v>68040</v>
+      </c>
+      <c r="L163" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>['Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView', 'Price to book ratio of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>TECILCHEM</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="F164" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="G164" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="H164" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="I164" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="J164" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="K164" t="n">
+        <v>80792</v>
+      </c>
+      <c r="L164" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>KOHINOOR</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Kohinoor Foods Limited</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="F165" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="G165" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="H165" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="I165" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="J165" t="n">
+        <v>31.69</v>
+      </c>
+      <c r="K165" t="n">
+        <v>1434186</v>
+      </c>
+      <c r="L165" t="n">
+        <v>15.57</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Price to earnings forward of Kohinoor Industries Ltd. – PSX:KOIL - TradingView</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>['Price to earnings forward of Kohinoor Industries Ltd. – PSX:KOIL - TradingView', 'Kohinoor Foods reports consolidated net profit of Rs 2.10 crore in the June 2026 quarter - Business Standard', '"Jadeja a Kohinoor, Suthar a jewel in making": Former players opine on two India spinners - Crictoday', 'Kohinoor Foods Rights Issue Date, Price, Market Lot, Subscription 2026 - IPO Central', "Ravindra Jadeja hailed as 'Kohinoor diamond' after 350-wicket milestone - CricTracker"]</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>EXCELINDUS</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Excel Industries Limited</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F166" t="n">
+        <v>991.05</v>
+      </c>
+      <c r="G166" t="n">
+        <v>1148.55</v>
+      </c>
+      <c r="H166" t="n">
+        <v>990.9</v>
+      </c>
+      <c r="I166" t="n">
+        <v>985.2</v>
+      </c>
+      <c r="J166" t="n">
+        <v>1129</v>
+      </c>
+      <c r="K166" t="n">
+        <v>1055831</v>
+      </c>
+      <c r="L166" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>Excel Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>['Excel Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Excel Industries Ltd. Share Price Update: Price Action View - univest.in']</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>ORIENTHOT</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Oriental Hotels Limited</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="F167" t="n">
+        <v>124</v>
+      </c>
+      <c r="G167" t="n">
+        <v>143</v>
+      </c>
+      <c r="H167" t="n">
+        <v>124</v>
+      </c>
+      <c r="I167" t="n">
+        <v>121.21</v>
+      </c>
+      <c r="J167" t="n">
+        <v>138.56</v>
+      </c>
+      <c r="K167" t="n">
+        <v>49651038</v>
+      </c>
+      <c r="L167" t="n">
+        <v>14.31</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Net current asset value per share of Oriental Hotels Limited – BSE:ORIENTHOT - TradingView</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>['Net current asset value per share of Oriental Hotels Limited – BSE:ORIENTHOT - TradingView', 'Oriental Hotels Share Price Today Up 11.9%: Stock Analysis - univest.in', 'Volume Gainers on August 19, 2026 at 11:30 AM IST - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="F168" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="G168" t="n">
+        <v>19.51</v>
+      </c>
+      <c r="H168" t="n">
+        <v>18</v>
+      </c>
+      <c r="I168" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="J168" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="K168" t="n">
+        <v>474236</v>
+      </c>
+      <c r="L168" t="n">
+        <v>13.53</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>['Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView', 'Kamanwala Housing &amp; Construction Ltd. Cash Flow – NSE:KAMANWALA - TradingView', 'Kilburn Engineering consolidated net profit declines 38.57% in the June 2026 quarter - Business Standard', 'SBEC Systems (India) consolidated net profit declines 13.64% in the June 2026 quarter - Business Standard', 'Parnax Lab consolidated net profit declines 86.85% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>SONAMLTD</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>SONAM LIMITED</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>68</v>
+      </c>
+      <c r="F169" t="n">
+        <v>62.3</v>
+      </c>
+      <c r="G169" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="H169" t="n">
+        <v>60.74</v>
+      </c>
+      <c r="I169" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="J169" t="n">
+        <v>68</v>
+      </c>
+      <c r="K169" t="n">
+        <v>977582</v>
+      </c>
+      <c r="L169" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>["Here's Why We Think Sonam (NSE:SONAMLTD) Is Well Worth Watching - simplywall.st"]</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>GFLLIMITED</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>GFL Limited</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="F170" t="n">
+        <v>52</v>
+      </c>
+      <c r="G170" t="n">
+        <v>58.05</v>
+      </c>
+      <c r="H170" t="n">
+        <v>51.23</v>
+      </c>
+      <c r="I170" t="n">
+        <v>51.22</v>
+      </c>
+      <c r="J170" t="n">
+        <v>57.2</v>
+      </c>
+      <c r="K170" t="n">
+        <v>770053</v>
+      </c>
+      <c r="L170" t="n">
+        <v>11.68</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>GFL Ltd. (GFLLIMITED) Share Price Rises 9.71% Today: Price Action and Stock Analysis - univest.in</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>['GFL Ltd. (GFLLIMITED) Share Price Rises 9.71% Today: Price Action and Stock Analysis - univest.in']</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>ZAGGLE</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Ocean Services Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>185.09</v>
+      </c>
+      <c r="F171" t="n">
+        <v>187.4</v>
+      </c>
+      <c r="G171" t="n">
+        <v>194.7</v>
+      </c>
+      <c r="H171" t="n">
+        <v>180</v>
+      </c>
+      <c r="I171" t="n">
+        <v>165.88</v>
+      </c>
+      <c r="J171" t="n">
+        <v>185.09</v>
+      </c>
+      <c r="K171" t="n">
+        <v>39149680</v>
+      </c>
+      <c r="L171" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>['Zaggle Prepaid Share Price Tanks 20% To Hit 52-Week Low After Q1 Results Spook Investors - NDTV Profit', 'Zaggle Prepaid Q1 Results: Profit Slumps 57% As Margin Shrinks; Revenue Falls 32% - NDTV Profit', 'Zaggle Q1 profit falls 33% despite 28% revenue growth as acquisition costs weigh on margins - CNBC TV18', 'Why Are Zaggle Shares Down Today? Q1 Profit Falls 33% Despite 27.5% Revenue Growth; Dice Costs Hit Margins - businessupturn.com', 'Zaggle Prepaid Ocean Services Limited Just Missed Earnings - But Analysts Have Updated Their Models - simplywall.st']</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NILKAMAL</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Nilkamal Limited</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>2049</v>
+      </c>
+      <c r="F172" t="n">
+        <v>1848.7</v>
+      </c>
+      <c r="G172" t="n">
+        <v>2105</v>
+      </c>
+      <c r="H172" t="n">
+        <v>1832.5</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1846.7</v>
+      </c>
+      <c r="J172" t="n">
+        <v>2049</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1424389</v>
+      </c>
+      <c r="L172" t="n">
+        <v>10.95</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Nilkamal Ltd Upgraded to Buy on Improved Technicals and Valuation - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>['Nilkamal Ltd Upgraded to Buy on Improved Technicals and Valuation - MarketsMojo', 'Nilkamal Ltd Upgraded to Buy by MarketsMOJO on Strong Financial and Technical Grounds - MarketsMojo', 'Nilkamal Ltd Technical Momentum Shifts Signal Bullish Outlook Amid Market Volatility - MarketsMojo', "Nilkamal Ltd Surges 8.0% to Day's High of Rs 1970 — Outperforms Sector by 7.27 Percentage Points - MarketsMojo", 'Nilkamal vs Supreme Industries: Plastics Compared - univest.in']</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="F173" t="n">
+        <v>37.4</v>
+      </c>
+      <c r="G173" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="H173" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="I173" t="n">
+        <v>36.43</v>
+      </c>
+      <c r="J173" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="K173" t="n">
+        <v>230285</v>
+      </c>
+      <c r="L173" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Primer: Ahlada Engineers (AHLADA IN) - Aug 2026 - Smartkarma</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>['Primer: Ahlada Engineers (AHLADA IN) - Aug 2026 - Smartkarma', 'NMDC Steel standalone net profit rises 97.61% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>RPEL</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Raghav Productivity Enhancers Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>1650</v>
+      </c>
+      <c r="F174" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G174" t="n">
+        <v>1665</v>
+      </c>
+      <c r="H174" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1495.2</v>
+      </c>
+      <c r="J174" t="n">
+        <v>1650</v>
+      </c>
+      <c r="K174" t="n">
+        <v>375056</v>
+      </c>
+      <c r="L174" t="n">
+        <v>10.35</v>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="F175" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="G175" t="n">
+        <v>21.28</v>
+      </c>
+      <c r="H175" t="n">
+        <v>18.54</v>
+      </c>
+      <c r="I175" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="J175" t="n">
+        <v>20.51</v>
+      </c>
+      <c r="K175" t="n">
+        <v>176515155</v>
+      </c>
+      <c r="L175" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Sugar stocks: Bajaj Hindusthan, Shree Renuka, Dwarikesh shares rally up to 12%; here's why - businesstoday.in</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>["Sugar stocks: Bajaj Hindusthan, Shree Renuka, Dwarikesh shares rally up to 12%; here's why - businesstoday.in", 'Sugar stocks rally up to 10% as domestic prices surge on tight supplies; import duty cut in focus - TradingView', 'Most Active Equities on August 19, 2026 at 11:30 AM IST - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MANBRO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Manbro Industries Limited</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="F176" t="n">
+        <v>53</v>
+      </c>
+      <c r="G176" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="H176" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="I176" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="J176" t="n">
+        <v>58.41</v>
+      </c>
+      <c r="K176" t="n">
+        <v>141932</v>
+      </c>
+      <c r="L176" t="n">
+        <v>10</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>['Manbro Ind Q1 Results FY27: Revenue Rs 34 crore, Net Profit Rs 3 Crore - univest.in', 'Total liabilities of KD Green Industries Limited – NSE:MANBRO - TradingView', 'KD Green Industries Limited Financial Statements – NSE:MANBRO - TradingView', 'KD Green Industries Limited Statistics – NSE:MANBRO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="F177" t="n">
+        <v>190</v>
+      </c>
+      <c r="G177" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="H177" t="n">
+        <v>190</v>
+      </c>
+      <c r="I177" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="J177" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="K177" t="n">
+        <v>29368751</v>
+      </c>
+      <c r="L177" t="n">
+        <v>10</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>['Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView', 'Basic earnings per share (basic EPS) of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView', 'Milky Mist Dairy Food Ltd. Earnings and Revenue – BSE:MILKYMIST - TradingView', 'Milky Mist Dairy Food Limited: Target Price Consensus and Analysts Recommendations | MILKYMIST | INE00IT01020 - marketscreener.com', 'EBITDA margin % of Milky Mist Dairy Food Ltd. – BSE:MILKYMIST - TradingView']</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>SALSTEEL</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>S.A.L. Steel Limited</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="F178" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="G178" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="H178" t="n">
+        <v>72.06999999999999</v>
+      </c>
+      <c r="I178" t="n">
+        <v>72.02</v>
+      </c>
+      <c r="J178" t="n">
+        <v>79.22</v>
+      </c>
+      <c r="K178" t="n">
+        <v>923773</v>
+      </c>
+      <c r="L178" t="n">
+        <v>10</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>S.A.L. Steel Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>['S.A.L. Steel Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'SAL Steel Share Price Rises 8.17%: Technicals, Valuation - univest.in']</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SIEL</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Superior Industrial Enterprises Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="F179" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="G179" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="H179" t="n">
+        <v>39.39</v>
+      </c>
+      <c r="I179" t="n">
+        <v>38.57</v>
+      </c>
+      <c r="J179" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="K179" t="n">
+        <v>20184</v>
+      </c>
+      <c r="L179" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Return on equity % of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>['Return on equity % of Superior Industrial Enterprises Limited – NSE:SIEL - TradingView', 'Superior Industrial Enterprises Limited Income Statement – NSE:SIEL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>PERMAGN</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Permanent Magnets Limited</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>885</v>
+      </c>
+      <c r="F180" t="n">
+        <v>821</v>
+      </c>
+      <c r="G180" t="n">
+        <v>929</v>
+      </c>
+      <c r="H180" t="n">
+        <v>821</v>
+      </c>
+      <c r="I180" t="n">
+        <v>804.75</v>
+      </c>
+      <c r="J180" t="n">
+        <v>885</v>
+      </c>
+      <c r="K180" t="n">
+        <v>43018</v>
+      </c>
+      <c r="L180" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Operating margin % of Permanent Magnets Limited – NSE:PERMAGN - TradingView</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>['Operating margin % of Permanent Magnets Limited – NSE:PERMAGN - TradingView', 'Permanent Magnets Limited Cash Flow – NSE:PERMAGN - TradingView', 'Permanent Magnets Limited Approves Final Dividend for the Year Ended March 31, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SHERVANI</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate Limited</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="F181" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="G181" t="n">
+        <v>367.4</v>
+      </c>
+      <c r="H181" t="n">
+        <v>338</v>
+      </c>
+      <c r="I181" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="J181" t="n">
+        <v>338.2</v>
+      </c>
+      <c r="K181" t="n">
+        <v>4397</v>
+      </c>
+      <c r="L181" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>['Shervani Industrial Syndicate consolidated net profit rises 291.18% in the June 2026 quarter - Business Standard', 'Shervani Industrial Syndicate posts profit; appoints new Executive Director - Whalesbook', 'Return on assets % of Shervani Industrial Syndicate Limited – NSE:SHERVANI - TradingView', 'Shervani Industrial Syndicate Limited Income Statement – NSE:SHERVANI - TradingView', 'Shervani Indust Standalone June 2026 Net Sales at Rs 4.60 crore, down 40.95% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O161"/>
+  <autoFilter ref="A1:O181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10137,7 +11346,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O161"/>
+  <dimension ref="A1:O181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18725,7 +19934,6 @@
       <c r="L143" t="n">
         <v>-4.64</v>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19148,7 +20356,6 @@
       <c r="L150" t="n">
         <v>-4.98</v>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr">
         <is>
           <t>[]</t>
@@ -19831,8 +21038,1216 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>KOKUYOCMLN</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Kokuyo Camlin Limited</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="F162" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="G162" t="n">
+        <v>85.5</v>
+      </c>
+      <c r="H162" t="n">
+        <v>79.8</v>
+      </c>
+      <c r="I162" t="n">
+        <v>84.77</v>
+      </c>
+      <c r="J162" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="K162" t="n">
+        <v>83330</v>
+      </c>
+      <c r="L162" t="n">
+        <v>-5.51</v>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>SUYOG</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Suyog Telematics Limited</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>757</v>
+      </c>
+      <c r="F163" t="n">
+        <v>801.85</v>
+      </c>
+      <c r="G163" t="n">
+        <v>805.05</v>
+      </c>
+      <c r="H163" t="n">
+        <v>750.5</v>
+      </c>
+      <c r="I163" t="n">
+        <v>801.2</v>
+      </c>
+      <c r="J163" t="n">
+        <v>757</v>
+      </c>
+      <c r="K163" t="n">
+        <v>90236</v>
+      </c>
+      <c r="L163" t="n">
+        <v>-5.52</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>Transcript : Suyog Telematics Limited, Q1 2027 Earnings Call, Aug 12, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>['Transcript : Suyog Telematics Limited, Q1 2027 Earnings Call, Aug 12, 2026 - marketscreener.com', 'Suyog Telematics consolidated net profit declines 16.28% in the June 2026 quarter - Business Standard', 'Suyog Gurbaxani Funicular Ropeways recommends ₹0.50 final dividend for FY26 - scanx.trade', 'Suyog Telematics Q1 FY27 Revenue Rs 71 Cr; VI Tenancy Target 3,000 - Whalesbook', 'Suyog Tele Standalone June 2026 Net Sales at Rs 65.27 crore, up 26.45% Y-o-Y - Moneycontrol.com']</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>DAVANGERE</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Company Limited</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="F164" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="G164" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="H164" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I164" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="J164" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="K164" t="n">
+        <v>53680313</v>
+      </c>
+      <c r="L164" t="n">
+        <v>-5.64</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Davangere Sugar Q1 Results: Net profit rises 16% YoY to ₹588 crore - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>['Davangere Sugar Q1 Results: Net profit rises 16% YoY to ₹588 crore - scanx.trade', 'Gold Rate Today in Davangere 18th August 2026 : 22 &amp; 24 Carat, Gold Price in Davangere - businesstoday.in', '‘Cuisines of Karnataka’ set to spice up Davangere - Deccan Herald', "How 'Benne' became a Rs 350 crore business: Harsh Goenka explains why its buttery Davangere-style dosa bec - The Economic Times", 'BSNL to expand 4G coverage, FTTH services in Dharwad-Davangere circle - The Hindu']</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>METROGLOBL</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Metroglobal Limited</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>141.29</v>
+      </c>
+      <c r="F165" t="n">
+        <v>149.94</v>
+      </c>
+      <c r="G165" t="n">
+        <v>151</v>
+      </c>
+      <c r="H165" t="n">
+        <v>140.26</v>
+      </c>
+      <c r="I165" t="n">
+        <v>149.94</v>
+      </c>
+      <c r="J165" t="n">
+        <v>141.29</v>
+      </c>
+      <c r="K165" t="n">
+        <v>3267</v>
+      </c>
+      <c r="L165" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>BHARATSE</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Bharat Seats Limited</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="F166" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="G166" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="H166" t="n">
+        <v>224.99</v>
+      </c>
+      <c r="I166" t="n">
+        <v>240.91</v>
+      </c>
+      <c r="J166" t="n">
+        <v>226.9</v>
+      </c>
+      <c r="K166" t="n">
+        <v>441229</v>
+      </c>
+      <c r="L166" t="n">
+        <v>-5.82</v>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>LGHL</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Laxmi Goldorna House Limited</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>170</v>
+      </c>
+      <c r="F167" t="n">
+        <v>185</v>
+      </c>
+      <c r="G167" t="n">
+        <v>185</v>
+      </c>
+      <c r="H167" t="n">
+        <v>168</v>
+      </c>
+      <c r="I167" t="n">
+        <v>180.84</v>
+      </c>
+      <c r="J167" t="n">
+        <v>170</v>
+      </c>
+      <c r="K167" t="n">
+        <v>7267</v>
+      </c>
+      <c r="L167" t="n">
+        <v>-5.99</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>LGHL Stock Tracks Insider Ownership Shift As Volatility Builds - StocksToTrade</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>['LGHL Stock Tracks Insider Ownership Shift As Volatility Builds - StocksToTrade', 'LGHL Stock In Focus As Insider Ownership Shifts - StocksToTrade', 'Laxmi Goldorna House Ltd. Revenue Breakdown – NSE:LGHL - TradingView', 'Lion Group Holding (LGHL) Sheds 6.74% to $0.90, Approaching Key Support at $0.85 - Rectangle Pattern - Vinanet', 'Lion Group Holding Launches Massive 2026 Share Incentive Plan No. 2 - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>HATSUN</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Hatsun Agro Product Limited</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>925.6</v>
+      </c>
+      <c r="F168" t="n">
+        <v>985.35</v>
+      </c>
+      <c r="G168" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H168" t="n">
+        <v>921</v>
+      </c>
+      <c r="I168" t="n">
+        <v>985.35</v>
+      </c>
+      <c r="J168" t="n">
+        <v>925.6</v>
+      </c>
+      <c r="K168" t="n">
+        <v>147018</v>
+      </c>
+      <c r="L168" t="n">
+        <v>-6.06</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>Hatsun Agro gains as Arun Icecreams expands US presence - Business Standard</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>['Hatsun Agro gains as Arun Icecreams expands US presence - Business Standard', 'Hatsun Agro Product Debuts Arun Icecreams At New York India Day Parade - Sahi', 'Dairy major Hatsun Agro Product plans ₹1000 crore capex in FY27 - BusinessLine', 'Hatsun Agro Product schedules investor meets with 11 funds - scanx.trade', 'Hatsun Agro Product: FY27లో ₹12,000 కోట్ల టార్గెట్.. ₹1,000 కోట్ల పెట్టుబడితో దూసుకెళ్లేందుకు రెడీ! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>PRECWIRE</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>429.85</v>
+      </c>
+      <c r="F169" t="n">
+        <v>458</v>
+      </c>
+      <c r="G169" t="n">
+        <v>458</v>
+      </c>
+      <c r="H169" t="n">
+        <v>425.1</v>
+      </c>
+      <c r="I169" t="n">
+        <v>458.2</v>
+      </c>
+      <c r="J169" t="n">
+        <v>429.85</v>
+      </c>
+      <c r="K169" t="n">
+        <v>883319</v>
+      </c>
+      <c r="L169" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Precision Wires India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>['Precision Wires India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Should You Be Adding Precision Wires India (NSE:PRECWIRE) To Your Watchlist Today? - simplywall.st', 'Precision Wires India FY26 Results: Net profit surges 72% to ₹155 crore - scanx.trade', 'Precision Wires India Q1 Results: Revenue rises 59% YoY to ₹1,779 crore - scanx.trade', 'Precision Wires India Limited Announces Chief Financial Officer Changes, Effective August 10, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>ANTELOPUS</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Limited</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>801</v>
+      </c>
+      <c r="F170" t="n">
+        <v>863</v>
+      </c>
+      <c r="G170" t="n">
+        <v>863</v>
+      </c>
+      <c r="H170" t="n">
+        <v>793.75</v>
+      </c>
+      <c r="I170" t="n">
+        <v>856.55</v>
+      </c>
+      <c r="J170" t="n">
+        <v>801</v>
+      </c>
+      <c r="K170" t="n">
+        <v>209723</v>
+      </c>
+      <c r="L170" t="n">
+        <v>-6.49</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>Antelopus Selan Energy Limited Announces Cessation of Mr. Manjit Singh as Independent Director and from Board Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>['Antelopus Selan Energy Limited Announces Cessation of Mr. Manjit Singh as Independent Director and from Board Committees, Effective August 09, 2026 - marketscreener.com', "Antelopus Selan Energy Ltd Surges 7.14% to Day's High of Rs 857.5 — Outperforms Sector by 6.12 Percentage Points - MarketsMojo", 'Antelopus Selan Energy reshapes board committees after independent director exits - The Globe and Mail', 'Antelopus Selan Energy sees Manjit Singh step down as Independent Director - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>INDSWFTLAB</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Limited</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="F171" t="n">
+        <v>347.47</v>
+      </c>
+      <c r="G171" t="n">
+        <v>348</v>
+      </c>
+      <c r="H171" t="n">
+        <v>320.05</v>
+      </c>
+      <c r="I171" t="n">
+        <v>346.87</v>
+      </c>
+      <c r="J171" t="n">
+        <v>323.5</v>
+      </c>
+      <c r="K171" t="n">
+        <v>1535652</v>
+      </c>
+      <c r="L171" t="n">
+        <v>-6.74</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>['Ind-Swift Laboratories Ltd. (INDSWFTLAB) Share Price Rises 8.68% as Small Cap Stock Gains Today - univest.in', 'Ind-Swift Labs releases Q1FY27 earnings call audio recording - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>BRIGHTBR</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Bright Brothers Limited</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>236.01</v>
+      </c>
+      <c r="F172" t="n">
+        <v>253.86</v>
+      </c>
+      <c r="G172" t="n">
+        <v>259</v>
+      </c>
+      <c r="H172" t="n">
+        <v>221</v>
+      </c>
+      <c r="I172" t="n">
+        <v>255.13</v>
+      </c>
+      <c r="J172" t="n">
+        <v>236.01</v>
+      </c>
+      <c r="K172" t="n">
+        <v>744</v>
+      </c>
+      <c r="L172" t="n">
+        <v>-7.49</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>Inventory turnover of Bright Brothers Limited – NSE:BRIGHTBR - TradingView</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>['Inventory turnover of Bright Brothers Limited – NSE:BRIGHTBR - TradingView', 'Bright Brothers Limited Statistics – NSE:BRIGHTBR - TradingView']</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PAKKA</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>PAKKA LIMITED</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="F173" t="n">
+        <v>95.8</v>
+      </c>
+      <c r="G173" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="H173" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="I173" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="J173" t="n">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="K173" t="n">
+        <v>446675</v>
+      </c>
+      <c r="L173" t="n">
+        <v>-7.74</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Pakka Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>['Pakka Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com', 'Earnings call transcript: Pakka posts record Q1 2026 revenue, shares jump 8% - Investing.com', 'PAKKA: Record quarterly revenue, strong profit growth, and PM4 commissioning to drive future expansion - TradingView', 'Pakka Limited Confirms No Deviation in Preferential Issue Fund Use - TipRanks', 'PAKKA: Record revenue, strong growth, and PM4 commissioning set to boost capacity and margins - TradingView']</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>FINKURVE</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="F174" t="n">
+        <v>77</v>
+      </c>
+      <c r="G174" t="n">
+        <v>78.29000000000001</v>
+      </c>
+      <c r="H174" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="I174" t="n">
+        <v>78.19</v>
+      </c>
+      <c r="J174" t="n">
+        <v>71.98999999999999</v>
+      </c>
+      <c r="K174" t="n">
+        <v>318389</v>
+      </c>
+      <c r="L174" t="n">
+        <v>-7.93</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>['Finkurve Financial Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Finkurve Financial Q1 Results: Revenue surges 89% YoY, net profit up 66% - scanx.trade', 'Finkurve Financial Services standalone net profit rises 65.82% in the June 2026 quarter - Business Standard', 'Finkurve Financial Services Reports Q1 Standalone Net Profit of 84M Rupees, Revenue Up at 751M Rupees - Sahi', 'Finkurve Financial Services Share Price Target 2027 to 2030 - univest.in']</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>AAKASH</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Aakash Exploration Services Limited</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="F175" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G175" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="H175" t="n">
+        <v>8.06</v>
+      </c>
+      <c r="I175" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="J175" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K175" t="n">
+        <v>719756</v>
+      </c>
+      <c r="L175" t="n">
+        <v>-8</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Aakash Exploration Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>['Aakash Exploration Services Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Aakash Exploration Services standalone net profit declines 3.70% in the June 2026 quarter - Business Standard', 'Aakash Explorat Standalone June 2026 Net Sales at Rs 27.89 crore, up 16.93% Y-o-Y - Moneycontrol.com', 'Aakash Educational Services Limited (AESL) Launches ANTHE 2026 | - odishabarta.com', 'Aakash Chopra reveals batting strategy for India on Day 4 of SL vs IND 2026 1st Test - Dafanews India']</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>MOLBIO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Molbio Diagnostics Limited</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>1019.25</v>
+      </c>
+      <c r="F176" t="n">
+        <v>1085</v>
+      </c>
+      <c r="G176" t="n">
+        <v>1132.85</v>
+      </c>
+      <c r="H176" t="n">
+        <v>1012</v>
+      </c>
+      <c r="I176" t="n">
+        <v>1110.9</v>
+      </c>
+      <c r="J176" t="n">
+        <v>1019.25</v>
+      </c>
+      <c r="K176" t="n">
+        <v>6151804</v>
+      </c>
+      <c r="L176" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>EBITDA margin % of Molbio Diagnostics Limited – NSE:MOLBIO - TradingView</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>['EBITDA margin % of Molbio Diagnostics Limited – NSE:MOLBIO - TradingView', 'Operating margin % of Molbio Diagnostics Limited – NSE:MOLBIO - TradingView', 'Molbio Diagnostics Limited Revenue Breakdown – NSE:MOLBIO - TradingView', 'Total revenue of Molbio Diagnostics Limited – NSE:MOLBIO - TradingView', 'Gross margin % of Molbio Diagnostics Limited – NSE:MOLBIO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>DEEPINDS</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Deep Industries Limited</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>658</v>
+      </c>
+      <c r="F177" t="n">
+        <v>717.95</v>
+      </c>
+      <c r="G177" t="n">
+        <v>720</v>
+      </c>
+      <c r="H177" t="n">
+        <v>656.7</v>
+      </c>
+      <c r="I177" t="n">
+        <v>717.95</v>
+      </c>
+      <c r="J177" t="n">
+        <v>658</v>
+      </c>
+      <c r="K177" t="n">
+        <v>622935</v>
+      </c>
+      <c r="L177" t="n">
+        <v>-8.35</v>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>["There's A Lot To Like About Deep Industries' (NSE:DEEPINDS) Upcoming ₹2.50 Dividend - simplywall.st"]</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>YASHO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Yasho Industries Limited</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>4455</v>
+      </c>
+      <c r="F178" t="n">
+        <v>4910</v>
+      </c>
+      <c r="G178" t="n">
+        <v>4911.2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>4411.6</v>
+      </c>
+      <c r="I178" t="n">
+        <v>4915.8</v>
+      </c>
+      <c r="J178" t="n">
+        <v>4455</v>
+      </c>
+      <c r="K178" t="n">
+        <v>167724</v>
+      </c>
+      <c r="L178" t="n">
+        <v>-9.369999999999999</v>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>["183.68% Stock Return, 372.3% Profit Growth: What's Driving Yasho Industries Ltd's Multibagger Rerating? - MarketsMojo", 'Yasho Industries Ltd Hits All-Time High of Rs 4640.95 as Momentum Builds Across Timeframes - MarketsMojo', 'Yasho Industries Ltd Hits Intraday Low Amid Price Pressure on 19 Aug 2026 - MarketsMojo', 'After years of capex pain, is Yasho Industries entering a new growth phase? - The Indian Express', 'Why Yasho Industries’ ₹150 Cr Deal Could Change Its Growth Story - outlookbusiness.com']</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>MODTHREAD</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Modern Threads (India) Limited</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="F179" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="G179" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="H179" t="n">
+        <v>51</v>
+      </c>
+      <c r="I179" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="J179" t="n">
+        <v>51.85</v>
+      </c>
+      <c r="K179" t="n">
+        <v>32489</v>
+      </c>
+      <c r="L179" t="n">
+        <v>-9.779999999999999</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Modern Threads (India) Ltd. (MODTHREAD) Share Price Rises 20% Today - univest.in</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>['Modern Threads (India) Ltd. (MODTHREAD) Share Price Rises 20% Today - univest.in', 'Modern Threads Q1 Results: Net profit up 9,800% YoY to ₹588 lakh - scanx.trade', 'Modern Threads (India) Share Price Fall: Price, Valuation - univest.in']</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="F180" t="n">
+        <v>103.04</v>
+      </c>
+      <c r="G180" t="n">
+        <v>111.51</v>
+      </c>
+      <c r="H180" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="I180" t="n">
+        <v>101.38</v>
+      </c>
+      <c r="J180" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="K180" t="n">
+        <v>1005935</v>
+      </c>
+      <c r="L180" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Indonesian Stocks Ease Ahead of BI Rate Decision - TradingView</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>['Indonesian Stocks Ease Ahead of BI Rate Decision - TradingView', 'Indonesia Stocks Fall 0.86% as Investors Digest BI Rate Decision - Jakarta Globe', 'Indonesia Stocks Slide 0.67% as Debt Concerns, BI Rate Outlook Weigh - Jakarta Globe', 'Three H-1B rejections later, an Indian techie secures O-1 ‘extraordinary ability’ Visa - livemint.com', 'Rupiah Gains as BI Holds Policy Rate at 5.75% - TradingPedia']</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-19 16:27:41 IST</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="F181" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="G181" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="H181" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="I181" t="n">
+        <v>61.99</v>
+      </c>
+      <c r="J181" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="K181" t="n">
+        <v>322</v>
+      </c>
+      <c r="L181" t="n">
+        <v>-10.71</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>['KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O161"/>
+  <autoFilter ref="A1:O181"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$181</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$201</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O181"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10289,7 +10289,6 @@
       <c r="L164" t="n">
         <v>19.91</v>
       </c>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr">
         <is>
           <t>[]</t>
@@ -10895,7 +10894,6 @@
       <c r="L174" t="n">
         <v>10.35</v>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11334,8 +11332,1212 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>MPDL</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="F182" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G182" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="H182" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="I182" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J182" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="K182" t="n">
+        <v>1</v>
+      </c>
+      <c r="L182" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>['MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView', 'MPDL Ltd Balance Sheet – NSE:MPDL - TradingView', 'MPDL Ltd Statistics – NSE:MPDL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="F183" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="G183" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="H183" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="I183" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="J183" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1</v>
+      </c>
+      <c r="L183" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>['KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>ISTLTD</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>I S T Limited</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="F184" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="G184" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="H184" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="I184" t="n">
+        <v>637.1</v>
+      </c>
+      <c r="J184" t="n">
+        <v>737.5</v>
+      </c>
+      <c r="K184" t="n">
+        <v>10</v>
+      </c>
+      <c r="L184" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>IST Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>['IST Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Operating margin % of IST Ltd – NSE:ISTLTD - TradingView', 'IST Ltd Statistics – NSE:ISTLTD - TradingView', 'IST Limited Reports Q1 Revenue Of ₹34.9 Crore And Consolidated Net Profit Of ₹83.1 Crore - Sahi']</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>SOMICONVEY</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Limited</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="F185" t="n">
+        <v>96</v>
+      </c>
+      <c r="G185" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="H185" t="n">
+        <v>95</v>
+      </c>
+      <c r="I185" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="J185" t="n">
+        <v>99.95</v>
+      </c>
+      <c r="K185" t="n">
+        <v>19483</v>
+      </c>
+      <c r="L185" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>MYSORPETRO</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="F186" t="n">
+        <v>160</v>
+      </c>
+      <c r="G186" t="n">
+        <v>160</v>
+      </c>
+      <c r="H186" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="I186" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="J186" t="n">
+        <v>158.9</v>
+      </c>
+      <c r="K186" t="n">
+        <v>28765</v>
+      </c>
+      <c r="L186" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>['Mysore Petro Chemicals Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Number of employees of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView', 'Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>CRSL</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F187" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G187" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="H187" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I187" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J187" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K187" t="n">
+        <v>433339</v>
+      </c>
+      <c r="L187" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>['Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com', 'Total liabilities of Cressanda Railway Solutions Ltd – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView', 'CRSL title race takes shape as leading trio pull clear - Herald.co.zw']</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>MOHITE</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Mohite Industries Limited</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F188" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="G188" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H188" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="I188" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="J188" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K188" t="n">
+        <v>208</v>
+      </c>
+      <c r="L188" t="n">
+        <v>10.88</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>['Mohite Industries Q1 Results: Net loss widens 142% YoY to ₹245.62 lakh - scanx.trade', 'Mohite Industries: Board Approves Q1 FY27 Unaudited Financial Results - InvestyWise', 'Mohite Industries reports consolidated net loss of Rs 2.46 crore in the June 2026 quarter - Business Standard', 'MOHITE Share Price Today - Mohite Industries Stock Analysis - Equitypandit', 'Book value per share of Mohite Industries Ltd. – NSE:MOHITE - TradingView']</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>GRAVISSHO</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Graviss Hospitality Limited</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="F189" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="G189" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="H189" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="I189" t="n">
+        <v>28.72</v>
+      </c>
+      <c r="J189" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="K189" t="n">
+        <v>450</v>
+      </c>
+      <c r="L189" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TECILCHEM</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="F190" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="G190" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H190" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="I190" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="J190" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="K190" t="n">
+        <v>12014</v>
+      </c>
+      <c r="L190" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>ODYCORP</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Odyssey Corporation Limited</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="G191" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H191" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I191" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="J191" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="K191" t="n">
+        <v>201</v>
+      </c>
+      <c r="L191" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Operating margin % of Odyssey Corporation Limited – NSE:ODYCORP - TradingView</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>['Operating margin % of Odyssey Corporation Limited – NSE:ODYCORP - TradingView', 'Odyssey Corporation Limited Statistics – NSE:ODYCORP - TradingView']</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>INFOMEDIA</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Infomedia Press Limited</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="F192" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="G192" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="H192" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="I192" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="J192" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K192" t="n">
+        <v>1020</v>
+      </c>
+      <c r="L192" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Bharatiya Global Infomedia reports consolidated net loss of Rs 0.08 crore in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>['Bharatiya Global Infomedia reports consolidated net loss of Rs 0.08 crore in the June 2026 quarter - Business Standard', 'Jupiter Infomedia reports consolidated net loss of Rs 0.18 crore in the June 2026 quarter - Business Standard', 'BGIL Q1 Results: Consolidated Net Loss ₹7.6 Lakh, Revenue Falls 68% - scanx.trade', 'Infomedia Group Number of Employees 2026 | Employee Count &amp; Headcount Data - Revelio Labs', 'Tube Investments of India consolidated net profit declines 15.25% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>HAVISHA</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Sri Havisha Hospitality and Infrastructure Limited</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="F193" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="G193" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H193" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I193" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J193" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="K193" t="n">
+        <v>51</v>
+      </c>
+      <c r="L193" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Sri Havisha Q1 Results: Board approves unaudited financials - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>['Sri Havisha Q1 Results: Board approves unaudited financials - scanx.trade', 'Sri Havisha Hospitality &amp; Infrastructure reports standalone net loss of Rs 1.82 crore in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>SAMBANDAM</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills Limited</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>114</v>
+      </c>
+      <c r="F194" t="n">
+        <v>114</v>
+      </c>
+      <c r="G194" t="n">
+        <v>114</v>
+      </c>
+      <c r="H194" t="n">
+        <v>114</v>
+      </c>
+      <c r="I194" t="n">
+        <v>105</v>
+      </c>
+      <c r="J194" t="n">
+        <v>114</v>
+      </c>
+      <c r="K194" t="n">
+        <v>380</v>
+      </c>
+      <c r="L194" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Price to sales forward of Sambandam Spinning Mills Limited – BSE:SAMBANDAM - TradingView</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>['Price to sales forward of Sambandam Spinning Mills Limited – BSE:SAMBANDAM - TradingView', 'Sambandam Spinning Mills Limited Balance Sheet – NSE:SAMBANDAM - TradingView', 'Sambandam Spinning Mills Limited Statistics – NSE:SAMBANDAM - TradingView', 'Sambandam Spinning Mills: कंपनी फायद्यात परतली! पण मागील वर्षाच्या तुलनेत प्रॉफिट कमी - Whalesbook', 'Sambandam Spinning Mills: Q1 FY27 ਵਿੱਚ ਮੁਨਾਫਾ ਕਮਾਇਆ, ਬੋਰਡ ਵਿੱਚ ਬਦਲਾਅ! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>NDLVENTURE</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NDL Ventures Limited</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>125</v>
+      </c>
+      <c r="F195" t="n">
+        <v>116</v>
+      </c>
+      <c r="G195" t="n">
+        <v>125</v>
+      </c>
+      <c r="H195" t="n">
+        <v>116</v>
+      </c>
+      <c r="I195" t="n">
+        <v>116.08</v>
+      </c>
+      <c r="J195" t="n">
+        <v>125</v>
+      </c>
+      <c r="K195" t="n">
+        <v>151</v>
+      </c>
+      <c r="L195" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>QUINT</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Quint Digital Limited</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="F196" t="n">
+        <v>38</v>
+      </c>
+      <c r="G196" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="H196" t="n">
+        <v>38</v>
+      </c>
+      <c r="I196" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="J196" t="n">
+        <v>38.89</v>
+      </c>
+      <c r="K196" t="n">
+        <v>1232</v>
+      </c>
+      <c r="L196" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>AI-Generated Image Shared To Show 'Old Photograph' of PM Modi and Amit Shah - The Quint</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>["AI-Generated Image Shared To Show 'Old Photograph' of PM Modi and Amit Shah - The Quint", 'AI-Generated Image Shared as Real One of Indira Gandhi Drinking With Yoga Guru - The Quint', "Jharkhand Protests 'Paused For 2 Months' After Exam Cancellations, Reforms - The Quint", "Aravallis' Legal Mapping and India’s 176th EPI Rank Are Part of the Same Story - The Quint", 'New Rules Give Maharashtra CM Fadnavis to Overrule Decisions by Any Minister - The Quint']</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>BEARDSELL</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Beardsell Limited</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="F197" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="G197" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="H197" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="I197" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="J197" t="n">
+        <v>26.9</v>
+      </c>
+      <c r="K197" t="n">
+        <v>1455</v>
+      </c>
+      <c r="L197" t="n">
+        <v>7.39</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>Beardsell consolidated net profit declines 22.07% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>['Beardsell consolidated net profit declines 22.07% in the June 2026 quarter - Business Standard', 'Beardsell Consolidated June 2026 Net Sales at Rs 72.20 crore, up 9.96% Y-o-Y - Moneycontrol.com', 'Beardsell Standalone June 2026 Net Sales at Rs 69.57 crore, up 10.55% Y-o-Y - Moneycontrol.com', 'Mangalam Cement standalone net profit declines 43.99% in the June 2026 quarter - Business Standard', 'Akums Drugs &amp; Pharmaceuticals consolidated net profit rises 57.55% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>SHIPROCKET</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Shiprocket Limited</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>153.62</v>
+      </c>
+      <c r="F198" t="n">
+        <v>149.9</v>
+      </c>
+      <c r="G198" t="n">
+        <v>155.69</v>
+      </c>
+      <c r="H198" t="n">
+        <v>149.59</v>
+      </c>
+      <c r="I198" t="n">
+        <v>143.45</v>
+      </c>
+      <c r="J198" t="n">
+        <v>153.62</v>
+      </c>
+      <c r="K198" t="n">
+        <v>5882800</v>
+      </c>
+      <c r="L198" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>Price to earnings ratio of Shiprocket Limited – BSE:SHIPROCKET - TradingView</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>['Price to earnings ratio of Shiprocket Limited – BSE:SHIPROCKET - TradingView', 'Shiprocket Limited Dividends – BSE:SHIPROCKET - TradingView', 'EBITDA of Shiprocket Limited – BSE:SHIPROCKET - TradingView', 'Shiprocket Limited Revenue Breakdown – BSE:SHIPROCKET - TradingView', 'Non-operating income (total) of Shiprocket Limited – BSE:SHIPROCKET - TradingView']</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>BLEL</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Behari Lal Engineering Limited</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>537.6</v>
+      </c>
+      <c r="F199" t="n">
+        <v>525.1</v>
+      </c>
+      <c r="G199" t="n">
+        <v>547</v>
+      </c>
+      <c r="H199" t="n">
+        <v>525.1</v>
+      </c>
+      <c r="I199" t="n">
+        <v>502.2</v>
+      </c>
+      <c r="J199" t="n">
+        <v>537.6</v>
+      </c>
+      <c r="K199" t="n">
+        <v>1112327</v>
+      </c>
+      <c r="L199" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Diluted earnings per share (diluted EPS) of Behari Lal Engineering Limited – NSE:BLEL - TradingView</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>['Diluted earnings per share (diluted EPS) of Behari Lal Engineering Limited – NSE:BLEL - TradingView', 'Basic earnings per share (basic EPS) of Behari Lal Engineering Limited – NSE:BLEL - TradingView', 'EBITDA per share of Behari Lal Engineering Limited – NSE:BLEL - TradingView', 'EBITDA margin % of Behari Lal Engineering Limited – NSE:BLEL - TradingView', 'EBITDA of Behari Lal Engineering Limited – NSE:BLEL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>STAR</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Strides Pharma Science Limited</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>1016.3</v>
+      </c>
+      <c r="F200" t="n">
+        <v>986.5</v>
+      </c>
+      <c r="G200" t="n">
+        <v>1018.8</v>
+      </c>
+      <c r="H200" t="n">
+        <v>985.4</v>
+      </c>
+      <c r="I200" t="n">
+        <v>957.5</v>
+      </c>
+      <c r="J200" t="n">
+        <v>1016.3</v>
+      </c>
+      <c r="K200" t="n">
+        <v>61767</v>
+      </c>
+      <c r="L200" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Earnings call transcript: Northern Star posts strong FY2026 as KCGM ramps up - Investing.com India</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>['Earnings call transcript: Northern Star posts strong FY2026 as KCGM ramps up - Investing.com India', 'China’s AI Boom Is Making Star 50 the Stock Index That Matters - Bloomberg.com', 'Northern Star FY26 slides: EBITDA surges 22% amid peak investment By Investing.com - Investing.com India', "Fastest-known star zooms under Milky Way black hole's influence - Reuters", "Milky Way's fastest star orbits our supermassive black hole so closely it feels its spin - Eso.org"]</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>FILATFASH</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Limited</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="F201" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I201" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J201" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K201" t="n">
+        <v>2213151</v>
+      </c>
+      <c r="L201" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>Filatex Fashions Limited Announces Resignation of Ayepu Hemalatha as Independent Director, Effective August 05, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>['Filatex Fashions Limited Announces Resignation of Ayepu Hemalatha as Independent Director, Effective August 05, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O181"/>
+  <autoFilter ref="A1:O201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -11346,7 +12548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O181"/>
+  <dimension ref="A1:O201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -21083,7 +22285,6 @@
       <c r="L162" t="n">
         <v>-5.51</v>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr">
         <is>
           <t>[]</t>
@@ -21262,7 +22463,6 @@
       <c r="L165" t="n">
         <v>-5.77</v>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr">
         <is>
           <t>[]</t>
@@ -21319,7 +22519,6 @@
       <c r="L166" t="n">
         <v>-5.82</v>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr">
         <is>
           <t>[]</t>
@@ -22246,8 +23445,1216 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>RUBYMILLS</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>The Ruby Mills Limited</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="F182" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="G182" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="H182" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="I182" t="n">
+        <v>410.25</v>
+      </c>
+      <c r="J182" t="n">
+        <v>395.8</v>
+      </c>
+      <c r="K182" t="n">
+        <v>25</v>
+      </c>
+      <c r="L182" t="n">
+        <v>-3.52</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Penalty for Wrong Availment of CENVAT Credit Not Allowable under Section 37(1) of Income Tax Act: ITAT - taxscan.in</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>['Penalty for Wrong Availment of CENVAT Credit Not Allowable under Section 37(1) of Income Tax Act: ITAT - taxscan.in']</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SHALPAINTS</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Shalimar Paints Limited</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="F183" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="G183" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="H183" t="n">
+        <v>79.55</v>
+      </c>
+      <c r="I183" t="n">
+        <v>82.54000000000001</v>
+      </c>
+      <c r="J183" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="K183" t="n">
+        <v>1952</v>
+      </c>
+      <c r="L183" t="n">
+        <v>-3.61</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>Shalimar Paints Posts Narrower Loss; Proposes Major Capital Restructuring - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>['Shalimar Paints Posts Narrower Loss; Proposes Major Capital Restructuring - Whalesbook', 'Shalimar Paints Share: ₹6,895 करोड़ के Preferential Issue में बड़ी गड़बड़ी! कंपनी ने जारी की सुधार सूचना - Whalesbook', 'Shalimar Paints Sets September 11 EGM With Remote E-Voting - TipRanks', 'Shalimar Paints: ₹6,895 कोटींच्या इश्यूमध्ये सुधारणा, गुंतवणूकदारांसाठी मोठी बातमी! - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>AAREYDRUGS</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="F184" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="G184" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="H184" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="I184" t="n">
+        <v>82.59</v>
+      </c>
+      <c r="J184" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="K184" t="n">
+        <v>5</v>
+      </c>
+      <c r="L184" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>Aarey Drugs Q1 Results: Revenue up 145% YoY, net profit falls 60% - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>['Aarey Drugs Q1 Results: Revenue up 145% YoY, net profit falls 60% - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>HALDER</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Halder Venture Limited</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>280</v>
+      </c>
+      <c r="F185" t="n">
+        <v>280</v>
+      </c>
+      <c r="G185" t="n">
+        <v>280</v>
+      </c>
+      <c r="H185" t="n">
+        <v>280</v>
+      </c>
+      <c r="I185" t="n">
+        <v>290.77</v>
+      </c>
+      <c r="J185" t="n">
+        <v>280</v>
+      </c>
+      <c r="K185" t="n">
+        <v>11</v>
+      </c>
+      <c r="L185" t="n">
+        <v>-3.7</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>Halder Venture Posts June-Quarter Consol Net Profit 59.8 Million Rupees - TradingView</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>['Halder Venture Posts June-Quarter Consol Net Profit 59.8 Million Rupees - TradingView', 'Halder Venture Share Price Target 2027 to 2030: Analyst Outlook - Univest', 'P. Ummer Elected Adhyaksh, Asha Manja Halder New Up-Adhyaksh of South Andaman Zilla Parishad - ANDAMAN SHEEKHA', 'Titas Halder Photo (August 11, 2026) - BroadwayWorld', "‘It may take three to six months to bring back PK Halder' - thefinancialexpress.com.bd"]</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>BI</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Bilcare Limited</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>88</v>
+      </c>
+      <c r="F186" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="G186" t="n">
+        <v>88</v>
+      </c>
+      <c r="H186" t="n">
+        <v>87.08</v>
+      </c>
+      <c r="I186" t="n">
+        <v>91.66</v>
+      </c>
+      <c r="J186" t="n">
+        <v>88</v>
+      </c>
+      <c r="K186" t="n">
+        <v>23605</v>
+      </c>
+      <c r="L186" t="n">
+        <v>-3.99</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>Indonesia Stocks Fall 0.86% as Investors Digest BI Rate Decision - Jakarta Globe</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>['Indonesia Stocks Fall 0.86% as Investors Digest BI Rate Decision - Jakarta Globe', '11 Best Generative BI Tools for Ecommerce: Where you can talk to your data - Ask Luca', 'Leading first BI meeting, Destry stresses growth, vigilance - The Jakarta Post', 'Indonesian Rupiah: Stability-focused BI stance – UOB - FXStreet', 'Saba Energy Provides Seventh Bi-Weekly MCTO Status Update - TradingView']</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>XTRANET</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>161.63</v>
+      </c>
+      <c r="F187" t="n">
+        <v>161</v>
+      </c>
+      <c r="G187" t="n">
+        <v>163.64</v>
+      </c>
+      <c r="H187" t="n">
+        <v>160.25</v>
+      </c>
+      <c r="I187" t="n">
+        <v>169.11</v>
+      </c>
+      <c r="J187" t="n">
+        <v>161.63</v>
+      </c>
+      <c r="K187" t="n">
+        <v>67070</v>
+      </c>
+      <c r="L187" t="n">
+        <v>-4.42</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>Xtranet Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>['Xtranet Technologies Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Xtranet Technologies hosts Q1 earnings call on August 24 - scanx.trade', 'Xtranet Technologies consolidated net profit rises 74.43% in the June 2026 quarter - Business Standard', 'Stocks to Watch Today: BSE, United Spirits, Hyundai Motor, XtraNet Tech, Autoline Industries, EMS, Ramco... - Moneycontrol.com', 'Xtranet Technologies adopts fair disclosure code for UPSI - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>39</v>
+      </c>
+      <c r="F188" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="G188" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="H188" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I188" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="J188" t="n">
+        <v>39</v>
+      </c>
+      <c r="K188" t="n">
+        <v>1462</v>
+      </c>
+      <c r="L188" t="n">
+        <v>-4.46</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers standalone net profit declines 70.69% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>['Ahlada Engineers standalone net profit declines 70.69% in the June 2026 quarter - Business Standard', 'Primer: Ahlada Engineers (AHLADA IN) - Aug 2026 - Smartkarma', 'NMDC Steel standalone net profit rises 97.61% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>POLYSPIN</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Limited</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>29</v>
+      </c>
+      <c r="F189" t="n">
+        <v>29</v>
+      </c>
+      <c r="G189" t="n">
+        <v>29</v>
+      </c>
+      <c r="H189" t="n">
+        <v>29</v>
+      </c>
+      <c r="I189" t="n">
+        <v>30.48</v>
+      </c>
+      <c r="J189" t="n">
+        <v>29</v>
+      </c>
+      <c r="K189" t="n">
+        <v>1</v>
+      </c>
+      <c r="L189" t="n">
+        <v>-4.86</v>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>Polyspin Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>['Polyspin Exports Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Shubham Polyspin Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Polyspin Exports Q1FY27 standalone net profit falls 24% to ₹87 lakh - scanx.trade', 'Book value per share of Polyspin Exports Limited – NSE:POLYSPIN - TradingView', 'Polyspin Exports Limited Cash Flow – NSE:POLYSPIN - TradingView']</t>
+        </is>
+      </c>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>GANGAFORGE</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Ganga Forging Limited</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="F190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="I190" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="J190" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="K190" t="n">
+        <v>50603</v>
+      </c>
+      <c r="L190" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>AKSHOPTFBR</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Aksh Optifibre Limited</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="F191" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G191" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="H191" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I191" t="n">
+        <v>7.68</v>
+      </c>
+      <c r="J191" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="K191" t="n">
+        <v>159286</v>
+      </c>
+      <c r="L191" t="n">
+        <v>-4.95</v>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>Aksh Optifibre Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>['Aksh Optifibre Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Aksh Optifibre Publishes Q1 FY27 Unaudited Results in Line With SEBI Norms - The Globe and Mail', 'Aksh Optifibre Posts Q1 Profit Amidst CIRP, Auditors Raise Concerns - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>BURNPUR</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Limited</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="F192" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="G192" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="H192" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="I192" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="J192" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="K192" t="n">
+        <v>2538</v>
+      </c>
+      <c r="L192" t="n">
+        <v>-4.96</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>Burnpur Cement Ltd Locks at Lower Circuit With 5.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>['Burnpur Cement Ltd Locks at Lower Circuit With 5.0% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', 'Burnpur Cement Ltd Locks at Lower Circuit With 4.97% Loss — Sellers Queue, No Buyers in Sight - MarketsMojo', 'Revenue per share of Burnpur Cement Limited – NSE:BURNPUR - TradingView', 'SEPC wins ₹854.57 crore order from SAIL for pellet plant package at Burnpur - smallcapspotlight.in', 'Burnpur Cement Ltd Falls to 52-Week Low Amidst Divergent Financial Signals - MarketsMojo']</t>
+        </is>
+      </c>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>INDOTHAI</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Limited</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="F193" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="G193" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="H193" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="I193" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J193" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="K193" t="n">
+        <v>3834</v>
+      </c>
+      <c r="L193" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>Indo Thai Securities Ltd. (INDOTHAI) Share Price Falls 9.99% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>['Indo Thai Securities Ltd. (INDOTHAI) Share Price Falls 9.99% Today - Univest', 'Indo Thai Securities Ltd. (INDOTHAI) Share Price Hits Fresh 52-Week Low - Univest', 'Indo Thai Securities schedules NCLT hearing for demerger scheme on September 24 - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>ONIXSOLAR</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Onix Solar Energy Limited</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="F194" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="G194" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="H194" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="I194" t="n">
+        <v>338.85</v>
+      </c>
+      <c r="J194" t="n">
+        <v>321.95</v>
+      </c>
+      <c r="K194" t="n">
+        <v>143</v>
+      </c>
+      <c r="L194" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>['Total common shares outstanding of Onix Solar Energy Ltd. – NSE:ONIXSOLAR - TradingView', 'Onix Solar Energy Ltd. Balance Sheet – NSE:ONIXSOLAR - TradingView', 'Onix Solar Energy Ltd. Income Statement – NSE:ONIXSOLAR - TradingView']</t>
+        </is>
+      </c>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>RSDFIN</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>RSD Finance Limited</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="F195" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="G195" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="H195" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="I195" t="n">
+        <v>96.34</v>
+      </c>
+      <c r="J195" t="n">
+        <v>91.53</v>
+      </c>
+      <c r="K195" t="n">
+        <v>865</v>
+      </c>
+      <c r="L195" t="n">
+        <v>-4.99</v>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>RSD Finance Ltd. (RSDFIN) Share Price Rises 9.98% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>['RSD Finance Ltd. (RSDFIN) Share Price Rises 9.98% Today - Univest']</t>
+        </is>
+      </c>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>GRANDOAK</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Grand Oak Canyons Distillery Limited</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="F196" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="G196" t="n">
+        <v>37.04</v>
+      </c>
+      <c r="H196" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="I196" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="J196" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="K196" t="n">
+        <v>2299</v>
+      </c>
+      <c r="L196" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>Grandoak Q1 FY27 Results: Revenue Rs 0.08 Cr, Net Loss Rs 0.02 Cr and Key Highlights - Univest</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>['Grandoak Q1 FY27 Results: Revenue Rs 0.08 Cr, Net Loss Rs 0.02 Cr and Key Highlights - Univest', 'Grand Oak Canyons Distillery Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>NATIONSTD</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>National Standard (India) Limited</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="F197" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="G197" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="H197" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="I197" t="n">
+        <v>127.3</v>
+      </c>
+      <c r="J197" t="n">
+        <v>120.94</v>
+      </c>
+      <c r="K197" t="n">
+        <v>5587</v>
+      </c>
+      <c r="L197" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>UEL</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Ujaas Energy Limited</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="F198" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="G198" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="H198" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="I198" t="n">
+        <v>200.8</v>
+      </c>
+      <c r="J198" t="n">
+        <v>190.76</v>
+      </c>
+      <c r="K198" t="n">
+        <v>1232</v>
+      </c>
+      <c r="L198" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>UEL Third Qualifying Round Results and 2026/27 Play-Off Draw - blog.ke.sportpesa.com</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>['UEL Third Qualifying Round Results and 2026/27 Play-Off Draw - blog.ke.sportpesa.com', 'Parkwood Leisure and UEL extend clinical placement partnership - Well Nation', 'Explained: UCL, UEL, UECL Knockout Stages Format｜Champions League｜Europa League｜Conference League Giancarlo Stanton (D4OKPIo24k) - mshale.com', 'Marseille 0-3 Atletico Madrid Griezmann Magical Double Hands Side UEL Champions|FOOTBALL NEWS 2018 Bitcoin (713AaOk7pu) - mshale.com', 'Son, Maddison &amp; Ange React After Spurs UEL Win! | Hoffenheim Vs Tottenham | Post-Match Interviews Beckett Sennecke (y6fizeNqNq) - mshale.com']</t>
+        </is>
+      </c>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>UNIVASTU</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Univastu India Limited</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="F199" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="G199" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="H199" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="I199" t="n">
+        <v>168.05</v>
+      </c>
+      <c r="J199" t="n">
+        <v>159.65</v>
+      </c>
+      <c r="K199" t="n">
+        <v>992</v>
+      </c>
+      <c r="L199" t="n">
+        <v>-5</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>Univastu India consolidated net profit rises 281.61% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>['Univastu India consolidated net profit rises 281.61% in the June 2026 quarter - Business Standard', 'Univastu India Consolidated June 2026 Net Sales at Rs 103.72 crore, up 252.69% Y-o-Y - Moneycontrol.com', 'Univastu India Standalone June 2026 Net Sales at Rs 99.94 crore, up 296.11% Y-o-Y - Moneycontrol.com', 'Univastu India Ltd Hits All-Time High of Rs 158 as Momentum Builds Across Timeframes - MarketsMojo', 'Aryan Share &amp; Stock Brokers standalone net profit declines 78.45% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>ORIENTHOT</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Oriental Hotels Limited</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="F200" t="n">
+        <v>138</v>
+      </c>
+      <c r="G200" t="n">
+        <v>138</v>
+      </c>
+      <c r="H200" t="n">
+        <v>131.02</v>
+      </c>
+      <c r="I200" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="J200" t="n">
+        <v>132.02</v>
+      </c>
+      <c r="K200" t="n">
+        <v>223195</v>
+      </c>
+      <c r="L200" t="n">
+        <v>-5.36</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>Net current asset value per share of Oriental Hotels Limited – BSE:ORIENTHOT - TradingView</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>['Net current asset value per share of Oriental Hotels Limited – BSE:ORIENTHOT - TradingView', 'Oriental Hotels Share Price Today Up 11.9%: Stock Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-20 09:16:48 IST</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>CURAA</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Cura Technologies Limited</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>63</v>
+      </c>
+      <c r="F201" t="n">
+        <v>63</v>
+      </c>
+      <c r="G201" t="n">
+        <v>63</v>
+      </c>
+      <c r="H201" t="n">
+        <v>63</v>
+      </c>
+      <c r="I201" t="n">
+        <v>72</v>
+      </c>
+      <c r="J201" t="n">
+        <v>63</v>
+      </c>
+      <c r="K201" t="n">
+        <v>125</v>
+      </c>
+      <c r="L201" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O181"/>
+  <autoFilter ref="A1:O201"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Losers" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$201</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Gainers'!$A$1:$O$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Losers'!$A$1:$O$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -11560,7 +11560,6 @@
       <c r="L185" t="n">
         <v>15.4</v>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11800,7 +11799,6 @@
       <c r="L189" t="n">
         <v>10.72</v>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr">
         <is>
           <t>[]</t>
@@ -11857,7 +11855,6 @@
       <c r="L190" t="n">
         <v>10.25</v>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12158,7 +12155,6 @@
       <c r="L195" t="n">
         <v>7.68</v>
       </c>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr">
         <is>
           <t>[]</t>
@@ -12536,8 +12532,1224 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>KJMCFIN</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="F202" t="n">
+        <v>66.34999999999999</v>
+      </c>
+      <c r="G202" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="H202" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="I202" t="n">
+        <v>55.35</v>
+      </c>
+      <c r="J202" t="n">
+        <v>66.42</v>
+      </c>
+      <c r="K202" t="n">
+        <v>3326</v>
+      </c>
+      <c r="L202" t="n">
+        <v>20</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>['KJMC Financial Services Limited Announces Cessation of Suhas Sahakari as Independent Director and Other Committees, Effective August 09, 2026 - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>KRONOX</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="F203" t="n">
+        <v>155.01</v>
+      </c>
+      <c r="G203" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="H203" t="n">
+        <v>155.01</v>
+      </c>
+      <c r="I203" t="n">
+        <v>155.16</v>
+      </c>
+      <c r="J203" t="n">
+        <v>186.19</v>
+      </c>
+      <c r="K203" t="n">
+        <v>5889347</v>
+      </c>
+      <c r="L203" t="n">
+        <v>20</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Kronox Lab Sciences Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>['Kronox Lab Sciences Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Rs 246 Crore Acquisition: Indo Borax &amp; Chemicals to Acquire 64.26% Stake in Kronox Lab Sciences; Share Price Rises 7% - Dalal Street Investment Journal', 'Kronox Lab Sciences Limited announces Annual dividend, payable on October 16, 2026 - marketscreener.com', 'Indo Borax &amp; Chemicals board approves acquisition of majority stake in Kronox Lab Sciences - Business Standard', 'Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>MPDL</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>MPDL Limited</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="F204" t="n">
+        <v>34.3</v>
+      </c>
+      <c r="G204" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="H204" t="n">
+        <v>23.26</v>
+      </c>
+      <c r="I204" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="J204" t="n">
+        <v>34.32</v>
+      </c>
+      <c r="K204" t="n">
+        <v>8795</v>
+      </c>
+      <c r="L204" t="n">
+        <v>20</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>['MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'MPDL Ltd Balance Sheet – NSE:MPDL - TradingView', 'MPDL Ltd Statistics – NSE:MPDL - TradingView', 'Number of employees of MPDL Ltd – NSE:MPDL - TradingView']</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>MYSORPETRO</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>165.49</v>
+      </c>
+      <c r="F205" t="n">
+        <v>160</v>
+      </c>
+      <c r="G205" t="n">
+        <v>165.49</v>
+      </c>
+      <c r="H205" t="n">
+        <v>155.3</v>
+      </c>
+      <c r="I205" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="J205" t="n">
+        <v>165.49</v>
+      </c>
+      <c r="K205" t="n">
+        <v>383979</v>
+      </c>
+      <c r="L205" t="n">
+        <v>20</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>['Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView', 'Non-controlling/minority interest of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView']</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>SAMBANDAM</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills Limited</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>126</v>
+      </c>
+      <c r="F206" t="n">
+        <v>114</v>
+      </c>
+      <c r="G206" t="n">
+        <v>126</v>
+      </c>
+      <c r="H206" t="n">
+        <v>113.99</v>
+      </c>
+      <c r="I206" t="n">
+        <v>105</v>
+      </c>
+      <c r="J206" t="n">
+        <v>126</v>
+      </c>
+      <c r="K206" t="n">
+        <v>8931</v>
+      </c>
+      <c r="L206" t="n">
+        <v>20</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Sambandam Spinning Mills Q1 Results: સતત નુકસાન બાદ કંપની ફરી નફામાં, બોર્ડમાં મોટા ફેરફારના સંકેત! - Whalesbook</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>['Sambandam Spinning Mills Q1 Results: સતત નુકસાન બાદ કંપની ફરી નફામાં, બોર્ડમાં મોટા ફેરફારના સંકેત! - Whalesbook', 'Price to sales forward of Sambandam Spinning Mills Limited – BSE:SAMBANDAM - TradingView', 'Sambandam Spinning Mills Limited Balance Sheet – NSE:SAMBANDAM - TradingView', 'Sambandam Spinning Mills Limited Statistics – NSE:SAMBANDAM - TradingView', "Sambandam Spinning Mills Ltd leads gainers in 'B' group - Business Standard"]</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>MINALIND</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Minal Industries Limited</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="F207" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="G207" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="H207" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="I207" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="J207" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="K207" t="n">
+        <v>312753</v>
+      </c>
+      <c r="L207" t="n">
+        <v>19.91</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>['MINALIND Share Price Today - Minal Industries Stock Analysis - Equitypandit', 'Total common shares outstanding of Minal Industries Limited – NSE:MINALIND - TradingView', 'Minal Industries Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Minal Industries Limited Cash Flow – NSE:MINALIND - TradingView', 'Minal Industries Limited Statistics – NSE:MINALIND - TradingView']</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>CRSL</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F208" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="G208" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="H208" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I208" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="J208" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="K208" t="n">
+        <v>8160299</v>
+      </c>
+      <c r="L208" t="n">
+        <v>19.77</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>['Cressanda Railway Solutions Limited Reports Earnings Results for the Fourth Quarter and Full Year Ended March 31, 2026 - marketscreener.com', 'Total liabilities of Cressanda Railway Solutions Ltd – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Income Statement – NSE:CRSL - TradingView', 'Cressanda Railway Solutions Ltd Statistics – NSE:CRSL - TradingView', 'CRSL title race takes shape as leading trio pull clear - Herald.co.zw']</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>BALRAMCHIN</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Limited</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>778</v>
+      </c>
+      <c r="F209" t="n">
+        <v>658.25</v>
+      </c>
+      <c r="G209" t="n">
+        <v>780.95</v>
+      </c>
+      <c r="H209" t="n">
+        <v>655.05</v>
+      </c>
+      <c r="I209" t="n">
+        <v>650.8</v>
+      </c>
+      <c r="J209" t="n">
+        <v>778</v>
+      </c>
+      <c r="K209" t="n">
+        <v>33514941</v>
+      </c>
+      <c r="L209" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>['Balrampur Chini Mills Ltd. (BALRAMCHIN) Share Price Near 52-Week High: Stock Trades Within 2% of One-Year Peak - Univest', 'Balrampur Chini Mills Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'BALRAMCHIN: Revenue growth, firm sugar prices, and PLA project progress drive a positive outlook - TradingView', 'BALRAMCHIN: Q1 FY27 saw revenue growth, capital infusion, and a new independent director appointment - TradingView', 'Balrampur Chini Mills holds 50th AGM on Sept 16; treats interim dividend as final - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>VIRTUALG</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Virtual Global Education Limited</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I210" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J210" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="K210" t="n">
+        <v>1278374</v>
+      </c>
+      <c r="L210" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Virtual Global Education Ltd (VIRTUALG) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>['Virtual Global Education Ltd (VIRTUALG) Share Price Today, Quote, Latest Discussions, Interactive Chart and News - Stocktwits', 'VIRTUALG Share Price Today - Virtual Global Education Stock Analysis - Equitypandit', 'Operating cash flow per share of Virtual Global Education Ltd. – NSE:VIRTUALG - TradingView']</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>SOMICONVEY</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Somi Conveyor Beltings Limited</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>101</v>
+      </c>
+      <c r="F211" t="n">
+        <v>96</v>
+      </c>
+      <c r="G211" t="n">
+        <v>103.93</v>
+      </c>
+      <c r="H211" t="n">
+        <v>95</v>
+      </c>
+      <c r="I211" t="n">
+        <v>86.61</v>
+      </c>
+      <c r="J211" t="n">
+        <v>101</v>
+      </c>
+      <c r="K211" t="n">
+        <v>687119</v>
+      </c>
+      <c r="L211" t="n">
+        <v>16.61</v>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>BAJAJHIND</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Bajaj Hindusthan Sugar Limited</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="F212" t="n">
+        <v>20.74</v>
+      </c>
+      <c r="G212" t="n">
+        <v>23.98</v>
+      </c>
+      <c r="H212" t="n">
+        <v>20.59</v>
+      </c>
+      <c r="I212" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="J212" t="n">
+        <v>23.76</v>
+      </c>
+      <c r="K212" t="n">
+        <v>256556792</v>
+      </c>
+      <c r="L212" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Balrampur Chini, Bajaj Hind, Shree Renuka shares rise up to 13%; here's why - Business Today</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>["Balrampur Chini, Bajaj Hind, Shree Renuka shares rise up to 13%; here's why - Business Today", 'Sugar stocks jump up to 4% despite tighter stockholding limits as government moves to curb record prices - TradingView', 'Bajaj Hindusthan, Shiprocket, VIL Among Most‑Traded Stocks - HDFC Sky']</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>DWARKESH</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Limited</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="F213" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="G213" t="n">
+        <v>56.45</v>
+      </c>
+      <c r="H213" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="I213" t="n">
+        <v>48.28</v>
+      </c>
+      <c r="J213" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="K213" t="n">
+        <v>42670090</v>
+      </c>
+      <c r="L213" t="n">
+        <v>15.78</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>['Dwarikesh Sugar Industries Ltd. (DWARKESH) Share Price Rises 8.84% Today - Univest', 'AI: The ‘Dwarkesh’ Compute Demand Bull Case (part 2). AI-RTZ #1174 - AI: Reset to Zero']</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>KWIL</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Kwality Wall's (India) Limited</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="F214" t="n">
+        <v>38</v>
+      </c>
+      <c r="G214" t="n">
+        <v>44.3</v>
+      </c>
+      <c r="H214" t="n">
+        <v>37.75</v>
+      </c>
+      <c r="I214" t="n">
+        <v>37.71</v>
+      </c>
+      <c r="J214" t="n">
+        <v>43.35</v>
+      </c>
+      <c r="K214" t="n">
+        <v>101299688</v>
+      </c>
+      <c r="L214" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Kwality Wall’s Reports Q1 FY27 Revenue of ₹878.3 Cr; Net Profit Jumps to ₹50.7 Cr - Trade Brains</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>['Kwality Wall’s Reports Q1 FY27 Revenue of ₹878.3 Cr; Net Profit Jumps to ₹50.7 Cr - Trade Brains', 'Kwality Walls (India) Reports Q1 Consolidated Net Profit of 507M Rupees Versus 376M YoY - Sahi']</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>INDOBORAX</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Indo Borax &amp; Chemicals Limited</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>498.1</v>
+      </c>
+      <c r="F215" t="n">
+        <v>439</v>
+      </c>
+      <c r="G215" t="n">
+        <v>509.9</v>
+      </c>
+      <c r="H215" t="n">
+        <v>431</v>
+      </c>
+      <c r="I215" t="n">
+        <v>433.85</v>
+      </c>
+      <c r="J215" t="n">
+        <v>498.1</v>
+      </c>
+      <c r="K215" t="n">
+        <v>6099644</v>
+      </c>
+      <c r="L215" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Price to sales forward of Indo Borax &amp; Chemicals Limited – NSE:INDOBORAX - TradingView</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>['Price to sales forward of Indo Borax &amp; Chemicals Limited – NSE:INDOBORAX - TradingView', 'Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com', 'Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky', 'Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade', 'Indo Borax Acquires 64.26% Stake in Kronox Lab for Rs 246 Crore - Whalesbook']</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>SOLARA</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>631.5</v>
+      </c>
+      <c r="F216" t="n">
+        <v>551.95</v>
+      </c>
+      <c r="G216" t="n">
+        <v>654.4</v>
+      </c>
+      <c r="H216" t="n">
+        <v>551.95</v>
+      </c>
+      <c r="I216" t="n">
+        <v>550.05</v>
+      </c>
+      <c r="J216" t="n">
+        <v>631.5</v>
+      </c>
+      <c r="K216" t="n">
+        <v>6915687</v>
+      </c>
+      <c r="L216" t="n">
+        <v>14.81</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>['Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest', 'Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest', 'Solara Active Pharma Sciences Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo', "Developer Files Pre-Application for Eight-Story 'Solara Village' at 1060 N.W. 79th St., Miami, Florida - Florida YIMBY", "Employment Law Attorneys, at Blumenthal Nordrehaug Bhowmik De Blouw LLP, File Lawsuit Against Solara Home Energy, LLC, for Underpayment of Employees' Wages - PR Newswire"]</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>BANARISUG</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Limited</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>4142.5</v>
+      </c>
+      <c r="F217" t="n">
+        <v>3635</v>
+      </c>
+      <c r="G217" t="n">
+        <v>4338</v>
+      </c>
+      <c r="H217" t="n">
+        <v>3635</v>
+      </c>
+      <c r="I217" t="n">
+        <v>3617.4</v>
+      </c>
+      <c r="J217" t="n">
+        <v>4142.5</v>
+      </c>
+      <c r="K217" t="n">
+        <v>71353</v>
+      </c>
+      <c r="L217" t="n">
+        <v>14.52</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>['Bannari Amman Sugars Posts Quarterly Loss Despite Strong Revenues - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>PACIFICI</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Pacific Industries Limited</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="F218" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="G218" t="n">
+        <v>159</v>
+      </c>
+      <c r="H218" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="I218" t="n">
+        <v>133.55</v>
+      </c>
+      <c r="J218" t="n">
+        <v>152.9</v>
+      </c>
+      <c r="K218" t="n">
+        <v>8374</v>
+      </c>
+      <c r="L218" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>Non-controlling/minority interest of Pacific Industries Ltd. – NSE:PACIFICI - TradingView</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>['Non-controlling/minority interest of Pacific Industries Ltd. – NSE:PACIFICI - TradingView', 'Seabed Mason Greenwood (IZgSO65kCu) - Mshale']</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>MEDICAPQ</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Medi Caps Limited</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="G219" t="n">
+        <v>27.49</v>
+      </c>
+      <c r="H219" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="I219" t="n">
+        <v>23.56</v>
+      </c>
+      <c r="J219" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="K219" t="n">
+        <v>7427</v>
+      </c>
+      <c r="L219" t="n">
+        <v>14.09</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>MEDICAPQ Share Price Today - Medi Caps Stock Analysis - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>['MEDICAPQ Share Price Today - Medi Caps Stock Analysis - Equitypandit', 'Medi-Caps Ltd. Cash Flow – NSE:MEDICAPQ - TradingView', 'Return on assets % of Medi-Caps Ltd. – NSE:MEDICAPQ - TradingView']</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>SUVEN</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Limited</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="F220" t="n">
+        <v>335</v>
+      </c>
+      <c r="G220" t="n">
+        <v>377.45</v>
+      </c>
+      <c r="H220" t="n">
+        <v>335</v>
+      </c>
+      <c r="I220" t="n">
+        <v>332.55</v>
+      </c>
+      <c r="J220" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="K220" t="n">
+        <v>3256478</v>
+      </c>
+      <c r="L220" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>['Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit', 'Suven Life Sciences reports consolidated net loss of Rs 127.61 crore in the June 2026 quarter - Business Standard', 'Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView', 'Suven Life Sciences Ltd. Share Price at Fresh 52-Week High - Univest', 'Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest']</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Gainer</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>UGARSUGAR</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Limited</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="F221" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="G221" t="n">
+        <v>57.64</v>
+      </c>
+      <c r="H221" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="I221" t="n">
+        <v>50.41</v>
+      </c>
+      <c r="J221" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="K221" t="n">
+        <v>3789593</v>
+      </c>
+      <c r="L221" t="n">
+        <v>12.64</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>['The Ugar Sugar Works Share Price Today: 9.09% Price Rise - Univest']</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
+  <autoFilter ref="A1:O221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -12548,7 +13760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O201"/>
+  <dimension ref="A1:O221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -23978,7 +25190,6 @@
       <c r="L190" t="n">
         <v>-4.87</v>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24401,7 +25612,6 @@
       <c r="L197" t="n">
         <v>-5</v>
       </c>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24641,7 +25851,6 @@
       <c r="L201" t="n">
         <v>-12.5</v>
       </c>
-      <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr">
         <is>
           <t>[]</t>
@@ -24653,8 +25862,1212 @@
         </is>
       </c>
     </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>KSR</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>KSR Footwear Limited</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="F202" t="n">
+        <v>28.51</v>
+      </c>
+      <c r="G202" t="n">
+        <v>30</v>
+      </c>
+      <c r="H202" t="n">
+        <v>27</v>
+      </c>
+      <c r="I202" t="n">
+        <v>28.84</v>
+      </c>
+      <c r="J202" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="K202" t="n">
+        <v>77843</v>
+      </c>
+      <c r="L202" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>KSR Footwear Q1 Results: Net profit turns positive to ₹3.17 million - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>['KSR Footwear Q1 Results: Net profit turns positive to ₹3.17 million - scanx.trade', 'KSR Footwear Q1 results FY27: PAT Rs 32 Lakh, Revenue Rs 52 Cr - Univest', 'KSR CBSE School celebrates Independence Day - Deccan Herald', 'KSR Show, 8/19: Live from 10 a.m. to noon with Billy in charge - On3', "KSR Show, 8/18: Celebrating Ryan Lemond's birthday - On3"]</t>
+        </is>
+      </c>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>INDOMIM</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>INDO-MIM Limited</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>916.7</v>
+      </c>
+      <c r="F203" t="n">
+        <v>965</v>
+      </c>
+      <c r="G203" t="n">
+        <v>965</v>
+      </c>
+      <c r="H203" t="n">
+        <v>907.3</v>
+      </c>
+      <c r="I203" t="n">
+        <v>967.95</v>
+      </c>
+      <c r="J203" t="n">
+        <v>916.7</v>
+      </c>
+      <c r="K203" t="n">
+        <v>3493814</v>
+      </c>
+      <c r="L203" t="n">
+        <v>-5.29</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>INDOMIM Historical Data - Equitypandit</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>['INDOMIM Historical Data - Equitypandit', 'Indo-Mim Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'INDO-MIM Board Clears Q1 FY27 Unaudited Results, Publishes in Newspapers - TipRanks', 'INDO-MIM Board Clears Q1 FY27 Results, New Secretarial Auditor and ESOP Ratification - TipRanks', 'INDO-MIM Board Clears Quarterly Results, Governance Moves and ESOP Plan - TipRanks']</t>
+        </is>
+      </c>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>DREDGECORP</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>1126</v>
+      </c>
+      <c r="F204" t="n">
+        <v>1199</v>
+      </c>
+      <c r="G204" t="n">
+        <v>1204</v>
+      </c>
+      <c r="H204" t="n">
+        <v>1111.5</v>
+      </c>
+      <c r="I204" t="n">
+        <v>1189.2</v>
+      </c>
+      <c r="J204" t="n">
+        <v>1126</v>
+      </c>
+      <c r="K204" t="n">
+        <v>253900</v>
+      </c>
+      <c r="L204" t="n">
+        <v>-5.31</v>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>AHLADA</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers Limited</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="F205" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="G205" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="H205" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I205" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="J205" t="n">
+        <v>38.51</v>
+      </c>
+      <c r="K205" t="n">
+        <v>42109</v>
+      </c>
+      <c r="L205" t="n">
+        <v>-5.66</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>Ahlada Engineers standalone net profit declines 70.69% in the June 2026 quarter - Business Standard</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>['Ahlada Engineers standalone net profit declines 70.69% in the June 2026 quarter - Business Standard', 'Primer: Ahlada Engineers (AHLADA IN) - Aug 2026 - Smartkarma', 'NMDC Steel standalone net profit rises 97.61% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>GLOBECIVIL</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="F206" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="G206" t="n">
+        <v>45.46</v>
+      </c>
+      <c r="H206" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="I206" t="n">
+        <v>44.97</v>
+      </c>
+      <c r="J206" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="K206" t="n">
+        <v>102837</v>
+      </c>
+      <c r="L206" t="n">
+        <v>-5.71</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>['Globe Civil Projects Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Globe Civil Projects Q1 Results: Earnings call scheduled for Aug 25 - scanx.trade', 'Globe Civil Projects Limited Announces Q1 FY27 Results - ThePrint']</t>
+        </is>
+      </c>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>BALAXI</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>BALAXI PHARMACEUTICALS LIMITED</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="F207" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="G207" t="n">
+        <v>24.2</v>
+      </c>
+      <c r="H207" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="I207" t="n">
+        <v>23.79</v>
+      </c>
+      <c r="J207" t="n">
+        <v>22.39</v>
+      </c>
+      <c r="K207" t="n">
+        <v>139295</v>
+      </c>
+      <c r="L207" t="n">
+        <v>-5.88</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>['Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest', 'Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com', 'Unapproved emergency contraceptive, antibiotics seized in Montreal - CityNews Montreal', 'Health Canada seizes unauthorized contraceptives, antibiotics at Montreal store - CBC']</t>
+        </is>
+      </c>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>TIJARIA</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Limited</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="F208" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="G208" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="H208" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="I208" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="J208" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="K208" t="n">
+        <v>209055</v>
+      </c>
+      <c r="L208" t="n">
+        <v>-6.05</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>['Tijaria Polypipes Q1 Results: Net loss widens 36% YoY to ₹36.11 lakh - scanx.trade', 'Tijaria Polypipes Share Price Today, Tijaria Polypipes Stock Price Live NSE/BSE Updates - The Economic Times', 'Tijaria Polypipes board to approve Q2FY27 results, accept director resignation - scanx.trade', 'Tijaria Polypipes reports standalone net loss of Rs 0.36 crore in the June 2026 quarter - Business Standard', 'Bhatia Communications &amp; Retail (India) standalone net profit rises 90.50% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>DHABRIYA</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Limited</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>550</v>
+      </c>
+      <c r="F209" t="n">
+        <v>600</v>
+      </c>
+      <c r="G209" t="n">
+        <v>600</v>
+      </c>
+      <c r="H209" t="n">
+        <v>548</v>
+      </c>
+      <c r="I209" t="n">
+        <v>587</v>
+      </c>
+      <c r="J209" t="n">
+        <v>550</v>
+      </c>
+      <c r="K209" t="n">
+        <v>59063</v>
+      </c>
+      <c r="L209" t="n">
+        <v>-6.3</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>['Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade', 'Dhabriya Polywood consolidated net profit rises 35.47% in the June 2026 quarter - Business Standard', 'Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView', 'Cost of goods sold of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView', 'Dhabriya Polywood Q1FY27 PAT up 35% to ₹8.86 crore; EBITDA margin expands - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>HSCL</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemical Limited</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>702.9</v>
+      </c>
+      <c r="F210" t="n">
+        <v>755</v>
+      </c>
+      <c r="G210" t="n">
+        <v>767.6</v>
+      </c>
+      <c r="H210" t="n">
+        <v>695.5</v>
+      </c>
+      <c r="I210" t="n">
+        <v>750.25</v>
+      </c>
+      <c r="J210" t="n">
+        <v>702.9</v>
+      </c>
+      <c r="K210" t="n">
+        <v>12482496</v>
+      </c>
+      <c r="L210" t="n">
+        <v>-6.31</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>['Himadri Speciality Chemicals Share Price - Live NSE: HSCL Stock Price &amp; Chart - Upstox', 'Himadri Speciality Chemical Ltd. (HSCL) Share Price Falls 7.32% Today - Univest', 'MoHUA Restructures NBCC Subsidiaries’ Boards; MD, Finance Posts Abolished in HSCL, Key Posts Scrapped in HSCC - Indianmasterminds', '5 Infra Stocks Under ₹100 With Strong Order Books Worth Up to ₹1.26 Lakh Cr to Keep on Your Radar - Trade Brains', 'RAILWAY BOARD LIKELY TO GET THREE ADDITIONAL MEMBERS SOON - IndianMandarins']</t>
+        </is>
+      </c>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>CENTEXT</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="F211" t="n">
+        <v>21.95</v>
+      </c>
+      <c r="G211" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="H211" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I211" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="J211" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="K211" t="n">
+        <v>441134</v>
+      </c>
+      <c r="L211" t="n">
+        <v>-6.39</v>
+      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>Century Extrusions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>['Century Extrusions Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Century Extrusions Limited Approves Appointment of Shri Charan Singh as A Non-Executive Independent Director - marketscreener.com']</t>
+        </is>
+      </c>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>LAXMICOT</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Laxmi Cotspin Limited</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="F212" t="n">
+        <v>15.26</v>
+      </c>
+      <c r="G212" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="H212" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="I212" t="n">
+        <v>14.89</v>
+      </c>
+      <c r="J212" t="n">
+        <v>13.92</v>
+      </c>
+      <c r="K212" t="n">
+        <v>64570</v>
+      </c>
+      <c r="L212" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>MILKYMIST</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Milky Mist Dairy Food Limited</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>186.11</v>
+      </c>
+      <c r="F213" t="n">
+        <v>207.8</v>
+      </c>
+      <c r="G213" t="n">
+        <v>211.8</v>
+      </c>
+      <c r="H213" t="n">
+        <v>181.5</v>
+      </c>
+      <c r="I213" t="n">
+        <v>199.65</v>
+      </c>
+      <c r="J213" t="n">
+        <v>186.11</v>
+      </c>
+      <c r="K213" t="n">
+        <v>56542171</v>
+      </c>
+      <c r="L213" t="n">
+        <v>-6.78</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>['Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Basic earnings per share (basic EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Price to earnings forward of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Gross profit of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Operating margin % of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView']</t>
+        </is>
+      </c>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>SINTERCOM</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="F214" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="G214" t="n">
+        <v>86.98999999999999</v>
+      </c>
+      <c r="H214" t="n">
+        <v>79.06</v>
+      </c>
+      <c r="I214" t="n">
+        <v>85</v>
+      </c>
+      <c r="J214" t="n">
+        <v>79.11</v>
+      </c>
+      <c r="K214" t="n">
+        <v>5959</v>
+      </c>
+      <c r="L214" t="n">
+        <v>-6.93</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>['Sintercom India Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'Sintercom India standalone net profit rises 88.46% in the June 2026 quarter - Business Standard', 'Axita Cotton standalone net profit rises 122.98% in the June 2026 quarter - Business Standard', 'Parvati Sweetners and Power reports standalone net profit of Rs 0.32 crore in the June 2026 quarter - Business Standard', 'Bliss GVS Pharma consolidated net profit rises 16.40% in the June 2026 quarter - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>GCSL</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Limited</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="F215" t="n">
+        <v>526.3</v>
+      </c>
+      <c r="G215" t="n">
+        <v>540.95</v>
+      </c>
+      <c r="H215" t="n">
+        <v>470</v>
+      </c>
+      <c r="I215" t="n">
+        <v>521.7</v>
+      </c>
+      <c r="J215" t="n">
+        <v>484.9</v>
+      </c>
+      <c r="K215" t="n">
+        <v>615899</v>
+      </c>
+      <c r="L215" t="n">
+        <v>-7.05</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>['Gretex Corporate Services Q1 Results: Revenue at ₹1,785 Mn, Net Profit ₹276 Mn - scanx.trade']</t>
+        </is>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ATAM</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Atam Valves Limited</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="F216" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="G216" t="n">
+        <v>60.95</v>
+      </c>
+      <c r="H216" t="n">
+        <v>54.6</v>
+      </c>
+      <c r="I216" t="n">
+        <v>59.36</v>
+      </c>
+      <c r="J216" t="n">
+        <v>54.75</v>
+      </c>
+      <c r="K216" t="n">
+        <v>88855</v>
+      </c>
+      <c r="L216" t="n">
+        <v>-7.77</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>['Atam Valves Q1 Results: Net profit falls 49% YoY to ₹63.5 lakh - scanx.trade', 'NJIT’s Atam Dhawan to Receive 2026 Catalyst Award - NJIT News']</t>
+        </is>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ADDIND</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Addi Industries Limited</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>80</v>
+      </c>
+      <c r="F217" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="G217" t="n">
+        <v>87.95</v>
+      </c>
+      <c r="H217" t="n">
+        <v>71.05</v>
+      </c>
+      <c r="I217" t="n">
+        <v>87</v>
+      </c>
+      <c r="J217" t="n">
+        <v>80</v>
+      </c>
+      <c r="K217" t="n">
+        <v>612</v>
+      </c>
+      <c r="L217" t="n">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits</t>
+        </is>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>['Addi Industries Ltd. (ADDIND) Fundamental and Financial Data - Stocktwits', 'After tax other income/expense of Addi Industries Limited – NSE:ADDIND - TradingView', 'Addi Industries Limited Income Statement – NSE:ADDIND - TradingView', 'Addi Industries Limited Statistics – NSE:ADDIND - TradingView']</t>
+        </is>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>BTML</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Bodhi Tree Multimedia Limited</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>8</v>
+      </c>
+      <c r="F218" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="G218" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="H218" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="I218" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="J218" t="n">
+        <v>8</v>
+      </c>
+      <c r="K218" t="n">
+        <v>1261909</v>
+      </c>
+      <c r="L218" t="n">
+        <v>-8.26</v>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>WEL</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Wonder Electricals Limited</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="F219" t="n">
+        <v>148.4</v>
+      </c>
+      <c r="G219" t="n">
+        <v>149.78</v>
+      </c>
+      <c r="H219" t="n">
+        <v>132</v>
+      </c>
+      <c r="I219" t="n">
+        <v>146.26</v>
+      </c>
+      <c r="J219" t="n">
+        <v>133.8</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1505698</v>
+      </c>
+      <c r="L219" t="n">
+        <v>-8.52</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 #WelbloomBioTech - Media OutReach Newswire</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>['Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 #WelbloomBioTech - Media OutReach Newswire', 'Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 - Bluefield Daily Telegraph', 'Grand final rematch to open new women’s season - Wellington Phoenix FC', 'Date set for Porirua Park return - Wellington Phoenix FC', 'New week grind, gm this Monday Nothing beats knowing how wel - KuCoin']</t>
+        </is>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>KAMANWALA</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Kamanwala Housing Construction Limited</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="F220" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="G220" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="H220" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="I220" t="n">
+        <v>18.63</v>
+      </c>
+      <c r="J220" t="n">
+        <v>16.99</v>
+      </c>
+      <c r="K220" t="n">
+        <v>56343</v>
+      </c>
+      <c r="L220" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>['Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView', 'Kamanwala Housing &amp; Construction Ltd. Cash Flow – NSE:KAMANWALA - TradingView', "Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard", 'Chinese stocks rebound as policy hopes build - Business Standard', 'Japanese stocks rebound as bond yields ease - Business Standard']</t>
+        </is>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-08-20 16:29:44 IST</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Loser</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>TECILCHEM</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>TECIL Chemicals and Hydro Power Limited</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="F221" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="G221" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H221" t="n">
+        <v>9</v>
+      </c>
+      <c r="I221" t="n">
+        <v>10.24</v>
+      </c>
+      <c r="J221" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="K221" t="n">
+        <v>306274</v>
+      </c>
+      <c r="L221" t="n">
+        <v>-11.62</v>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>AI remarks unavailable.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O201"/>
+  <autoFilter ref="A1:O221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -12535,7 +12535,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12596,7 +12596,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12657,7 +12657,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>['MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'MPDL Ltd Balance Sheet – NSE:MPDL - TradingView', 'MPDL Ltd Statistics – NSE:MPDL - TradingView', 'Number of employees of MPDL Ltd – NSE:MPDL - TradingView']</t>
+          <t>['MPDL Limited Reports Earnings Results for the First Quarter Ended June 30, 2026 - marketscreener.com', 'MPDL Ltd Q1 Results: Board approves financials for quarter ended June 30 - scanx.trade', 'Total common shares outstanding of MPDL Ltd – NSE:MPDL - TradingView', 'MPDL Ltd Balance Sheet – NSE:MPDL - TradingView', 'MPDL Ltd Statistics – NSE:MPDL - TradingView']</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -12718,7 +12718,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12762,12 +12762,12 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView</t>
+          <t>Number of employees of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
         <is>
-          <t>['Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView', 'Non-controlling/minority interest of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView']</t>
+          <t>['Number of employees of Mysore Petro Chemicals Limited – NSE:MYSORPETRO - TradingView', 'Mysore Petro Chemicals Limited Financial Statements – NSE:MYSORPETRO - TradingView']</t>
         </is>
       </c>
       <c r="O205" t="inlineStr">
@@ -12779,7 +12779,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12840,7 +12840,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12901,7 +12901,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12962,7 +12962,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13023,7 +13023,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13084,7 +13084,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13141,7 +13141,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -13263,7 +13263,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -13324,7 +13324,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="N215" t="inlineStr">
         <is>
-          <t>['Price to sales forward of Indo Borax &amp; Chemicals Limited – NSE:INDOBORAX - TradingView', 'Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com', 'Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky', 'Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade', 'Indo Borax Acquires 64.26% Stake in Kronox Lab for Rs 246 Crore - Whalesbook']</t>
+          <t>['Price to sales forward of Indo Borax &amp; Chemicals Limited – NSE:INDOBORAX - TradingView', 'Indo Borax &amp; Chemicals Limited executed a Share Purchase Agreement to acquire 64.26% stake in Kronox Lab Sciences Limited from Ketan Vinodchandra Ramani, Pritesh Vinodchandra Ramani and Jogindersingh Gianchand Jaswal for INR 2.5 billion. - marketscreener.com', 'Indo Borax &amp; Chemicals Ltd. Share Price Today Gains 10.15% - Univest', 'Indo Borax Approves Kronox Lab Stake Purchase; Shares Rise 7.44% - HDFC Sky', 'Kronox Lab Sciences promoters sell 64.26% stake to Indo Borax - scanx.trade']</t>
         </is>
       </c>
       <c r="O215" t="inlineStr">
@@ -13385,7 +13385,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="N216" t="inlineStr">
         <is>
-          <t>['Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest', 'Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest', 'Solara Active Pharma Sciences Ltd Upgraded to Hold on Technical and Financial Improvements - MarketsMojo', "Developer Files Pre-Application for Eight-Story 'Solara Village' at 1060 N.W. 79th St., Miami, Florida - Florida YIMBY", "Employment Law Attorneys, at Blumenthal Nordrehaug Bhowmik De Blouw LLP, File Lawsuit Against Solara Home Energy, LLC, for Underpayment of Employees' Wages - PR Newswire"]</t>
+          <t>['Solara Active Pharma Sciences Ltd. Share Price Rises 8.49% - Univest', 'Solara Active Pharma Sciences Ltd. Share Price Today Up - Univest', "Employment Law Attorneys, at Blumenthal Nordrehaug Bhowmik De Blouw LLP, File Lawsuit Against Solara Home Energy, LLC, for Underpayment of Employees' Wages - PR Newswire", "Developer Files Pre-Application for Eight-Story 'Solara Village' at 1060 N.W. 79th St., Miami, Florida - Florida YIMBY", 'Armen Living’s new Solara Collection is Creating the Vibe for the Ultimate Outdoor Kitchen - The National Law Review']</t>
         </is>
       </c>
       <c r="O216" t="inlineStr">
@@ -13446,7 +13446,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -13507,7 +13507,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -13568,7 +13568,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -13629,7 +13629,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13678,7 +13678,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>['Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit', 'Suven Life Sciences reports consolidated net loss of Rs 127.61 crore in the June 2026 quarter - Business Standard', 'Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView', 'Suven Life Sciences Ltd. Share Price at Fresh 52-Week High - Univest', 'Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest']</t>
+          <t>['Suven Life Sciences Shares Decline Over 5% As Q1 Net Loss Widens To Rs 128 Crore - NDTV Profit', 'Suven Pharmaceuticals Q1 FY27 Results: Revenue &amp; PAT Highlights - Univest', 'Suven Life Sciences reports consolidated net loss of Rs 127.61 crore in the June 2026 quarter - Business Standard', 'Suven Life Sciences Limited Rights 2022-10.11.22 For Shares Revenue Breakdown – BSE:SUVEN_RE - TradingView', 'Suven Pharmaceuticals Ltd. Share Price News and Analysis - Univest']</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -13690,7 +13690,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -25865,7 +25865,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -25926,7 +25926,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -25987,7 +25987,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -26029,10 +26029,14 @@
       <c r="L204" t="n">
         <v>-5.31</v>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Dredging Corporation of India Q1 FY27 Results: Revenue Surges 46.7% YoY to ₹355 Crore, Returns to Profit - DredgeWire</t>
+        </is>
+      </c>
       <c r="N204" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['Dredging Corporation of India Q1 FY27 Results: Revenue Surges 46.7% YoY to ₹355 Crore, Returns to Profit - DredgeWire']</t>
         </is>
       </c>
       <c r="O204" t="inlineStr">
@@ -26044,7 +26048,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -26105,7 +26109,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -26166,7 +26170,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -26215,7 +26219,7 @@
       </c>
       <c r="N207" t="inlineStr">
         <is>
-          <t>['Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest', 'Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com', 'Unapproved emergency contraceptive, antibiotics seized in Montreal - CityNews Montreal', 'Health Canada seizes unauthorized contraceptives, antibiotics at Montreal store - CBC']</t>
+          <t>['Balaxi Pharma Q1 results FY27: PAT Rs 1 Cr, Revenue Rs 80 Cr - Univest', 'Balaxi Pharma Standalone June 2026 Net Sales at Rs 15.58 crore, down 6.73% Y-o-Y - Moneycontrol.com', 'Health Canada seizes unauthorized contraceptives, antibiotics at Montreal store - CBC']</t>
         </is>
       </c>
       <c r="O207" t="inlineStr">
@@ -26227,7 +26231,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -26288,7 +26292,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -26337,7 +26341,7 @@
       </c>
       <c r="N209" t="inlineStr">
         <is>
-          <t>['Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade', 'Dhabriya Polywood consolidated net profit rises 35.47% in the June 2026 quarter - Business Standard', 'Dhabriya Polywood Ltd Income Statement – NSE:DHABRIYA - TradingView', 'Cost of goods sold of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView', 'Dhabriya Polywood Q1FY27 PAT up 35% to ₹8.86 crore; EBITDA margin expands - scanx.trade']</t>
+          <t>['Dhabriya Polywood Q1 Results: Net profit rises 35% YoY to ₹885.81 lakh - scanx.trade', 'Dhabriya Polywood consolidated net profit rises 35.47% in the June 2026 quarter - Business Standard', 'Dhabriya Polywood Ltd. Share Price and 52-Week High View - Univest', 'Cost of goods sold of Dhabriya Polywood Ltd – NSE:DHABRIYA - TradingView', 'Dhabriya Polywood Q1FY27 PAT up 35% to ₹8.86 crore; EBITDA margin expands - scanx.trade']</t>
         </is>
       </c>
       <c r="O209" t="inlineStr">
@@ -26349,7 +26353,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -26410,7 +26414,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -26471,7 +26475,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -26528,7 +26532,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -26577,7 +26581,7 @@
       </c>
       <c r="N213" t="inlineStr">
         <is>
-          <t>['Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Basic earnings per share (basic EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Price to earnings forward of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Gross profit of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Operating margin % of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView']</t>
+          <t>['Diluted earnings per share (diluted EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Basic earnings per share (basic EPS) of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'EBITDA per share of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView', 'Milky Mist Dairy Food Ltd. Revenue Breakdown – NSE:MILKYMIST - TradingView', 'EBITDA margin % of Milky Mist Dairy Food Ltd. – NSE:MILKYMIST - TradingView']</t>
         </is>
       </c>
       <c r="O213" t="inlineStr">
@@ -26589,7 +26593,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -26650,7 +26654,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -26711,7 +26715,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -26772,7 +26776,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -26833,7 +26837,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -26890,7 +26894,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -26934,12 +26938,12 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 #WelbloomBioTech - Media OutReach Newswire</t>
+          <t>Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 - pan african visions</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
         <is>
-          <t>['Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 #WelbloomBioTech - Media OutReach Newswire', 'Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 - Bluefield Daily Telegraph', 'Grand final rematch to open new women’s season - Wellington Phoenix FC', 'Date set for Porirua Park return - Wellington Phoenix FC', 'New week grind, gm this Monday Nothing beats knowing how wel - KuCoin']</t>
+          <t>['Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 - pan african visions', 'Wel-Bloom to Showcase Functional Jelly Innovations at Vitafoods Asia 2026 - Bluefield Daily Telegraph', 'Grand final rematch to open new women’s season - Wellington Phoenix FC', 'Date set for Porirua Park return - Wellington Phoenix FC', 'New week grind, gm this Monday Nothing beats knowing how wel - KuCoin']</t>
         </is>
       </c>
       <c r="O219" t="inlineStr">
@@ -26951,7 +26955,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -27000,7 +27004,7 @@
       </c>
       <c r="N220" t="inlineStr">
         <is>
-          <t>['Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView', 'Kamanwala Housing &amp; Construction Ltd. Cash Flow – NSE:KAMANWALA - TradingView', "Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard", 'Chinese stocks rebound as policy hopes build - Business Standard', 'Japanese stocks rebound as bond yields ease - Business Standard']</t>
+          <t>['Return on assets % of Kamanwala Housing &amp; Construction Ltd. – NSE:KAMANWALA - TradingView', 'Kamanwala Housing &amp; Construction Ltd. Cash Flow – NSE:KAMANWALA - TradingView', "Kamanwala Housing Construction Ltd leads losers in 'B' group - Business Standard", "Kamanwala Housing Construction Ltd leads losers in 'B' group - Dailyhunt", 'Chinese stocks rebound as policy hopes build - Business Standard']</t>
         </is>
       </c>
       <c r="O220" t="inlineStr">
@@ -27012,7 +27016,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>2026-08-20 16:29:44 IST</t>
+          <t>2026-08-20 16:49:59 IST</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">

--- a/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
+++ b/NSE_MARKET_REPORT/output/excel/NSE_Market_Report.xlsx
@@ -13126,7 +13126,6 @@
       <c r="L211" t="n">
         <v>16.61</v>
       </c>
-      <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr">
         <is>
           <t>[]</t>
@@ -26517,7 +26516,6 @@
       <c r="L212" t="n">
         <v>-6.51</v>
       </c>
-      <c r="M212" t="inlineStr"/>
       <c r="N212" t="inlineStr">
         <is>
           <t>[]</t>
@@ -26879,7 +26877,6 @@
       <c r="L218" t="n">
         <v>-8.26</v>
       </c>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="inlineStr">
         <is>
           <t>[]</t>
@@ -27058,7 +27055,6 @@
       <c r="L221" t="n">
         <v>-11.62</v>
       </c>
-      <c r="M221" t="inlineStr"/>
       <c r="N221" t="inlineStr">
         <is>
           <t>[]</t>
